--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59AC972-0017-42D0-BDDA-18D12A990782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D0DD618-EB17-4751-A296-1C5650DB012B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="45">
   <si>
     <t>Id</t>
   </si>
@@ -74,24 +74,6 @@
     <t>選択仲間加入</t>
   </si>
   <si>
-    <t>エリシャ加入</t>
-  </si>
-  <si>
-    <t>ソラ加入</t>
-  </si>
-  <si>
-    <t>リジェ加入</t>
-  </si>
-  <si>
-    <t>ミシェル加入</t>
-  </si>
-  <si>
-    <t>シイナ加入</t>
-  </si>
-  <si>
-    <t>ルネ加入</t>
-  </si>
-  <si>
     <t>魔法・ウォーターヒール</t>
   </si>
   <si>
@@ -171,13 +153,17 @@
   </si>
   <si>
     <t>Ending</t>
+  </si>
+  <si>
+    <t>加入</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,6 +173,14 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -215,8 +209,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -748,8 +745,8 @@
       <c r="E15" t="s">
         <v>15</v>
       </c>
-      <c r="F15" t="s">
-        <v>17</v>
+      <c r="F15" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -768,8 +765,8 @@
       <c r="E16" t="s">
         <v>15</v>
       </c>
-      <c r="F16" t="s">
-        <v>18</v>
+      <c r="F16" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -788,8 +785,8 @@
       <c r="E17" t="s">
         <v>15</v>
       </c>
-      <c r="F17" t="s">
-        <v>19</v>
+      <c r="F17" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -808,8 +805,8 @@
       <c r="E18" t="s">
         <v>15</v>
       </c>
-      <c r="F18" t="s">
-        <v>20</v>
+      <c r="F18" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -828,8 +825,8 @@
       <c r="E19" t="s">
         <v>15</v>
       </c>
-      <c r="F19" t="s">
-        <v>21</v>
+      <c r="F19" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -848,8 +845,8 @@
       <c r="E20" t="s">
         <v>15</v>
       </c>
-      <c r="F20" t="s">
-        <v>22</v>
+      <c r="F20" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -866,7 +863,7 @@
         <v>10</v>
       </c>
       <c r="E21" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -883,7 +880,7 @@
         <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -900,7 +897,7 @@
         <v>10</v>
       </c>
       <c r="E23" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -917,7 +914,7 @@
         <v>10</v>
       </c>
       <c r="E24" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -934,7 +931,7 @@
         <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
@@ -951,7 +948,7 @@
         <v>10</v>
       </c>
       <c r="E26" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
@@ -968,7 +965,7 @@
         <v>10</v>
       </c>
       <c r="E27" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -985,7 +982,7 @@
         <v>10</v>
       </c>
       <c r="E28" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -1002,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -1019,7 +1016,7 @@
         <v>20</v>
       </c>
       <c r="E30" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -1036,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -1053,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -1070,7 +1067,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -1087,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
@@ -1104,7 +1101,7 @@
         <v>20</v>
       </c>
       <c r="E35" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -1121,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
@@ -1138,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -1155,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -1172,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -1189,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -1206,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -1223,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -1240,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -1257,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
@@ -1274,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
@@ -1291,7 +1288,7 @@
         <v>210</v>
       </c>
       <c r="E46" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
@@ -1308,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -1325,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
@@ -1342,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
@@ -1359,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
@@ -1376,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
@@ -1393,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
@@ -1410,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
@@ -1427,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
@@ -1444,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
@@ -1461,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
@@ -1478,7 +1475,7 @@
         <v>210</v>
       </c>
       <c r="E57" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
@@ -1495,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
@@ -1512,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
@@ -1529,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
@@ -1546,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
@@ -1563,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
@@ -1580,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
@@ -1597,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
@@ -1614,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
@@ -1631,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
@@ -1648,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
@@ -1665,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
@@ -1682,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
@@ -1699,7 +1696,7 @@
         <v>210</v>
       </c>
       <c r="E70" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
@@ -1716,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
@@ -1733,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
@@ -1750,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
@@ -1767,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
@@ -1784,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
@@ -1801,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
@@ -1818,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
@@ -1835,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
@@ -1852,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="E79" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
@@ -1869,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
@@ -1886,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
@@ -1903,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
@@ -1920,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
@@ -1937,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
@@ -1954,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
@@ -1971,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
@@ -1988,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
@@ -2005,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
@@ -2022,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
@@ -2039,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
@@ -2056,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -2072,7 +2069,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -2080,7 +2077,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -2088,7 +2085,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -2096,7 +2093,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -2104,7 +2101,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -2120,7 +2117,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -2128,7 +2125,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -2136,7 +2133,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -2144,7 +2141,7 @@
         <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -2152,7 +2149,7 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -2160,7 +2157,7 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -2168,7 +2165,7 @@
         <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -2176,7 +2173,7 @@
         <v>101</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -2184,7 +2181,7 @@
         <v>210</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D0DD618-EB17-4751-A296-1C5650DB012B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4194CF3-88C2-4595-9C3B-67D13432D628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,12 @@
     <sheet name="PrizeSets" sheetId="1" r:id="rId1"/>
     <sheet name="Define" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="37">
   <si>
     <t>Id</t>
   </si>
@@ -74,34 +74,10 @@
     <t>選択仲間加入</t>
   </si>
   <si>
-    <t>魔法・ウォーターヒール</t>
-  </si>
-  <si>
-    <t>魔法ランダム</t>
-  </si>
-  <si>
-    <t>魔法・ブラッドドレイン</t>
-  </si>
-  <si>
-    <t>魔法選択</t>
-  </si>
-  <si>
-    <t>魔法・リフレッシュ</t>
-  </si>
-  <si>
-    <t>救出</t>
-  </si>
-  <si>
-    <t>Nu</t>
-  </si>
-  <si>
     <t>Nu獲得量アップ</t>
   </si>
   <si>
     <t>敵Lvアップ</t>
-  </si>
-  <si>
-    <t>ED</t>
   </si>
   <si>
     <t>魔法</t>
@@ -491,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -746,7 +722,7 @@
         <v>15</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -766,7 +742,7 @@
         <v>15</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -786,7 +762,7 @@
         <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -806,7 +782,7 @@
         <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -826,7 +802,7 @@
         <v>15</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -846,55 +822,55 @@
         <v>15</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>1011</v>
+        <v>11010</v>
       </c>
       <c r="B21">
         <v>100</v>
       </c>
       <c r="C21">
-        <v>3120</v>
+        <v>11010</v>
       </c>
       <c r="D21">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>1021</v>
+        <v>11020</v>
       </c>
       <c r="B22">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>11020</v>
       </c>
       <c r="D22">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>1031</v>
+        <v>11030</v>
       </c>
       <c r="B23">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>5110</v>
+        <v>11030</v>
       </c>
       <c r="D23">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
@@ -902,1158 +878,291 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>1041</v>
+        <v>11040</v>
       </c>
       <c r="B24">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>11040</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>1101</v>
+        <v>12020</v>
       </c>
       <c r="B25">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>3</v>
+        <v>12020</v>
       </c>
       <c r="D25">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>2011</v>
+        <v>12030</v>
       </c>
       <c r="B26">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>12030</v>
       </c>
       <c r="D26">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>2021</v>
+        <v>12040</v>
       </c>
       <c r="B27">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>12040</v>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>2022</v>
+        <v>13020</v>
       </c>
       <c r="B28">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>13020</v>
       </c>
       <c r="D28">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>2031</v>
+        <v>13030</v>
       </c>
       <c r="B29">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>14110</v>
+        <v>13030</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>2101</v>
+        <v>13040</v>
       </c>
       <c r="B30">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>5</v>
+        <v>13040</v>
       </c>
       <c r="D30">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>3041</v>
+        <v>14010</v>
       </c>
       <c r="B31">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>14010</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>3041</v>
+        <v>14020</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>30</v>
+        <v>14020</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>3042</v>
+        <v>14030</v>
       </c>
       <c r="B33">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>14030</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>3042</v>
+        <v>15020</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34">
-        <v>50</v>
+        <v>15020</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>3042</v>
+        <v>15030</v>
       </c>
       <c r="B35">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>15030</v>
       </c>
       <c r="D35">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>3101</v>
+        <v>15050</v>
       </c>
       <c r="B36">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>15050</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>3101</v>
+        <v>20010</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="C37">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>3102</v>
+        <v>20020</v>
       </c>
       <c r="B38">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>3102</v>
+        <v>20030</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="C39">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>3102</v>
+        <v>20040</v>
       </c>
       <c r="B40">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="C40">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>3102</v>
-      </c>
-      <c r="B41">
-        <v>63</v>
-      </c>
-      <c r="C41">
-        <v>5</v>
-      </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-      <c r="E41" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>4041</v>
-      </c>
-      <c r="B42">
-        <v>61</v>
-      </c>
-      <c r="C42">
-        <v>2</v>
-      </c>
-      <c r="D42">
-        <v>0</v>
-      </c>
-      <c r="E42" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>4041</v>
-      </c>
-      <c r="B43">
-        <v>2</v>
-      </c>
-      <c r="C43">
-        <v>40</v>
-      </c>
-      <c r="D43">
-        <v>0</v>
-      </c>
-      <c r="E43" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>4042</v>
-      </c>
-      <c r="B44">
-        <v>61</v>
-      </c>
-      <c r="C44">
-        <v>3</v>
-      </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
-      <c r="E44" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>4042</v>
-      </c>
-      <c r="B45">
-        <v>2</v>
-      </c>
-      <c r="C45">
-        <v>60</v>
-      </c>
-      <c r="D45">
-        <v>0</v>
-      </c>
-      <c r="E45" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <v>4042</v>
-      </c>
-      <c r="B46">
-        <v>71</v>
-      </c>
-      <c r="C46">
-        <v>0</v>
-      </c>
-      <c r="D46">
-        <v>210</v>
-      </c>
-      <c r="E46" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47">
-        <v>4101</v>
-      </c>
-      <c r="B47">
-        <v>61</v>
-      </c>
-      <c r="C47">
-        <v>4</v>
-      </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
-      <c r="E47" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48">
-        <v>4101</v>
-      </c>
-      <c r="B48">
-        <v>2</v>
-      </c>
-      <c r="C48">
-        <v>50</v>
-      </c>
-      <c r="D48">
-        <v>0</v>
-      </c>
-      <c r="E48" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49">
-        <v>4102</v>
-      </c>
-      <c r="B49">
-        <v>61</v>
-      </c>
-      <c r="C49">
-        <v>4</v>
-      </c>
-      <c r="D49">
-        <v>0</v>
-      </c>
-      <c r="E49" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50">
-        <v>4102</v>
-      </c>
-      <c r="B50">
-        <v>2</v>
-      </c>
-      <c r="C50">
-        <v>60</v>
-      </c>
-      <c r="D50">
-        <v>0</v>
-      </c>
-      <c r="E50" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51">
-        <v>4102</v>
-      </c>
-      <c r="B51">
-        <v>62</v>
-      </c>
-      <c r="C51">
-        <v>5</v>
-      </c>
-      <c r="D51">
-        <v>0</v>
-      </c>
-      <c r="E51" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52">
-        <v>4102</v>
-      </c>
-      <c r="B52">
-        <v>63</v>
-      </c>
-      <c r="C52">
-        <v>5</v>
-      </c>
-      <c r="D52">
-        <v>0</v>
-      </c>
-      <c r="E52" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53">
-        <v>5041</v>
-      </c>
-      <c r="B53">
-        <v>61</v>
-      </c>
-      <c r="C53">
-        <v>2</v>
-      </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
-      <c r="E53" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54">
-        <v>5041</v>
-      </c>
-      <c r="B54">
-        <v>2</v>
-      </c>
-      <c r="C54">
-        <v>50</v>
-      </c>
-      <c r="D54">
-        <v>0</v>
-      </c>
-      <c r="E54" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55">
-        <v>5042</v>
-      </c>
-      <c r="B55">
-        <v>61</v>
-      </c>
-      <c r="C55">
-        <v>3</v>
-      </c>
-      <c r="D55">
-        <v>0</v>
-      </c>
-      <c r="E55" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56">
-        <v>5042</v>
-      </c>
-      <c r="B56">
-        <v>2</v>
-      </c>
-      <c r="C56">
-        <v>75</v>
-      </c>
-      <c r="D56">
-        <v>0</v>
-      </c>
-      <c r="E56" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57">
-        <v>5042</v>
-      </c>
-      <c r="B57">
-        <v>71</v>
-      </c>
-      <c r="C57">
-        <v>0</v>
-      </c>
-      <c r="D57">
-        <v>210</v>
-      </c>
-      <c r="E57" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58">
-        <v>5101</v>
-      </c>
-      <c r="B58">
-        <v>61</v>
-      </c>
-      <c r="C58">
-        <v>4</v>
-      </c>
-      <c r="D58">
-        <v>0</v>
-      </c>
-      <c r="E58" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59">
-        <v>5101</v>
-      </c>
-      <c r="B59">
-        <v>2</v>
-      </c>
-      <c r="C59">
-        <v>60</v>
-      </c>
-      <c r="D59">
-        <v>0</v>
-      </c>
-      <c r="E59" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60">
-        <v>5102</v>
-      </c>
-      <c r="B60">
-        <v>61</v>
-      </c>
-      <c r="C60">
-        <v>4</v>
-      </c>
-      <c r="D60">
-        <v>0</v>
-      </c>
-      <c r="E60" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61">
-        <v>5102</v>
-      </c>
-      <c r="B61">
-        <v>2</v>
-      </c>
-      <c r="C61">
-        <v>70</v>
-      </c>
-      <c r="D61">
-        <v>0</v>
-      </c>
-      <c r="E61" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62">
-        <v>5102</v>
-      </c>
-      <c r="B62">
-        <v>62</v>
-      </c>
-      <c r="C62">
-        <v>5</v>
-      </c>
-      <c r="D62">
-        <v>0</v>
-      </c>
-      <c r="E62" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63">
-        <v>5102</v>
-      </c>
-      <c r="B63">
-        <v>63</v>
-      </c>
-      <c r="C63">
-        <v>5</v>
-      </c>
-      <c r="D63">
-        <v>0</v>
-      </c>
-      <c r="E63" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A64">
-        <v>6021</v>
-      </c>
-      <c r="B64">
-        <v>61</v>
-      </c>
-      <c r="C64">
-        <v>2</v>
-      </c>
-      <c r="D64">
-        <v>0</v>
-      </c>
-      <c r="E64" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65">
-        <v>6021</v>
-      </c>
-      <c r="B65">
-        <v>2</v>
-      </c>
-      <c r="C65">
-        <v>50</v>
-      </c>
-      <c r="D65">
-        <v>0</v>
-      </c>
-      <c r="E65" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A66">
-        <v>6022</v>
-      </c>
-      <c r="B66">
-        <v>61</v>
-      </c>
-      <c r="C66">
-        <v>2</v>
-      </c>
-      <c r="D66">
-        <v>0</v>
-      </c>
-      <c r="E66" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67">
-        <v>6022</v>
-      </c>
-      <c r="B67">
-        <v>2</v>
-      </c>
-      <c r="C67">
-        <v>50</v>
-      </c>
-      <c r="D67">
-        <v>0</v>
-      </c>
-      <c r="E67" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68">
-        <v>6031</v>
-      </c>
-      <c r="B68">
-        <v>61</v>
-      </c>
-      <c r="C68">
-        <v>4</v>
-      </c>
-      <c r="D68">
-        <v>0</v>
-      </c>
-      <c r="E68" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69">
-        <v>6031</v>
-      </c>
-      <c r="B69">
-        <v>2</v>
-      </c>
-      <c r="C69">
-        <v>100</v>
-      </c>
-      <c r="D69">
-        <v>0</v>
-      </c>
-      <c r="E69" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A70">
-        <v>6031</v>
-      </c>
-      <c r="B70">
-        <v>71</v>
-      </c>
-      <c r="C70">
-        <v>0</v>
-      </c>
-      <c r="D70">
-        <v>210</v>
-      </c>
-      <c r="E70" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A71">
-        <v>6101</v>
-      </c>
-      <c r="B71">
-        <v>61</v>
-      </c>
-      <c r="C71">
-        <v>5</v>
-      </c>
-      <c r="D71">
-        <v>0</v>
-      </c>
-      <c r="E71" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72">
-        <v>6101</v>
-      </c>
-      <c r="B72">
-        <v>21</v>
-      </c>
-      <c r="C72">
-        <v>0</v>
-      </c>
-      <c r="D72">
-        <v>0</v>
-      </c>
-      <c r="E72" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A73">
-        <v>11020</v>
-      </c>
-      <c r="B73">
-        <v>1</v>
-      </c>
-      <c r="C73">
-        <v>11020</v>
-      </c>
-      <c r="D73">
-        <v>0</v>
-      </c>
-      <c r="E73" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74">
-        <v>11030</v>
-      </c>
-      <c r="B74">
-        <v>1</v>
-      </c>
-      <c r="C74">
-        <v>11030</v>
-      </c>
-      <c r="D74">
-        <v>0</v>
-      </c>
-      <c r="E74" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75">
-        <v>11040</v>
-      </c>
-      <c r="B75">
-        <v>1</v>
-      </c>
-      <c r="C75">
-        <v>11040</v>
-      </c>
-      <c r="D75">
-        <v>0</v>
-      </c>
-      <c r="E75" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A76">
-        <v>12020</v>
-      </c>
-      <c r="B76">
-        <v>1</v>
-      </c>
-      <c r="C76">
-        <v>12020</v>
-      </c>
-      <c r="D76">
-        <v>0</v>
-      </c>
-      <c r="E76" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A77">
-        <v>12030</v>
-      </c>
-      <c r="B77">
-        <v>1</v>
-      </c>
-      <c r="C77">
-        <v>12030</v>
-      </c>
-      <c r="D77">
-        <v>0</v>
-      </c>
-      <c r="E77" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A78">
-        <v>12040</v>
-      </c>
-      <c r="B78">
-        <v>1</v>
-      </c>
-      <c r="C78">
-        <v>12040</v>
-      </c>
-      <c r="D78">
-        <v>0</v>
-      </c>
-      <c r="E78" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A79">
-        <v>13020</v>
-      </c>
-      <c r="B79">
-        <v>1</v>
-      </c>
-      <c r="C79">
-        <v>13020</v>
-      </c>
-      <c r="D79">
-        <v>0</v>
-      </c>
-      <c r="E79" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A80">
-        <v>13030</v>
-      </c>
-      <c r="B80">
-        <v>1</v>
-      </c>
-      <c r="C80">
-        <v>13030</v>
-      </c>
-      <c r="D80">
-        <v>0</v>
-      </c>
-      <c r="E80" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A81">
-        <v>13040</v>
-      </c>
-      <c r="B81">
-        <v>1</v>
-      </c>
-      <c r="C81">
-        <v>13040</v>
-      </c>
-      <c r="D81">
-        <v>0</v>
-      </c>
-      <c r="E81" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82">
-        <v>14010</v>
-      </c>
-      <c r="B82">
-        <v>1</v>
-      </c>
-      <c r="C82">
-        <v>14010</v>
-      </c>
-      <c r="D82">
-        <v>0</v>
-      </c>
-      <c r="E82" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A83">
-        <v>14020</v>
-      </c>
-      <c r="B83">
-        <v>1</v>
-      </c>
-      <c r="C83">
-        <v>14020</v>
-      </c>
-      <c r="D83">
-        <v>0</v>
-      </c>
-      <c r="E83" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84">
-        <v>14030</v>
-      </c>
-      <c r="B84">
-        <v>1</v>
-      </c>
-      <c r="C84">
-        <v>14030</v>
-      </c>
-      <c r="D84">
-        <v>0</v>
-      </c>
-      <c r="E84" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A85">
-        <v>15020</v>
-      </c>
-      <c r="B85">
-        <v>1</v>
-      </c>
-      <c r="C85">
-        <v>15020</v>
-      </c>
-      <c r="D85">
-        <v>0</v>
-      </c>
-      <c r="E85" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A86">
-        <v>15030</v>
-      </c>
-      <c r="B86">
-        <v>1</v>
-      </c>
-      <c r="C86">
-        <v>15030</v>
-      </c>
-      <c r="D86">
-        <v>0</v>
-      </c>
-      <c r="E86" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A87">
-        <v>15050</v>
-      </c>
-      <c r="B87">
-        <v>1</v>
-      </c>
-      <c r="C87">
-        <v>15050</v>
-      </c>
-      <c r="D87">
-        <v>0</v>
-      </c>
-      <c r="E87" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A88">
-        <v>20010</v>
-      </c>
-      <c r="B88">
-        <v>101</v>
-      </c>
-      <c r="C88">
-        <v>0</v>
-      </c>
-      <c r="D88">
-        <v>0</v>
-      </c>
-      <c r="E88" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A89">
-        <v>20020</v>
-      </c>
-      <c r="B89">
-        <v>102</v>
-      </c>
-      <c r="C89">
-        <v>0</v>
-      </c>
-      <c r="D89">
-        <v>0</v>
-      </c>
-      <c r="E89" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A90">
-        <v>20030</v>
-      </c>
-      <c r="B90">
-        <v>103</v>
-      </c>
-      <c r="C90">
-        <v>0</v>
-      </c>
-      <c r="D90">
-        <v>0</v>
-      </c>
-      <c r="E90" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A91">
-        <v>20040</v>
-      </c>
-      <c r="B91">
-        <v>104</v>
-      </c>
-      <c r="C91">
-        <v>0</v>
-      </c>
-      <c r="D91">
-        <v>0</v>
-      </c>
-      <c r="E91" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -2069,7 +1178,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -2077,7 +1186,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -2085,7 +1194,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -2093,7 +1202,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -2101,7 +1210,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -2117,7 +1226,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -2125,7 +1234,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -2133,7 +1242,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -2141,7 +1250,7 @@
         <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -2149,7 +1258,7 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -2157,7 +1266,7 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -2165,7 +1274,7 @@
         <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -2173,7 +1282,7 @@
         <v>101</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -2181,7 +1290,7 @@
         <v>210</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4194CF3-88C2-4595-9C3B-67D13432D628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="PrizeSets" sheetId="1" r:id="rId1"/>
@@ -21,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
   <si>
     <t>Id</t>
   </si>
@@ -74,54 +68,60 @@
     <t>選択仲間加入</t>
   </si>
   <si>
+    <t>選択して加入</t>
+  </si>
+  <si>
+    <t>加入</t>
+  </si>
+  <si>
+    <t>魔法</t>
+  </si>
+  <si>
+    <t>過去改編</t>
+  </si>
+  <si>
+    <t>並行世界化</t>
+  </si>
+  <si>
+    <t>初期仲間変更</t>
+  </si>
+  <si>
+    <t>レベルリンク</t>
+  </si>
+  <si>
+    <t>GetItemType</t>
+  </si>
+  <si>
+    <t>LearnSkill</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>Demigod</t>
+  </si>
+  <si>
+    <t>Rebirth</t>
+  </si>
+  <si>
+    <t>LevelUp</t>
+  </si>
+  <si>
+    <t>StatusUp</t>
+  </si>
+  <si>
+    <t>Regene</t>
+  </si>
+  <si>
+    <t>バトルボーナス</t>
+  </si>
+  <si>
     <t>Nu獲得量アップ</t>
   </si>
   <si>
     <t>敵Lvアップ</t>
   </si>
   <si>
-    <t>魔法</t>
-  </si>
-  <si>
-    <t>過去改編</t>
-  </si>
-  <si>
-    <t>並行世界化</t>
-  </si>
-  <si>
-    <t>初期仲間変更</t>
-  </si>
-  <si>
-    <t>レベルリンク</t>
-  </si>
-  <si>
-    <t>GetItemType</t>
-  </si>
-  <si>
-    <t>LearnSkill</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>Demigod</t>
-  </si>
-  <si>
-    <t>Rebirth</t>
-  </si>
-  <si>
-    <t>LevelUp</t>
-  </si>
-  <si>
-    <t>StatusUp</t>
-  </si>
-  <si>
-    <t>Regene</t>
-  </si>
-  <si>
-    <t>バトルボーナス</t>
-  </si>
-  <si>
     <t>SelectRelic</t>
   </si>
   <si>
@@ -129,17 +129,19 @@
   </si>
   <si>
     <t>Ending</t>
-  </si>
-  <si>
-    <t>加入</t>
-    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,30 +150,352 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -179,9 +503,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -189,21 +755,65 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
+    <cellStyle name="入力" xfId="2" builtinId="20"/>
+    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
+    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
+    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
+    <cellStyle name="通貨" xfId="6" builtinId="4"/>
+    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
+    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
+    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="良い" xfId="13" builtinId="26"/>
+    <cellStyle name="警告文" xfId="14" builtinId="11"/>
+    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
+    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
+    <cellStyle name="説明文" xfId="17" builtinId="53"/>
+    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
+    <cellStyle name="出力" xfId="19" builtinId="21"/>
+    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
+    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
+    <cellStyle name="計算" xfId="22" builtinId="22"/>
+    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
+    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
+    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
+    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
+    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
+    <cellStyle name="集計" xfId="28" builtinId="25"/>
+    <cellStyle name="悪い" xfId="29" builtinId="27"/>
+    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
+    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
+    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
+    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
+    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
+    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
+    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
+    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
+    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
+    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
+    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
+    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
+    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
+    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
+    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
+    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
+    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -461,16 +1071,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F40"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F41"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -484,7 +1094,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>5</v>
       </c>
@@ -501,7 +1111,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>10</v>
       </c>
@@ -518,7 +1128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>15</v>
       </c>
@@ -535,7 +1145,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>20</v>
       </c>
@@ -552,7 +1162,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>25</v>
       </c>
@@ -569,7 +1179,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>30</v>
       </c>
@@ -586,7 +1196,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>40</v>
       </c>
@@ -603,7 +1213,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>50</v>
       </c>
@@ -620,7 +1230,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>60</v>
       </c>
@@ -637,7 +1247,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>75</v>
       </c>
@@ -654,7 +1264,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>100</v>
       </c>
@@ -671,7 +1281,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>111</v>
       </c>
@@ -688,7 +1298,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>252</v>
       </c>
@@ -705,15 +1315,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6">
       <c r="A15">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B15">
         <v>11</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -722,18 +1332,18 @@
         <v>15</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B16">
         <v>11</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -742,18 +1352,18 @@
         <v>15</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B17">
         <v>11</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -762,18 +1372,18 @@
         <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B18">
         <v>11</v>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -782,18 +1392,18 @@
         <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B19">
         <v>11</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -802,18 +1412,18 @@
         <v>15</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B20">
         <v>11</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -822,35 +1432,38 @@
         <v>15</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
+        <v>1006</v>
+      </c>
+      <c r="B21">
+        <v>11</v>
+      </c>
+      <c r="C21">
+        <v>6</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
         <v>11010</v>
       </c>
-      <c r="B21">
+      <c r="B22">
         <v>100</v>
       </c>
-      <c r="C21">
+      <c r="C22">
         <v>11010</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>11020</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22">
-        <v>11020</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -859,15 +1472,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5">
       <c r="A23">
-        <v>11030</v>
+        <v>11020</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23">
-        <v>11030</v>
+        <v>11020</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -876,15 +1489,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5">
       <c r="A24">
-        <v>11040</v>
+        <v>11030</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24">
-        <v>11040</v>
+        <v>11030</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -893,15 +1506,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5">
       <c r="A25">
-        <v>12020</v>
+        <v>11040</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25">
-        <v>12020</v>
+        <v>11040</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -910,15 +1523,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5">
       <c r="A26">
-        <v>12030</v>
+        <v>12020</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26">
-        <v>12030</v>
+        <v>12020</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -927,15 +1540,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5">
       <c r="A27">
-        <v>12040</v>
+        <v>12030</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27">
-        <v>12040</v>
+        <v>12030</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -944,15 +1557,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5">
       <c r="A28">
-        <v>13020</v>
+        <v>12040</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28">
-        <v>13020</v>
+        <v>12040</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -961,15 +1574,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5">
       <c r="A29">
-        <v>13030</v>
+        <v>13020</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29">
-        <v>13030</v>
+        <v>13020</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -978,15 +1591,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5">
       <c r="A30">
-        <v>13040</v>
+        <v>13030</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30">
-        <v>13040</v>
+        <v>13030</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -995,15 +1608,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5">
       <c r="A31">
-        <v>14010</v>
+        <v>13040</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31">
-        <v>14010</v>
+        <v>13040</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1012,15 +1625,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5">
       <c r="A32">
-        <v>14020</v>
+        <v>14010</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32">
-        <v>14020</v>
+        <v>14010</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1029,15 +1642,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5">
       <c r="A33">
-        <v>14030</v>
+        <v>14020</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33">
-        <v>14030</v>
+        <v>14020</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1046,15 +1659,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5">
       <c r="A34">
-        <v>15020</v>
+        <v>14030</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34">
-        <v>15020</v>
+        <v>14030</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1063,15 +1676,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5">
       <c r="A35">
-        <v>15030</v>
+        <v>15020</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35">
-        <v>15030</v>
+        <v>15020</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -1080,15 +1693,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5">
       <c r="A36">
-        <v>15050</v>
+        <v>15030</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36">
-        <v>15050</v>
+        <v>15030</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -1097,91 +1710,109 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5">
       <c r="A37">
+        <v>15050</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37">
+        <v>15050</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38">
         <v>20010</v>
       </c>
-      <c r="B37">
+      <c r="B38">
         <v>101</v>
       </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38">
+    <row r="39" spans="1:5">
+      <c r="A39">
         <v>20020</v>
       </c>
-      <c r="B38">
+      <c r="B39">
         <v>102</v>
       </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-      <c r="E38" t="s">
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39">
+    <row r="40" spans="1:5">
+      <c r="A40">
         <v>20030</v>
       </c>
-      <c r="B39">
+      <c r="B40">
         <v>103</v>
       </c>
-      <c r="C39">
-        <v>0</v>
-      </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40">
+    <row r="41" spans="1:5">
+      <c r="A41">
         <v>20040</v>
       </c>
-      <c r="B40">
+      <c r="B41">
         <v>104</v>
       </c>
-      <c r="C40">
-        <v>0</v>
-      </c>
-      <c r="D40">
-        <v>0</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="1"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1189,7 +1820,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1197,7 +1828,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1205,7 +1836,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1213,7 +1844,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>11</v>
       </c>
@@ -1221,7 +1852,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>21</v>
       </c>
@@ -1229,7 +1860,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>22</v>
       </c>
@@ -1237,7 +1868,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>31</v>
       </c>
@@ -1245,7 +1876,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>61</v>
       </c>
@@ -1253,48 +1884,48 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14">
         <v>101</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15">
         <v>210</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="PrizeSets" sheetId="1" r:id="rId1"/>
@@ -136,10 +136,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -158,16 +158,62 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -179,17 +225,69 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -202,104 +300,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -310,6 +310,132 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -322,13 +448,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -340,157 +472,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -521,9 +521,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -533,6 +535,15 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -552,17 +563,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -582,22 +587,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -609,145 +609,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="PrizeSets" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="40">
   <si>
     <t>Id</t>
   </si>
@@ -74,6 +74,9 @@
     <t>加入</t>
   </si>
   <si>
+    <t>炎の精霊石x1</t>
+  </si>
+  <si>
     <t>魔法</t>
   </si>
   <si>
@@ -129,6 +132,9 @@
   </si>
   <si>
     <t>Ending</t>
+  </si>
+  <si>
+    <t>Item</t>
   </si>
 </sst>
 </file>
@@ -136,10 +142,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -158,7 +164,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -172,6 +185,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -179,8 +207,41 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -194,16 +255,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -217,38 +271,20 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -265,37 +301,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,13 +316,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -328,169 +496,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -501,6 +507,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -521,6 +536,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -530,20 +554,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -566,8 +587,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -586,21 +607,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -609,145 +615,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1079,6 +1085,9 @@
   <sheetPr/>
   <dimension ref="A1:F41"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
+  <cols>
+    <col min="5" max="5" width="14" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
@@ -1457,16 +1466,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>11010</v>
+        <v>10010</v>
       </c>
       <c r="B22">
-        <v>100</v>
+        <v>1010</v>
       </c>
       <c r="C22">
-        <v>11010</v>
+        <v>1010</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
@@ -1486,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1503,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1520,7 +1529,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1537,7 +1546,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1554,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1571,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1588,7 +1597,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1605,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1622,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1639,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1656,7 +1665,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1673,7 +1682,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1690,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1707,7 +1716,7 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1724,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1741,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1758,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1775,7 +1784,7 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1792,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1804,12 +1813,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1817,7 +1826,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1825,7 +1834,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1833,7 +1842,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1841,7 +1850,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1857,7 +1866,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1865,7 +1874,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1873,7 +1882,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1881,7 +1890,7 @@
         <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1889,7 +1898,7 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1897,7 +1906,7 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1905,7 +1914,7 @@
         <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1913,7 +1922,7 @@
         <v>101</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1921,7 +1930,15 @@
         <v>210</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>1010</v>
+      </c>
+      <c r="B16" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="38">
   <si>
     <t>Id</t>
   </si>
@@ -80,16 +80,7 @@
     <t>魔法</t>
   </si>
   <si>
-    <t>過去改編</t>
-  </si>
-  <si>
-    <t>並行世界化</t>
-  </si>
-  <si>
-    <t>初期仲間変更</t>
-  </si>
-  <si>
-    <t>レベルリンク</t>
+    <t>Rankアップ</t>
   </si>
   <si>
     <t>GetItemType</t>
@@ -135,6 +126,9 @@
   </si>
   <si>
     <t>Item</t>
+  </si>
+  <si>
+    <t>RankUp</t>
   </si>
 </sst>
 </file>
@@ -142,10 +136,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -163,15 +157,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -185,6 +187,104 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -193,20 +293,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -214,98 +300,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -316,187 +310,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -510,11 +504,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -536,15 +536,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -554,17 +545,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -587,23 +596,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -615,145 +609,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1083,7 +1077,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -1741,7 +1735,7 @@
         <v>20010</v>
       </c>
       <c r="B38">
-        <v>101</v>
+        <v>2010</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -1751,57 +1745,6 @@
       </c>
       <c r="E38" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39">
-        <v>20020</v>
-      </c>
-      <c r="B39">
-        <v>102</v>
-      </c>
-      <c r="C39">
-        <v>0</v>
-      </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
-      <c r="E39" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40">
-        <v>20030</v>
-      </c>
-      <c r="B40">
-        <v>103</v>
-      </c>
-      <c r="C40">
-        <v>0</v>
-      </c>
-      <c r="D40">
-        <v>0</v>
-      </c>
-      <c r="E40" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41">
-        <v>20040</v>
-      </c>
-      <c r="B41">
-        <v>104</v>
-      </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-      <c r="E41" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1813,12 +1756,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1826,7 +1769,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1834,7 +1777,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1842,7 +1785,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1850,7 +1793,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1866,7 +1809,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1874,7 +1817,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1882,7 +1825,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1890,7 +1833,7 @@
         <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1898,7 +1841,7 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1906,7 +1849,7 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1914,7 +1857,7 @@
         <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1922,7 +1865,7 @@
         <v>101</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1930,7 +1873,7 @@
         <v>210</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1938,7 +1881,15 @@
         <v>1010</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>2010</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="42">
   <si>
     <t>Id</t>
   </si>
@@ -75,6 +75,18 @@
   </si>
   <si>
     <t>炎の精霊石x1</t>
+  </si>
+  <si>
+    <t>雷の精霊石</t>
+  </si>
+  <si>
+    <t>氷の精霊石</t>
+  </si>
+  <si>
+    <t>光の精霊石</t>
+  </si>
+  <si>
+    <t>闇の精霊石</t>
   </si>
   <si>
     <t>魔法</t>
@@ -136,10 +148,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -154,6 +166,80 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -165,15 +251,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -187,15 +282,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -208,98 +312,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -310,19 +322,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -334,13 +466,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -352,31 +478,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -388,109 +490,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -501,47 +513,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -560,11 +531,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -593,6 +570,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -601,6 +602,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -609,145 +621,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1077,7 +1089,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -1477,16 +1489,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>11020</v>
+        <v>10020</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>1020</v>
       </c>
       <c r="C23">
-        <v>11020</v>
+        <v>1020</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="s">
         <v>20</v>
@@ -1494,257 +1506,325 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>11030</v>
+        <v>10030</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>1030</v>
       </c>
       <c r="C24">
-        <v>11030</v>
+        <v>1030</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>11040</v>
+        <v>10040</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>1040</v>
       </c>
       <c r="C25">
-        <v>11040</v>
+        <v>1040</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>12020</v>
+        <v>10050</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>1050</v>
       </c>
       <c r="C26">
-        <v>12020</v>
+        <v>1050</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>12030</v>
+        <v>11020</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27">
-        <v>12030</v>
+        <v>11020</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>12040</v>
+        <v>11030</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28">
-        <v>12040</v>
+        <v>11030</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>13020</v>
+        <v>11040</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29">
-        <v>13020</v>
+        <v>11040</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>13030</v>
+        <v>12020</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30">
-        <v>13030</v>
+        <v>12020</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>13040</v>
+        <v>12030</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31">
-        <v>13040</v>
+        <v>12030</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>14010</v>
+        <v>12040</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32">
-        <v>14010</v>
+        <v>12040</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>14020</v>
+        <v>13020</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33">
-        <v>14020</v>
+        <v>13020</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>14030</v>
+        <v>13030</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34">
-        <v>14030</v>
+        <v>13030</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>15020</v>
+        <v>13040</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35">
-        <v>15020</v>
+        <v>13040</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>15030</v>
+        <v>14010</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36">
-        <v>15030</v>
+        <v>14010</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>15050</v>
+        <v>14020</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37">
-        <v>15050</v>
+        <v>14020</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
+        <v>14030</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38">
+        <v>14030</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39">
+        <v>15020</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39">
+        <v>15020</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40">
+        <v>15030</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40">
+        <v>15030</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41">
+        <v>15050</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41">
+        <v>15050</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42">
         <v>20010</v>
       </c>
-      <c r="B38">
+      <c r="B42">
         <v>2010</v>
       </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-      <c r="E38" t="s">
-        <v>21</v>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1761,7 +1841,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1769,7 +1849,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1777,7 +1857,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1785,7 +1865,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1793,7 +1873,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1809,7 +1889,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1817,7 +1897,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1825,7 +1905,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1833,7 +1913,7 @@
         <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1841,7 +1921,7 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1849,7 +1929,7 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1857,7 +1937,7 @@
         <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1865,7 +1945,7 @@
         <v>101</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1873,7 +1953,7 @@
         <v>210</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1881,7 +1961,7 @@
         <v>1010</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1889,7 +1969,7 @@
         <v>2010</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -148,9 +148,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -170,7 +170,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -184,7 +184,46 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -200,7 +239,37 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -213,8 +282,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -228,90 +306,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -322,31 +322,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -364,6 +424,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -376,25 +442,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,103 +466,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -516,17 +516,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -585,20 +588,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,145 +621,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1492,7 +1492,7 @@
         <v>10020</v>
       </c>
       <c r="B23">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="C23">
         <v>1020</v>
@@ -1509,7 +1509,7 @@
         <v>10030</v>
       </c>
       <c r="B24">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="C24">
         <v>1030</v>
@@ -1526,7 +1526,7 @@
         <v>10040</v>
       </c>
       <c r="B25">
-        <v>1040</v>
+        <v>1010</v>
       </c>
       <c r="C25">
         <v>1040</v>
@@ -1543,7 +1543,7 @@
         <v>10050</v>
       </c>
       <c r="B26">
-        <v>1050</v>
+        <v>1010</v>
       </c>
       <c r="C26">
         <v>1050</v>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="44">
   <si>
     <t>Id</t>
   </si>
@@ -89,12 +89,15 @@
     <t>闇の精霊石</t>
   </si>
   <si>
-    <t>魔法</t>
-  </si>
-  <si>
     <t>Rankアップ</t>
   </si>
   <si>
+    <t>魔晶石セット</t>
+  </si>
+  <si>
+    <t>評価値</t>
+  </si>
+  <si>
     <t>GetItemType</t>
   </si>
   <si>
@@ -141,6 +144,9 @@
   </si>
   <si>
     <t>RankUp</t>
+  </si>
+  <si>
+    <t>評価値加算</t>
   </si>
 </sst>
 </file>
@@ -148,10 +154,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -176,33 +182,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -214,9 +205,47 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -237,23 +266,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -261,30 +290,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -299,15 +312,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -322,43 +328,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -370,139 +502,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -520,7 +526,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -528,8 +534,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -552,8 +573,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -573,6 +594,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -587,32 +619,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -621,145 +627,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1089,7 +1095,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -1557,13 +1563,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>11020</v>
+        <v>20010</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>2010</v>
       </c>
       <c r="C27">
-        <v>11020</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1574,257 +1580,393 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>11030</v>
+        <v>30010</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>1010</v>
       </c>
       <c r="C28">
-        <v>11030</v>
+        <v>1110</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>11040</v>
+        <v>30010</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>1010</v>
       </c>
       <c r="C29">
-        <v>11040</v>
+        <v>1120</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>12020</v>
+        <v>30010</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>1010</v>
       </c>
       <c r="C30">
-        <v>12020</v>
+        <v>1130</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>12030</v>
+        <v>30010</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>1010</v>
       </c>
       <c r="C31">
-        <v>12030</v>
+        <v>1140</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>12040</v>
+        <v>30010</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>1010</v>
       </c>
       <c r="C32">
-        <v>12040</v>
+        <v>1150</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>13020</v>
+        <v>30010</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>1010</v>
       </c>
       <c r="C33">
-        <v>13020</v>
+        <v>1010</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>13030</v>
+        <v>30010</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>1010</v>
       </c>
       <c r="C34">
-        <v>13030</v>
+        <v>1020</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>13040</v>
+        <v>30010</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>1010</v>
       </c>
       <c r="C35">
-        <v>13040</v>
+        <v>1030</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>14010</v>
+        <v>30010</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>1010</v>
       </c>
       <c r="C36">
-        <v>14010</v>
+        <v>1040</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>14020</v>
+        <v>30010</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>1010</v>
       </c>
       <c r="C37">
-        <v>14020</v>
+        <v>1050</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>14030</v>
+        <v>30020</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>1010</v>
       </c>
       <c r="C38">
-        <v>14030</v>
+        <v>1110</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>15020</v>
+        <v>30020</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>1010</v>
       </c>
       <c r="C39">
-        <v>15020</v>
+        <v>1120</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>15030</v>
+        <v>30020</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>1010</v>
       </c>
       <c r="C40">
-        <v>15030</v>
+        <v>1130</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>15050</v>
+        <v>30020</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>1010</v>
       </c>
       <c r="C41">
-        <v>15050</v>
+        <v>1140</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>20010</v>
+        <v>30020</v>
       </c>
       <c r="B42">
-        <v>2010</v>
+        <v>1010</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>1150</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43">
+        <v>30030</v>
+      </c>
+      <c r="B43">
+        <v>1010</v>
+      </c>
+      <c r="C43">
+        <v>1010</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44">
+        <v>30030</v>
+      </c>
+      <c r="B44">
+        <v>1010</v>
+      </c>
+      <c r="C44">
+        <v>1020</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45">
+        <v>30030</v>
+      </c>
+      <c r="B45">
+        <v>1010</v>
+      </c>
+      <c r="C45">
+        <v>1030</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46">
+        <v>30030</v>
+      </c>
+      <c r="B46">
+        <v>1010</v>
+      </c>
+      <c r="C46">
+        <v>1040</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47">
+        <v>30030</v>
+      </c>
+      <c r="B47">
+        <v>1010</v>
+      </c>
+      <c r="C47">
+        <v>1050</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
+        <v>40010</v>
+      </c>
+      <c r="B48">
+        <v>3010</v>
+      </c>
+      <c r="C48">
+        <v>15</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49">
+        <v>40020</v>
+      </c>
+      <c r="B49">
+        <v>3010</v>
+      </c>
+      <c r="C49">
+        <v>10</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50">
+        <v>40030</v>
+      </c>
+      <c r="B50">
+        <v>3010</v>
+      </c>
+      <c r="C50">
+        <v>5</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1836,12 +1978,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1849,7 +1991,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1857,7 +1999,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1865,7 +2007,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1873,7 +2015,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1889,7 +2031,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1897,7 +2039,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1905,7 +2047,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1913,7 +2055,7 @@
         <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1921,7 +2063,7 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1929,7 +2071,7 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1937,7 +2079,7 @@
         <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1945,7 +2087,7 @@
         <v>101</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1953,7 +2095,7 @@
         <v>210</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1961,7 +2103,7 @@
         <v>1010</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1969,7 +2111,15 @@
         <v>2010</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>3010</v>
+      </c>
+      <c r="B18" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -154,10 +154,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -175,8 +175,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -191,22 +208,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -221,7 +237,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -251,31 +289,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -290,30 +306,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -328,31 +328,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -364,31 +490,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -400,115 +508,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,8 +524,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -536,6 +538,30 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -551,21 +577,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -594,17 +605,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -627,145 +627,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1923,7 +1923,7 @@
         <v>40010</v>
       </c>
       <c r="B48">
-        <v>3010</v>
+        <v>2020</v>
       </c>
       <c r="C48">
         <v>15</v>
@@ -1940,7 +1940,7 @@
         <v>40020</v>
       </c>
       <c r="B49">
-        <v>3010</v>
+        <v>2020</v>
       </c>
       <c r="C49">
         <v>10</v>
@@ -1957,7 +1957,7 @@
         <v>40030</v>
       </c>
       <c r="B50">
-        <v>3010</v>
+        <v>2020</v>
       </c>
       <c r="C50">
         <v>5</v>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>3010</v>
+        <v>2020</v>
       </c>
       <c r="B18" t="s">
         <v>43</v>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="44">
   <si>
     <t>Id</t>
   </si>
@@ -155,9 +155,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -172,6 +172,29 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -184,6 +207,50 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -199,6 +266,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -207,88 +304,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -297,27 +312,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -334,55 +334,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -394,25 +472,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -424,36 +484,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -466,49 +496,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -519,6 +519,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -533,11 +557,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -545,23 +575,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -584,23 +599,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -627,16 +627,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -645,127 +645,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1095,7 +1095,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -1563,104 +1563,104 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20010</v>
+        <v>11010</v>
       </c>
       <c r="B27">
-        <v>2010</v>
+        <v>1010</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1110</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>30010</v>
+        <v>11020</v>
       </c>
       <c r="B28">
         <v>1010</v>
       </c>
       <c r="C28">
-        <v>1110</v>
+        <v>1120</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>30010</v>
+        <v>11030</v>
       </c>
       <c r="B29">
         <v>1010</v>
       </c>
       <c r="C29">
-        <v>1120</v>
+        <v>1130</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>30010</v>
+        <v>11040</v>
       </c>
       <c r="B30">
         <v>1010</v>
       </c>
       <c r="C30">
-        <v>1130</v>
+        <v>1140</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>30010</v>
+        <v>11050</v>
       </c>
       <c r="B31">
         <v>1010</v>
       </c>
       <c r="C31">
-        <v>1140</v>
+        <v>1150</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>30010</v>
+        <v>20010</v>
       </c>
       <c r="B32">
-        <v>1010</v>
+        <v>2010</v>
       </c>
       <c r="C32">
-        <v>1150</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1671,7 +1671,7 @@
         <v>1010</v>
       </c>
       <c r="C33">
-        <v>1010</v>
+        <v>1100</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1682,13 +1682,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>30010</v>
+        <v>30020</v>
       </c>
       <c r="B34">
         <v>1010</v>
       </c>
       <c r="C34">
-        <v>1020</v>
+        <v>1000</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1699,273 +1699,52 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>30010</v>
+        <v>40010</v>
       </c>
       <c r="B35">
-        <v>1010</v>
+        <v>2020</v>
       </c>
       <c r="C35">
-        <v>1030</v>
+        <v>15</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>30010</v>
+        <v>40020</v>
       </c>
       <c r="B36">
-        <v>1010</v>
+        <v>2020</v>
       </c>
       <c r="C36">
-        <v>1040</v>
+        <v>10</v>
       </c>
       <c r="D36">
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>30010</v>
+        <v>40030</v>
       </c>
       <c r="B37">
-        <v>1010</v>
+        <v>2020</v>
       </c>
       <c r="C37">
-        <v>1050</v>
+        <v>5</v>
       </c>
       <c r="D37">
         <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38">
-        <v>30020</v>
-      </c>
-      <c r="B38">
-        <v>1010</v>
-      </c>
-      <c r="C38">
-        <v>1110</v>
-      </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-      <c r="E38" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39">
-        <v>30020</v>
-      </c>
-      <c r="B39">
-        <v>1010</v>
-      </c>
-      <c r="C39">
-        <v>1120</v>
-      </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="E39" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40">
-        <v>30020</v>
-      </c>
-      <c r="B40">
-        <v>1010</v>
-      </c>
-      <c r="C40">
-        <v>1130</v>
-      </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-      <c r="E40" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41">
-        <v>30020</v>
-      </c>
-      <c r="B41">
-        <v>1010</v>
-      </c>
-      <c r="C41">
-        <v>1140</v>
-      </c>
-      <c r="D41">
-        <v>1</v>
-      </c>
-      <c r="E41" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42">
-        <v>30020</v>
-      </c>
-      <c r="B42">
-        <v>1010</v>
-      </c>
-      <c r="C42">
-        <v>1150</v>
-      </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
-      <c r="E42" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43">
-        <v>30030</v>
-      </c>
-      <c r="B43">
-        <v>1010</v>
-      </c>
-      <c r="C43">
-        <v>1010</v>
-      </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
-      <c r="E43" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44">
-        <v>30030</v>
-      </c>
-      <c r="B44">
-        <v>1010</v>
-      </c>
-      <c r="C44">
-        <v>1020</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="E44" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45">
-        <v>30030</v>
-      </c>
-      <c r="B45">
-        <v>1010</v>
-      </c>
-      <c r="C45">
-        <v>1030</v>
-      </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-      <c r="E45" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46">
-        <v>30030</v>
-      </c>
-      <c r="B46">
-        <v>1010</v>
-      </c>
-      <c r="C46">
-        <v>1040</v>
-      </c>
-      <c r="D46">
-        <v>1</v>
-      </c>
-      <c r="E46" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47">
-        <v>30030</v>
-      </c>
-      <c r="B47">
-        <v>1010</v>
-      </c>
-      <c r="C47">
-        <v>1050</v>
-      </c>
-      <c r="D47">
-        <v>1</v>
-      </c>
-      <c r="E47" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48">
-        <v>40010</v>
-      </c>
-      <c r="B48">
-        <v>2020</v>
-      </c>
-      <c r="C48">
-        <v>15</v>
-      </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
-      <c r="E48" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49">
-        <v>40020</v>
-      </c>
-      <c r="B49">
-        <v>2020</v>
-      </c>
-      <c r="C49">
-        <v>10</v>
-      </c>
-      <c r="D49">
-        <v>1</v>
-      </c>
-      <c r="E49" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50">
-        <v>40030</v>
-      </c>
-      <c r="B50">
-        <v>2020</v>
-      </c>
-      <c r="C50">
-        <v>5</v>
-      </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-      <c r="E50" t="s">
         <v>26</v>
       </c>
     </row>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -154,10 +154,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -176,7 +176,90 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -190,17 +273,39 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -213,111 +318,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -328,187 +328,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -522,17 +522,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -541,17 +535,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -572,11 +555,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -598,9 +587,20 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -627,145 +627,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E1284A-51D5-47D9-A05D-AF4BAC3AF6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PrizeSets" sheetId="1" r:id="rId1"/>
@@ -15,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="46">
   <si>
     <t>Id</t>
   </si>
@@ -147,19 +153,24 @@
   </si>
   <si>
     <t>評価値加算</t>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>魔法</t>
+    <rPh sb="0" eb="2">
+      <t>マホウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,344 +187,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="6"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -521,317 +217,34 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
-    <cellStyle name="入力" xfId="2" builtinId="20"/>
-    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
-    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
-    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
-    <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
-    <cellStyle name="良い" xfId="13" builtinId="26"/>
-    <cellStyle name="警告文" xfId="14" builtinId="11"/>
-    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
-    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
-    <cellStyle name="説明文" xfId="17" builtinId="53"/>
-    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
-    <cellStyle name="出力" xfId="19" builtinId="21"/>
-    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
-    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
-    <cellStyle name="計算" xfId="22" builtinId="22"/>
-    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
-    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
-    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
-    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
-    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
-    <cellStyle name="集計" xfId="28" builtinId="25"/>
-    <cellStyle name="悪い" xfId="29" builtinId="27"/>
-    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
-    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
-    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
-    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
-    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
-    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
-    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
-    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
-    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
-    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
-    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
-    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
-    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
-    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
-    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
-    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
-    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
-    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1089,19 +502,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F37"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1115,7 +528,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>5</v>
       </c>
@@ -1132,7 +545,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>10</v>
       </c>
@@ -1149,7 +562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>15</v>
       </c>
@@ -1166,7 +579,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>20</v>
       </c>
@@ -1183,7 +596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>25</v>
       </c>
@@ -1200,7 +613,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>30</v>
       </c>
@@ -1217,7 +630,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>40</v>
       </c>
@@ -1234,7 +647,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>50</v>
       </c>
@@ -1251,7 +664,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>60</v>
       </c>
@@ -1268,7 +681,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>75</v>
       </c>
@@ -1285,7 +698,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>100</v>
       </c>
@@ -1302,7 +715,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>111</v>
       </c>
@@ -1319,7 +732,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>252</v>
       </c>
@@ -1336,7 +749,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1000</v>
       </c>
@@ -1356,7 +769,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>1001</v>
       </c>
@@ -1376,7 +789,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1002</v>
       </c>
@@ -1396,7 +809,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>1003</v>
       </c>
@@ -1416,7 +829,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>1004</v>
       </c>
@@ -1436,7 +849,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1005</v>
       </c>
@@ -1456,7 +869,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>1006</v>
       </c>
@@ -1476,7 +889,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>10010</v>
       </c>
@@ -1493,7 +906,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>10020</v>
       </c>
@@ -1510,7 +923,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>10030</v>
       </c>
@@ -1527,7 +940,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>10040</v>
       </c>
@@ -1544,7 +957,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>10050</v>
       </c>
@@ -1561,7 +974,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>11010</v>
       </c>
@@ -1578,7 +991,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>11020</v>
       </c>
@@ -1595,7 +1008,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>11030</v>
       </c>
@@ -1612,7 +1025,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>11040</v>
       </c>
@@ -1629,7 +1042,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>11050</v>
       </c>
@@ -1646,7 +1059,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>20010</v>
       </c>
@@ -1663,7 +1076,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>30010</v>
       </c>
@@ -1680,7 +1093,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>30020</v>
       </c>
@@ -1697,7 +1110,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>40010</v>
       </c>
@@ -1714,7 +1127,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>40020</v>
       </c>
@@ -1731,7 +1144,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>40030</v>
       </c>
@@ -1748,24 +1161,41 @@
         <v>26</v>
       </c>
     </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>50010</v>
+      </c>
+      <c r="B38">
+        <v>100</v>
+      </c>
+      <c r="C38">
+        <v>1020</v>
+      </c>
+      <c r="D38">
+        <v>15</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1773,7 +1203,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1781,7 +1211,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1789,7 +1219,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1797,7 +1227,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>11</v>
       </c>
@@ -1805,7 +1235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>21</v>
       </c>
@@ -1813,7 +1243,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>22</v>
       </c>
@@ -1821,7 +1251,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>31</v>
       </c>
@@ -1829,7 +1259,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>61</v>
       </c>
@@ -1837,7 +1267,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>62</v>
       </c>
@@ -1845,7 +1275,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>63</v>
       </c>
@@ -1853,7 +1283,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>71</v>
       </c>
@@ -1861,48 +1291,56 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14">
+        <v>100</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15">
         <v>101</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16">
         <v>210</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17">
         <v>1010</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18">
         <v>2010</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
         <v>2020</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>43</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E1284A-51D5-47D9-A05D-AF4BAC3AF6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="PrizeSets" sheetId="1" r:id="rId1"/>
@@ -21,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="47">
   <si>
     <t>Id</t>
   </si>
@@ -95,6 +89,9 @@
     <t>闇の精霊石</t>
   </si>
   <si>
+    <t>初級指南書</t>
+  </si>
+  <si>
     <t>Rankアップ</t>
   </si>
   <si>
@@ -104,6 +101,9 @@
     <t>評価値</t>
   </si>
   <si>
+    <t>魔法</t>
+  </si>
+  <si>
     <t>GetItemType</t>
   </si>
   <si>
@@ -140,6 +140,9 @@
     <t>SelectRelic</t>
   </si>
   <si>
+    <t>Skill</t>
+  </si>
+  <si>
     <t>SelectSkill</t>
   </si>
   <si>
@@ -153,24 +156,19 @@
   </si>
   <si>
     <t>評価値加算</t>
-  </si>
-  <si>
-    <t>Skill</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>魔法</t>
-    <rPh sb="0" eb="2">
-      <t>マホウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -189,27 +187,349 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -217,9 +537,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -234,17 +796,61 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
+    <cellStyle name="入力" xfId="2" builtinId="20"/>
+    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
+    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
+    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
+    <cellStyle name="通貨" xfId="6" builtinId="4"/>
+    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
+    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
+    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="良い" xfId="13" builtinId="26"/>
+    <cellStyle name="警告文" xfId="14" builtinId="11"/>
+    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
+    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
+    <cellStyle name="説明文" xfId="17" builtinId="53"/>
+    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
+    <cellStyle name="出力" xfId="19" builtinId="21"/>
+    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
+    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
+    <cellStyle name="計算" xfId="22" builtinId="22"/>
+    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
+    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
+    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
+    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
+    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
+    <cellStyle name="集計" xfId="28" builtinId="25"/>
+    <cellStyle name="悪い" xfId="29" builtinId="27"/>
+    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
+    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
+    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
+    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
+    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
+    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
+    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
+    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
+    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
+    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
+    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
+    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
+    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
+    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
+    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
+    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
+    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -502,19 +1108,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F38"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F39"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -528,7 +1134,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>5</v>
       </c>
@@ -545,7 +1151,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>10</v>
       </c>
@@ -562,7 +1168,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>15</v>
       </c>
@@ -579,7 +1185,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>20</v>
       </c>
@@ -596,7 +1202,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>25</v>
       </c>
@@ -613,7 +1219,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>30</v>
       </c>
@@ -630,7 +1236,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>40</v>
       </c>
@@ -647,7 +1253,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>50</v>
       </c>
@@ -664,7 +1270,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>60</v>
       </c>
@@ -681,7 +1287,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>75</v>
       </c>
@@ -698,7 +1304,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>100</v>
       </c>
@@ -715,7 +1321,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>111</v>
       </c>
@@ -732,7 +1338,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>252</v>
       </c>
@@ -749,7 +1355,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>1000</v>
       </c>
@@ -765,11 +1371,11 @@
       <c r="E15" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>1001</v>
       </c>
@@ -785,11 +1391,11 @@
       <c r="E16" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>1002</v>
       </c>
@@ -805,11 +1411,11 @@
       <c r="E17" t="s">
         <v>15</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>1003</v>
       </c>
@@ -825,11 +1431,11 @@
       <c r="E18" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>1004</v>
       </c>
@@ -845,11 +1451,11 @@
       <c r="E19" t="s">
         <v>15</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>1005</v>
       </c>
@@ -865,11 +1471,11 @@
       <c r="E20" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>1006</v>
       </c>
@@ -885,11 +1491,11 @@
       <c r="E21" t="s">
         <v>15</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>10010</v>
       </c>
@@ -906,7 +1512,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>10020</v>
       </c>
@@ -923,7 +1529,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>10030</v>
       </c>
@@ -940,7 +1546,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>10040</v>
       </c>
@@ -957,7 +1563,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>10050</v>
       </c>
@@ -974,7 +1580,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>11010</v>
       </c>
@@ -991,7 +1597,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>11020</v>
       </c>
@@ -1008,7 +1614,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>11030</v>
       </c>
@@ -1025,7 +1631,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>11040</v>
       </c>
@@ -1042,7 +1648,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>11050</v>
       </c>
@@ -1059,66 +1665,66 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5">
       <c r="A32">
-        <v>20010</v>
+        <v>14010</v>
       </c>
       <c r="B32">
-        <v>2010</v>
+        <v>1010</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>4010</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5">
       <c r="A33">
-        <v>30010</v>
+        <v>20010</v>
       </c>
       <c r="B33">
-        <v>1010</v>
+        <v>2010</v>
       </c>
       <c r="C33">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5">
       <c r="A34">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B34">
         <v>1010</v>
       </c>
       <c r="C34">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35">
-        <v>40010</v>
+        <v>30020</v>
       </c>
       <c r="B35">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="C35">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1127,107 +1733,125 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5">
       <c r="A36">
-        <v>40020</v>
+        <v>40010</v>
       </c>
       <c r="B36">
         <v>2020</v>
       </c>
       <c r="C36">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D36">
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37">
-        <v>40030</v>
+        <v>40020</v>
       </c>
       <c r="B37">
         <v>2020</v>
       </c>
       <c r="C37">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D37">
         <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38">
+        <v>40030</v>
+      </c>
+      <c r="B38">
+        <v>2020</v>
+      </c>
+      <c r="C38">
+        <v>5</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39">
         <v>50010</v>
       </c>
-      <c r="B38">
+      <c r="B39">
         <v>100</v>
       </c>
-      <c r="C38">
+      <c r="C39">
         <v>1020</v>
       </c>
-      <c r="D38">
+      <c r="D39">
         <v>15</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>45</v>
+      <c r="E39" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="1"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>11</v>
       </c>
@@ -1235,112 +1859,112 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14">
         <v>100</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B14" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15">
         <v>101</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16">
         <v>210</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>1010</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>2010</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>2020</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="50">
   <si>
     <t>Id</t>
   </si>
@@ -90,6 +90,15 @@
   </si>
   <si>
     <t>初級指南書</t>
+  </si>
+  <si>
+    <t>中級指南書</t>
+  </si>
+  <si>
+    <t>上級指南書</t>
+  </si>
+  <si>
+    <t>特級指南書</t>
   </si>
   <si>
     <t>Rankアップ</t>
@@ -164,11 +173,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,37 +196,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -230,9 +208,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -253,22 +253,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -276,37 +262,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -321,19 +277,65 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -344,13 +346,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -362,49 +490,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,115 +520,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -535,21 +537,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -568,21 +555,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -590,6 +562,15 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -618,11 +599,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -643,7 +645,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -652,7 +654,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -661,138 +663,135 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1114,7 +1113,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -1371,7 +1370,7 @@
       <c r="E15" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="1" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1391,7 +1390,7 @@
       <c r="E16" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1411,7 +1410,7 @@
       <c r="E17" t="s">
         <v>15</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1431,7 +1430,7 @@
       <c r="E18" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1451,7 +1450,7 @@
       <c r="E19" t="s">
         <v>15</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1471,7 +1470,7 @@
       <c r="E20" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1491,7 +1490,7 @@
       <c r="E21" t="s">
         <v>15</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1684,16 +1683,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20010</v>
+        <v>14020</v>
       </c>
       <c r="B33">
-        <v>2010</v>
+        <v>1010</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>4020</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" t="s">
         <v>25</v>
@@ -1701,13 +1700,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>30010</v>
+        <v>14030</v>
       </c>
       <c r="B34">
         <v>1010</v>
       </c>
       <c r="C34">
-        <v>1100</v>
+        <v>4030</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1718,87 +1717,138 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>30020</v>
+        <v>14040</v>
       </c>
       <c r="B35">
         <v>1010</v>
       </c>
       <c r="C35">
-        <v>1000</v>
+        <v>4040</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>40010</v>
+        <v>20010</v>
       </c>
       <c r="B36">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="C36">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>40020</v>
+        <v>30010</v>
       </c>
       <c r="B37">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="C37">
-        <v>10</v>
+        <v>1100</v>
       </c>
       <c r="D37">
         <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>40030</v>
+        <v>30020</v>
       </c>
       <c r="B38">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
+        <v>40010</v>
+      </c>
+      <c r="B39">
+        <v>2020</v>
+      </c>
+      <c r="C39">
+        <v>15</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40">
+        <v>40020</v>
+      </c>
+      <c r="B40">
+        <v>2020</v>
+      </c>
+      <c r="C40">
+        <v>10</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41">
+        <v>40030</v>
+      </c>
+      <c r="B41">
+        <v>2020</v>
+      </c>
+      <c r="C41">
+        <v>5</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42">
         <v>50010</v>
       </c>
-      <c r="B39">
+      <c r="B42">
         <v>100</v>
       </c>
-      <c r="C39">
+      <c r="C42">
         <v>1020</v>
       </c>
-      <c r="D39">
+      <c r="D42">
         <v>15</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>28</v>
+      <c r="E42" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1816,7 +1866,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1824,7 +1874,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1832,7 +1882,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1840,7 +1890,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1848,7 +1898,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1864,7 +1914,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1872,7 +1922,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1880,7 +1930,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1888,7 +1938,7 @@
         <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1896,7 +1946,7 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1904,7 +1954,7 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1912,7 +1962,7 @@
         <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1920,7 +1970,7 @@
         <v>100</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1928,7 +1978,7 @@
         <v>101</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1936,7 +1986,7 @@
         <v>210</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1944,7 +1994,7 @@
         <v>1010</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1952,7 +2002,7 @@
         <v>2010</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1960,7 +2010,7 @@
         <v>2020</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="52">
   <si>
     <t>Id</t>
   </si>
@@ -110,7 +110,7 @@
     <t>評価値</t>
   </si>
   <si>
-    <t>魔法</t>
+    <t>取引用</t>
   </si>
   <si>
     <t>GetItemType</t>
@@ -165,6 +165,12 @@
   </si>
   <si>
     <t>評価値加算</t>
+  </si>
+  <si>
+    <t>取引用・ランダムアイテム</t>
+  </si>
+  <si>
+    <t>取引用・ランダム魔法</t>
   </si>
 </sst>
 </file>
@@ -172,10 +178,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -193,23 +199,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -217,91 +209,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,9 +223,100 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -330,8 +328,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -346,13 +352,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -364,13 +484,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -382,151 +526,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -540,37 +546,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -590,11 +576,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -614,17 +606,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -637,6 +632,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -645,145 +651,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1113,7 +1119,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -1839,15 +1845,576 @@
         <v>50010</v>
       </c>
       <c r="B42">
-        <v>100</v>
+        <v>4020</v>
       </c>
       <c r="C42">
-        <v>1020</v>
+        <v>10</v>
       </c>
       <c r="D42">
+        <v>10</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43">
+        <v>50010</v>
+      </c>
+      <c r="B43">
+        <v>4020</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43">
         <v>15</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E43" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44">
+        <v>50010</v>
+      </c>
+      <c r="B44">
+        <v>1010</v>
+      </c>
+      <c r="C44">
+        <v>4010</v>
+      </c>
+      <c r="D44">
+        <v>5</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45">
+        <v>50010</v>
+      </c>
+      <c r="B45">
+        <v>4010</v>
+      </c>
+      <c r="C45">
+        <v>30</v>
+      </c>
+      <c r="D45">
+        <v>5</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46">
+        <v>50010</v>
+      </c>
+      <c r="B46">
+        <v>4010</v>
+      </c>
+      <c r="C46">
+        <v>20</v>
+      </c>
+      <c r="D46">
+        <v>10</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47">
+        <v>50020</v>
+      </c>
+      <c r="B47">
+        <v>4020</v>
+      </c>
+      <c r="C47">
+        <v>10</v>
+      </c>
+      <c r="D47">
+        <v>10</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
+        <v>50020</v>
+      </c>
+      <c r="B48">
+        <v>4020</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48">
+        <v>15</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49">
+        <v>50020</v>
+      </c>
+      <c r="B49">
+        <v>1010</v>
+      </c>
+      <c r="C49">
+        <v>4010</v>
+      </c>
+      <c r="D49">
+        <v>5</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50">
+        <v>50020</v>
+      </c>
+      <c r="B50">
+        <v>4010</v>
+      </c>
+      <c r="C50">
+        <v>30</v>
+      </c>
+      <c r="D50">
+        <v>5</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51">
+        <v>50020</v>
+      </c>
+      <c r="B51">
+        <v>4010</v>
+      </c>
+      <c r="C51">
+        <v>20</v>
+      </c>
+      <c r="D51">
+        <v>10</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52">
+        <v>50030</v>
+      </c>
+      <c r="B52">
+        <v>4020</v>
+      </c>
+      <c r="C52">
+        <v>10</v>
+      </c>
+      <c r="D52">
+        <v>10</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53">
+        <v>50030</v>
+      </c>
+      <c r="B53">
+        <v>4020</v>
+      </c>
+      <c r="C53">
+        <v>20</v>
+      </c>
+      <c r="D53">
+        <v>20</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54">
+        <v>50030</v>
+      </c>
+      <c r="B54">
+        <v>4020</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="D54">
+        <v>15</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55">
+        <v>50030</v>
+      </c>
+      <c r="B55">
+        <v>1010</v>
+      </c>
+      <c r="C55">
+        <v>4020</v>
+      </c>
+      <c r="D55">
+        <v>5</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56">
+        <v>50030</v>
+      </c>
+      <c r="B56">
+        <v>4010</v>
+      </c>
+      <c r="C56">
+        <v>30</v>
+      </c>
+      <c r="D56">
+        <v>5</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57">
+        <v>50030</v>
+      </c>
+      <c r="B57">
+        <v>4010</v>
+      </c>
+      <c r="C57">
+        <v>20</v>
+      </c>
+      <c r="D57">
+        <v>10</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58">
+        <v>50040</v>
+      </c>
+      <c r="B58">
+        <v>4020</v>
+      </c>
+      <c r="C58">
+        <v>10</v>
+      </c>
+      <c r="D58">
+        <v>10</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59">
+        <v>50040</v>
+      </c>
+      <c r="B59">
+        <v>4020</v>
+      </c>
+      <c r="C59">
+        <v>20</v>
+      </c>
+      <c r="D59">
+        <v>20</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60">
+        <v>50040</v>
+      </c>
+      <c r="B60">
+        <v>4020</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+      <c r="D60">
+        <v>15</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61">
+        <v>50040</v>
+      </c>
+      <c r="B61">
+        <v>1010</v>
+      </c>
+      <c r="C61">
+        <v>4020</v>
+      </c>
+      <c r="D61">
+        <v>5</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62">
+        <v>50040</v>
+      </c>
+      <c r="B62">
+        <v>4010</v>
+      </c>
+      <c r="C62">
+        <v>30</v>
+      </c>
+      <c r="D62">
+        <v>5</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63">
+        <v>50040</v>
+      </c>
+      <c r="B63">
+        <v>4010</v>
+      </c>
+      <c r="C63">
+        <v>20</v>
+      </c>
+      <c r="D63">
+        <v>10</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64">
+        <v>50050</v>
+      </c>
+      <c r="B64">
+        <v>4020</v>
+      </c>
+      <c r="C64">
+        <v>10</v>
+      </c>
+      <c r="D64">
+        <v>10</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65">
+        <v>50050</v>
+      </c>
+      <c r="B65">
+        <v>4020</v>
+      </c>
+      <c r="C65">
+        <v>20</v>
+      </c>
+      <c r="D65">
+        <v>20</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66">
+        <v>50050</v>
+      </c>
+      <c r="B66">
+        <v>4020</v>
+      </c>
+      <c r="C66">
+        <v>2</v>
+      </c>
+      <c r="D66">
+        <v>15</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67">
+        <v>50050</v>
+      </c>
+      <c r="B67">
+        <v>1010</v>
+      </c>
+      <c r="C67">
+        <v>4030</v>
+      </c>
+      <c r="D67">
+        <v>5</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68">
+        <v>50050</v>
+      </c>
+      <c r="B68">
+        <v>4010</v>
+      </c>
+      <c r="C68">
+        <v>30</v>
+      </c>
+      <c r="D68">
+        <v>5</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69">
+        <v>50050</v>
+      </c>
+      <c r="B69">
+        <v>4010</v>
+      </c>
+      <c r="C69">
+        <v>20</v>
+      </c>
+      <c r="D69">
+        <v>10</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70">
+        <v>50060</v>
+      </c>
+      <c r="B70">
+        <v>4020</v>
+      </c>
+      <c r="C70">
+        <v>10</v>
+      </c>
+      <c r="D70">
+        <v>10</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71">
+        <v>50060</v>
+      </c>
+      <c r="B71">
+        <v>4020</v>
+      </c>
+      <c r="C71">
+        <v>20</v>
+      </c>
+      <c r="D71">
+        <v>20</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72">
+        <v>50060</v>
+      </c>
+      <c r="B72">
+        <v>4020</v>
+      </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
+      <c r="D72">
+        <v>15</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73">
+        <v>50060</v>
+      </c>
+      <c r="B73">
+        <v>1010</v>
+      </c>
+      <c r="C73">
+        <v>4030</v>
+      </c>
+      <c r="D73">
+        <v>5</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74">
+        <v>50060</v>
+      </c>
+      <c r="B74">
+        <v>4010</v>
+      </c>
+      <c r="C74">
+        <v>30</v>
+      </c>
+      <c r="D74">
+        <v>5</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75">
+        <v>50060</v>
+      </c>
+      <c r="B75">
+        <v>4010</v>
+      </c>
+      <c r="C75">
+        <v>20</v>
+      </c>
+      <c r="D75">
+        <v>10</v>
+      </c>
+      <c r="E75" s="1" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1861,7 +2428,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -2013,6 +2580,22 @@
         <v>49</v>
       </c>
     </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>4010</v>
+      </c>
+      <c r="B20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>4020</v>
+      </c>
+      <c r="B21" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -178,10 +178,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -199,31 +199,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -237,14 +214,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,9 +243,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -296,11 +273,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -313,10 +305,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -330,7 +322,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -342,6 +334,14 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -352,61 +352,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -418,115 +526,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -543,21 +543,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -591,6 +576,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -602,15 +596,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,6 +618,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -651,145 +651,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="53">
   <si>
     <t>Id</t>
   </si>
@@ -27,6 +27,9 @@
   </si>
   <si>
     <t>Param2</t>
+  </si>
+  <si>
+    <t>Nu+2</t>
   </si>
   <si>
     <t>Nu+5</t>
@@ -178,10 +181,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -200,99 +203,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -306,14 +219,35 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -329,7 +263,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -342,6 +284,67 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -352,187 +355,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -546,41 +549,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -603,17 +576,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -643,6 +622,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -651,145 +654,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1119,7 +1122,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -1141,13 +1144,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1158,13 +1161,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1175,13 +1178,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1192,13 +1195,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1209,13 +1212,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1226,13 +1229,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1243,13 +1246,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1260,13 +1263,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1277,13 +1280,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1294,13 +1297,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1311,13 +1314,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1328,13 +1331,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B13">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1345,13 +1348,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>252</v>
+        <v>111</v>
       </c>
       <c r="B14">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1360,41 +1363,38 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:5">
       <c r="A15">
-        <v>1000</v>
+        <v>252</v>
       </c>
       <c r="B15">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B16">
         <v>11</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>18</v>
@@ -1402,130 +1402,133 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B17">
         <v>11</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B18">
         <v>11</v>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B19">
         <v>11</v>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B20">
         <v>11</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B21">
         <v>11</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
-        <v>10010</v>
+        <v>1006</v>
       </c>
       <c r="B22">
-        <v>1010</v>
+        <v>11</v>
       </c>
       <c r="C22">
-        <v>1010</v>
+        <v>6</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>10020</v>
+        <v>10010</v>
       </c>
       <c r="B23">
         <v>1010</v>
       </c>
       <c r="C23">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1536,13 +1539,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>10030</v>
+        <v>10020</v>
       </c>
       <c r="B24">
         <v>1010</v>
       </c>
       <c r="C24">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1553,13 +1556,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>10040</v>
+        <v>10030</v>
       </c>
       <c r="B25">
         <v>1010</v>
       </c>
       <c r="C25">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1570,13 +1573,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>10050</v>
+        <v>10040</v>
       </c>
       <c r="B26">
         <v>1010</v>
       </c>
       <c r="C26">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1587,30 +1590,30 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>11010</v>
+        <v>10050</v>
       </c>
       <c r="B27">
         <v>1010</v>
       </c>
       <c r="C27">
-        <v>1110</v>
+        <v>1050</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>11020</v>
+        <v>11010</v>
       </c>
       <c r="B28">
         <v>1010</v>
       </c>
       <c r="C28">
-        <v>1120</v>
+        <v>1110</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -1621,13 +1624,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>11030</v>
+        <v>11020</v>
       </c>
       <c r="B29">
         <v>1010</v>
       </c>
       <c r="C29">
-        <v>1130</v>
+        <v>1120</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1638,13 +1641,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>11040</v>
+        <v>11030</v>
       </c>
       <c r="B30">
         <v>1010</v>
       </c>
       <c r="C30">
-        <v>1140</v>
+        <v>1130</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1655,13 +1658,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>11050</v>
+        <v>11040</v>
       </c>
       <c r="B31">
         <v>1010</v>
       </c>
       <c r="C31">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1672,13 +1675,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>14010</v>
+        <v>11050</v>
       </c>
       <c r="B32">
         <v>1010</v>
       </c>
       <c r="C32">
-        <v>4010</v>
+        <v>1150</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -1689,13 +1692,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>14020</v>
+        <v>14010</v>
       </c>
       <c r="B33">
         <v>1010</v>
       </c>
       <c r="C33">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1706,13 +1709,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>14030</v>
+        <v>14020</v>
       </c>
       <c r="B34">
         <v>1010</v>
       </c>
       <c r="C34">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1723,13 +1726,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>14040</v>
+        <v>14030</v>
       </c>
       <c r="B35">
         <v>1010</v>
       </c>
       <c r="C35">
-        <v>4040</v>
+        <v>4030</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1740,16 +1743,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>20010</v>
+        <v>14040</v>
       </c>
       <c r="B36">
-        <v>2010</v>
+        <v>1010</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>4040</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" t="s">
         <v>28</v>
@@ -1757,16 +1760,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>30010</v>
+        <v>20010</v>
       </c>
       <c r="B37">
-        <v>1010</v>
+        <v>2010</v>
       </c>
       <c r="C37">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" t="s">
         <v>29</v>
@@ -1774,30 +1777,30 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B38">
         <v>1010</v>
       </c>
       <c r="C38">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>40010</v>
+        <v>30020</v>
       </c>
       <c r="B39">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="C39">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1808,52 +1811,52 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>40020</v>
+        <v>40010</v>
       </c>
       <c r="B40">
         <v>2020</v>
       </c>
       <c r="C40">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D40">
         <v>1</v>
       </c>
       <c r="E40" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>40030</v>
+        <v>40020</v>
       </c>
       <c r="B41">
         <v>2020</v>
       </c>
       <c r="C41">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D41">
         <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>50010</v>
+        <v>40030</v>
       </c>
       <c r="B42">
-        <v>4020</v>
+        <v>2020</v>
       </c>
       <c r="C42">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D42">
-        <v>10</v>
-      </c>
-      <c r="E42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E42" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1865,13 +1868,13 @@
         <v>4020</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D43">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1879,16 +1882,16 @@
         <v>50010</v>
       </c>
       <c r="B44">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C44">
-        <v>4010</v>
+        <v>2</v>
       </c>
       <c r="D44">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1896,33 +1899,33 @@
         <v>50010</v>
       </c>
       <c r="B45">
+        <v>1010</v>
+      </c>
+      <c r="C45">
         <v>4010</v>
       </c>
-      <c r="C45">
-        <v>30</v>
-      </c>
       <c r="D45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46">
-        <v>50010</v>
+        <v>50020</v>
       </c>
       <c r="B46">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="C46">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D46">
         <v>10</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1933,13 +1936,13 @@
         <v>4020</v>
       </c>
       <c r="C47">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D47">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1947,67 +1950,67 @@
         <v>50020</v>
       </c>
       <c r="B48">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>4010</v>
       </c>
       <c r="D48">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49">
-        <v>50020</v>
+        <v>50030</v>
       </c>
       <c r="B49">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C49">
-        <v>4010</v>
+        <v>10</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50">
-        <v>50020</v>
+        <v>50030</v>
       </c>
       <c r="B50">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="C50">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D50">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51">
-        <v>50020</v>
+        <v>50030</v>
       </c>
       <c r="B51">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="C51">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D51">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2015,16 +2018,16 @@
         <v>50030</v>
       </c>
       <c r="B52">
+        <v>1010</v>
+      </c>
+      <c r="C52">
         <v>4020</v>
       </c>
-      <c r="C52">
-        <v>10</v>
-      </c>
       <c r="D52">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2032,84 +2035,84 @@
         <v>50030</v>
       </c>
       <c r="B53">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="C53">
         <v>20</v>
       </c>
       <c r="D53">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>50030</v>
+        <v>50040</v>
       </c>
       <c r="B54">
         <v>4020</v>
       </c>
       <c r="C54">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D54">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>50030</v>
+        <v>50040</v>
       </c>
       <c r="B55">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C55">
-        <v>4020</v>
+        <v>20</v>
       </c>
       <c r="D55">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56">
-        <v>50030</v>
+        <v>50040</v>
       </c>
       <c r="B56">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="C56">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D56">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57">
-        <v>50030</v>
+        <v>50040</v>
       </c>
       <c r="B57">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C57">
-        <v>20</v>
+        <v>4020</v>
       </c>
       <c r="D57">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2117,101 +2120,101 @@
         <v>50040</v>
       </c>
       <c r="B58">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="C58">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D58">
         <v>10</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>50040</v>
+        <v>50050</v>
       </c>
       <c r="B59">
         <v>4020</v>
       </c>
       <c r="C59">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D59">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60">
-        <v>50040</v>
+        <v>50050</v>
       </c>
       <c r="B60">
         <v>4020</v>
       </c>
       <c r="C60">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D60">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61">
-        <v>50040</v>
+        <v>50050</v>
       </c>
       <c r="B61">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C61">
-        <v>4020</v>
+        <v>2</v>
       </c>
       <c r="D61">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62">
-        <v>50040</v>
+        <v>50050</v>
       </c>
       <c r="B62">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C62">
-        <v>30</v>
+        <v>4030</v>
       </c>
       <c r="D62">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>50040</v>
+        <v>50050</v>
       </c>
       <c r="B63">
         <v>4010</v>
       </c>
       <c r="C63">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D63">
         <v>10</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2219,101 +2222,101 @@
         <v>50050</v>
       </c>
       <c r="B64">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="C64">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D64">
         <v>10</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>50050</v>
+        <v>50060</v>
       </c>
       <c r="B65">
         <v>4020</v>
       </c>
       <c r="C65">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D65">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>50050</v>
+        <v>50060</v>
       </c>
       <c r="B66">
         <v>4020</v>
       </c>
       <c r="C66">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D66">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>50050</v>
+        <v>50060</v>
       </c>
       <c r="B67">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C67">
-        <v>4030</v>
+        <v>2</v>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>50050</v>
+        <v>50060</v>
       </c>
       <c r="B68">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C68">
-        <v>30</v>
+        <v>4030</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>50050</v>
+        <v>50060</v>
       </c>
       <c r="B69">
         <v>4010</v>
       </c>
       <c r="C69">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D69">
         <v>10</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2321,101 +2324,16 @@
         <v>50060</v>
       </c>
       <c r="B70">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="C70">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D70">
         <v>10</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71">
-        <v>50060</v>
-      </c>
-      <c r="B71">
-        <v>4020</v>
-      </c>
-      <c r="C71">
-        <v>20</v>
-      </c>
-      <c r="D71">
-        <v>20</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72">
-        <v>50060</v>
-      </c>
-      <c r="B72">
-        <v>4020</v>
-      </c>
-      <c r="C72">
-        <v>2</v>
-      </c>
-      <c r="D72">
-        <v>15</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73">
-        <v>50060</v>
-      </c>
-      <c r="B73">
-        <v>1010</v>
-      </c>
-      <c r="C73">
-        <v>4030</v>
-      </c>
-      <c r="D73">
-        <v>5</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74">
-        <v>50060</v>
-      </c>
-      <c r="B74">
-        <v>4010</v>
-      </c>
-      <c r="C74">
-        <v>30</v>
-      </c>
-      <c r="D74">
-        <v>5</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75">
-        <v>50060</v>
-      </c>
-      <c r="B75">
-        <v>4010</v>
-      </c>
-      <c r="C75">
-        <v>20</v>
-      </c>
-      <c r="D75">
-        <v>10</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2433,7 +2351,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2441,7 +2359,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2449,7 +2367,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2457,7 +2375,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2465,7 +2383,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2473,7 +2391,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2481,7 +2399,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2489,7 +2407,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2497,7 +2415,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2505,7 +2423,7 @@
         <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2513,7 +2431,7 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2521,7 +2439,7 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2529,7 +2447,7 @@
         <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2537,7 +2455,7 @@
         <v>100</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2545,7 +2463,7 @@
         <v>101</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2553,7 +2471,7 @@
         <v>210</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2561,7 +2479,7 @@
         <v>1010</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2569,7 +2487,7 @@
         <v>2010</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2577,7 +2495,7 @@
         <v>2020</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2585,7 +2503,7 @@
         <v>4010</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2593,7 +2511,7 @@
         <v>4020</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="55">
   <si>
     <t>Id</t>
   </si>
@@ -77,6 +77,9 @@
     <t>加入</t>
   </si>
   <si>
+    <t>招聘コマンド回数+1</t>
+  </si>
+  <si>
     <t>炎の精霊石x1</t>
   </si>
   <si>
@@ -168,6 +171,9 @@
   </si>
   <si>
     <t>評価値加算</t>
+  </si>
+  <si>
+    <t>招聘コマンド回数</t>
   </si>
   <si>
     <t>取引用・ランダムアイテム</t>
@@ -181,10 +187,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -202,6 +208,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -210,23 +231,15 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -239,8 +252,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -254,70 +298,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,19 +321,36 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -355,43 +361,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -403,139 +541,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -549,35 +555,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -597,28 +585,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -640,6 +617,35 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
@@ -654,145 +660,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1122,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -1520,32 +1526,33 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:6">
       <c r="A23">
-        <v>10010</v>
+        <v>1100</v>
       </c>
       <c r="B23">
-        <v>1010</v>
+        <v>2030</v>
       </c>
       <c r="C23">
-        <v>1010</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="s">
         <v>20</v>
       </c>
+      <c r="F23" s="1"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>10020</v>
+        <v>10010</v>
       </c>
       <c r="B24">
         <v>1010</v>
       </c>
       <c r="C24">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1556,13 +1563,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>10030</v>
+        <v>10020</v>
       </c>
       <c r="B25">
         <v>1010</v>
       </c>
       <c r="C25">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1573,13 +1580,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>10040</v>
+        <v>10030</v>
       </c>
       <c r="B26">
         <v>1010</v>
       </c>
       <c r="C26">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1590,13 +1597,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>10050</v>
+        <v>10040</v>
       </c>
       <c r="B27">
         <v>1010</v>
       </c>
       <c r="C27">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1607,30 +1614,30 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>11010</v>
+        <v>10050</v>
       </c>
       <c r="B28">
         <v>1010</v>
       </c>
       <c r="C28">
-        <v>1110</v>
+        <v>1050</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>11020</v>
+        <v>11010</v>
       </c>
       <c r="B29">
         <v>1010</v>
       </c>
       <c r="C29">
-        <v>1120</v>
+        <v>1110</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1641,13 +1648,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>11030</v>
+        <v>11020</v>
       </c>
       <c r="B30">
         <v>1010</v>
       </c>
       <c r="C30">
-        <v>1130</v>
+        <v>1120</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1658,13 +1665,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>11040</v>
+        <v>11030</v>
       </c>
       <c r="B31">
         <v>1010</v>
       </c>
       <c r="C31">
-        <v>1140</v>
+        <v>1130</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1675,13 +1682,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>11050</v>
+        <v>11040</v>
       </c>
       <c r="B32">
         <v>1010</v>
       </c>
       <c r="C32">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -1692,13 +1699,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>14010</v>
+        <v>11050</v>
       </c>
       <c r="B33">
         <v>1010</v>
       </c>
       <c r="C33">
-        <v>4010</v>
+        <v>1150</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1709,13 +1716,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>14020</v>
+        <v>14010</v>
       </c>
       <c r="B34">
         <v>1010</v>
       </c>
       <c r="C34">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1726,13 +1733,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>14030</v>
+        <v>14020</v>
       </c>
       <c r="B35">
         <v>1010</v>
       </c>
       <c r="C35">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1743,13 +1750,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>14040</v>
+        <v>14030</v>
       </c>
       <c r="B36">
         <v>1010</v>
       </c>
       <c r="C36">
-        <v>4040</v>
+        <v>4030</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1760,16 +1767,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>20010</v>
+        <v>14040</v>
       </c>
       <c r="B37">
-        <v>2010</v>
+        <v>1010</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>4040</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="s">
         <v>29</v>
@@ -1777,16 +1784,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>30010</v>
+        <v>20010</v>
       </c>
       <c r="B38">
-        <v>1010</v>
+        <v>2010</v>
       </c>
       <c r="C38">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="s">
         <v>30</v>
@@ -1794,30 +1801,30 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B39">
         <v>1010</v>
       </c>
       <c r="C39">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="D39">
         <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>40010</v>
+        <v>30020</v>
       </c>
       <c r="B40">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="C40">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1828,52 +1835,52 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>40020</v>
+        <v>40010</v>
       </c>
       <c r="B41">
         <v>2020</v>
       </c>
       <c r="C41">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D41">
         <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>40030</v>
+        <v>40020</v>
       </c>
       <c r="B42">
         <v>2020</v>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D42">
         <v>1</v>
       </c>
       <c r="E42" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>50010</v>
+        <v>40030</v>
       </c>
       <c r="B43">
-        <v>4020</v>
+        <v>2020</v>
       </c>
       <c r="C43">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D43">
-        <v>10</v>
-      </c>
-      <c r="E43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1885,13 +1892,13 @@
         <v>4020</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D44">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1899,33 +1906,33 @@
         <v>50010</v>
       </c>
       <c r="B45">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C45">
-        <v>4010</v>
+        <v>2</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46">
-        <v>50020</v>
+        <v>50010</v>
       </c>
       <c r="B46">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C46">
-        <v>10</v>
+        <v>4010</v>
       </c>
       <c r="D46">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1936,13 +1943,13 @@
         <v>4020</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D47">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1950,33 +1957,33 @@
         <v>50020</v>
       </c>
       <c r="B48">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C48">
-        <v>4010</v>
+        <v>2</v>
       </c>
       <c r="D48">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B49">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C49">
-        <v>10</v>
+        <v>4010</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1987,13 +1994,13 @@
         <v>4020</v>
       </c>
       <c r="C50">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D50">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2004,13 +2011,13 @@
         <v>4020</v>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D51">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2018,16 +2025,16 @@
         <v>50030</v>
       </c>
       <c r="B52">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C52">
-        <v>4020</v>
+        <v>2</v>
       </c>
       <c r="D52">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2035,33 +2042,33 @@
         <v>50030</v>
       </c>
       <c r="B53">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C53">
-        <v>20</v>
+        <v>4020</v>
       </c>
       <c r="D53">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B54">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="C54">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D54">
         <v>10</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2072,13 +2079,13 @@
         <v>4020</v>
       </c>
       <c r="C55">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D55">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2089,13 +2096,13 @@
         <v>4020</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D56">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2103,16 +2110,16 @@
         <v>50040</v>
       </c>
       <c r="B57">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C57">
-        <v>4020</v>
+        <v>2</v>
       </c>
       <c r="D57">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2120,33 +2127,33 @@
         <v>50040</v>
       </c>
       <c r="B58">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C58">
-        <v>20</v>
+        <v>4020</v>
       </c>
       <c r="D58">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B59">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="C59">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D59">
         <v>10</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2157,13 +2164,13 @@
         <v>4020</v>
       </c>
       <c r="C60">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D60">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2174,13 +2181,13 @@
         <v>4020</v>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D61">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2188,16 +2195,16 @@
         <v>50050</v>
       </c>
       <c r="B62">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C62">
-        <v>4030</v>
+        <v>2</v>
       </c>
       <c r="D62">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2205,16 +2212,16 @@
         <v>50050</v>
       </c>
       <c r="B63">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C63">
-        <v>30</v>
+        <v>4030</v>
       </c>
       <c r="D63">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2225,30 +2232,30 @@
         <v>4010</v>
       </c>
       <c r="C64">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D64">
         <v>10</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B65">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="C65">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D65">
         <v>10</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2259,13 +2266,13 @@
         <v>4020</v>
       </c>
       <c r="C66">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D66">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2276,13 +2283,13 @@
         <v>4020</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D67">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2290,16 +2297,16 @@
         <v>50060</v>
       </c>
       <c r="B68">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C68">
-        <v>4030</v>
+        <v>2</v>
       </c>
       <c r="D68">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2307,16 +2314,16 @@
         <v>50060</v>
       </c>
       <c r="B69">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C69">
-        <v>30</v>
+        <v>4030</v>
       </c>
       <c r="D69">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2327,13 +2334,30 @@
         <v>4010</v>
       </c>
       <c r="C70">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D70">
         <v>10</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71">
+        <v>50060</v>
+      </c>
+      <c r="B71">
+        <v>4010</v>
+      </c>
+      <c r="C71">
+        <v>20</v>
+      </c>
+      <c r="D71">
+        <v>10</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2346,12 +2370,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2359,7 +2383,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2367,7 +2391,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2375,7 +2399,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2383,7 +2407,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2399,7 +2423,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2407,7 +2431,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2415,7 +2439,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2423,7 +2447,7 @@
         <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2431,7 +2455,7 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2439,7 +2463,7 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2447,7 +2471,7 @@
         <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2455,7 +2479,7 @@
         <v>100</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2463,7 +2487,7 @@
         <v>101</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2471,7 +2495,7 @@
         <v>210</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2479,7 +2503,7 @@
         <v>1010</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2487,7 +2511,7 @@
         <v>2010</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2495,23 +2519,31 @@
         <v>2020</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>4010</v>
+        <v>2030</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
+        <v>4010</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
         <v>4020</v>
       </c>
-      <c r="B21" t="s">
-        <v>52</v>
+      <c r="B22" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -189,8 +189,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -208,9 +208,84 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,29 +299,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -260,9 +329,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -270,69 +338,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -343,14 +351,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -361,174 +361,180 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -536,12 +542,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -585,17 +585,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -617,17 +622,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
@@ -635,11 +629,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,7 +660,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -669,7 +669,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -678,127 +678,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2065,7 +2065,7 @@
         <v>20</v>
       </c>
       <c r="D54">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>33</v>
@@ -2150,7 +2150,7 @@
         <v>20</v>
       </c>
       <c r="D59">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>33</v>
@@ -2252,7 +2252,7 @@
         <v>20</v>
       </c>
       <c r="D65">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>33</v>
@@ -2354,7 +2354,7 @@
         <v>20</v>
       </c>
       <c r="D71">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>33</v>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="55">
   <si>
     <t>Id</t>
   </si>
@@ -188,8 +188,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -210,7 +210,28 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,54 +246,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -285,21 +261,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -321,6 +290,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -329,8 +305,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -344,11 +337,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -361,25 +361,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -391,157 +505,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -555,17 +555,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -581,26 +575,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -648,7 +622,33 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,7 +660,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -669,7 +669,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -678,127 +678,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -2045,10 +2045,10 @@
         <v>1010</v>
       </c>
       <c r="C53">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D53">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>33</v>
@@ -2059,13 +2059,13 @@
         <v>50030</v>
       </c>
       <c r="B54">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C54">
-        <v>20</v>
+        <v>4020</v>
       </c>
       <c r="D54">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>33</v>
@@ -2073,16 +2073,16 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B55">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="C55">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D55">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>33</v>
@@ -2096,10 +2096,10 @@
         <v>4020</v>
       </c>
       <c r="C56">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D56">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>33</v>
@@ -2113,10 +2113,10 @@
         <v>4020</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D57">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>33</v>
@@ -2127,13 +2127,13 @@
         <v>50040</v>
       </c>
       <c r="B58">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C58">
-        <v>4020</v>
+        <v>2</v>
       </c>
       <c r="D58">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>33</v>
@@ -2144,13 +2144,13 @@
         <v>50040</v>
       </c>
       <c r="B59">
+        <v>1010</v>
+      </c>
+      <c r="C59">
         <v>4010</v>
       </c>
-      <c r="C59">
-        <v>20</v>
-      </c>
       <c r="D59">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>33</v>
@@ -2158,16 +2158,16 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B60">
+        <v>1010</v>
+      </c>
+      <c r="C60">
         <v>4020</v>
       </c>
-      <c r="C60">
-        <v>10</v>
-      </c>
       <c r="D60">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>33</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B61">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="C61">
         <v>20</v>
@@ -2198,10 +2198,10 @@
         <v>4020</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D62">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>33</v>
@@ -2212,13 +2212,13 @@
         <v>50050</v>
       </c>
       <c r="B63">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C63">
-        <v>4030</v>
+        <v>20</v>
       </c>
       <c r="D63">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>33</v>
@@ -2229,13 +2229,13 @@
         <v>50050</v>
       </c>
       <c r="B64">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="C64">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D64">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>33</v>
@@ -2246,13 +2246,13 @@
         <v>50050</v>
       </c>
       <c r="B65">
+        <v>1010</v>
+      </c>
+      <c r="C65">
         <v>4010</v>
       </c>
-      <c r="C65">
-        <v>20</v>
-      </c>
       <c r="D65">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>33</v>
@@ -2260,16 +2260,16 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B66">
+        <v>1010</v>
+      </c>
+      <c r="C66">
         <v>4020</v>
       </c>
-      <c r="C66">
-        <v>10</v>
-      </c>
       <c r="D66">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>33</v>
@@ -2277,16 +2277,16 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B67">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C67">
-        <v>20</v>
+        <v>4030</v>
       </c>
       <c r="D67">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>33</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B68">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="C68">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D68">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>33</v>
@@ -2311,16 +2311,16 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B69">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C69">
-        <v>4030</v>
+        <v>20</v>
       </c>
       <c r="D69">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>33</v>
@@ -2331,10 +2331,10 @@
         <v>50060</v>
       </c>
       <c r="B70">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="C70">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D70">
         <v>10</v>
@@ -2348,7 +2348,7 @@
         <v>50060</v>
       </c>
       <c r="B71">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="C71">
         <v>20</v>
@@ -2357,6 +2357,108 @@
         <v>20</v>
       </c>
       <c r="E71" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72">
+        <v>50060</v>
+      </c>
+      <c r="B72">
+        <v>4020</v>
+      </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
+      <c r="D72">
+        <v>15</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73">
+        <v>50060</v>
+      </c>
+      <c r="B73">
+        <v>1010</v>
+      </c>
+      <c r="C73">
+        <v>4010</v>
+      </c>
+      <c r="D73">
+        <v>4</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74">
+        <v>50060</v>
+      </c>
+      <c r="B74">
+        <v>1010</v>
+      </c>
+      <c r="C74">
+        <v>4020</v>
+      </c>
+      <c r="D74">
+        <v>8</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75">
+        <v>50060</v>
+      </c>
+      <c r="B75">
+        <v>1010</v>
+      </c>
+      <c r="C75">
+        <v>4030</v>
+      </c>
+      <c r="D75">
+        <v>12</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76">
+        <v>50060</v>
+      </c>
+      <c r="B76">
+        <v>4010</v>
+      </c>
+      <c r="C76">
+        <v>30</v>
+      </c>
+      <c r="D76">
+        <v>10</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77">
+        <v>50060</v>
+      </c>
+      <c r="B77">
+        <v>4010</v>
+      </c>
+      <c r="C77">
+        <v>20</v>
+      </c>
+      <c r="D77">
+        <v>20</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>33</v>
       </c>
     </row>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="55">
   <si>
     <t>Id</t>
   </si>
@@ -187,9 +187,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -208,11 +208,70 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -230,36 +289,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -267,10 +297,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -282,24 +313,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -314,10 +330,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -329,28 +345,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -361,187 +361,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -552,30 +552,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -597,8 +573,56 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -620,15 +644,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -637,21 +652,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -660,16 +660,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -678,127 +678,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -2328,16 +2328,16 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B70">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C70">
-        <v>10</v>
+        <v>4310</v>
       </c>
       <c r="D70">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>33</v>
@@ -2351,10 +2351,10 @@
         <v>4020</v>
       </c>
       <c r="C71">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D71">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>33</v>
@@ -2368,10 +2368,10 @@
         <v>4020</v>
       </c>
       <c r="C72">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D72">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>33</v>
@@ -2382,13 +2382,13 @@
         <v>50060</v>
       </c>
       <c r="B73">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C73">
-        <v>4010</v>
+        <v>2</v>
       </c>
       <c r="D73">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>33</v>
@@ -2402,10 +2402,10 @@
         <v>1010</v>
       </c>
       <c r="C74">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D74">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>33</v>
@@ -2419,10 +2419,10 @@
         <v>1010</v>
       </c>
       <c r="C75">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D75">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>33</v>
@@ -2433,13 +2433,13 @@
         <v>50060</v>
       </c>
       <c r="B76">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C76">
-        <v>30</v>
+        <v>4030</v>
       </c>
       <c r="D76">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>33</v>
@@ -2453,12 +2453,46 @@
         <v>4010</v>
       </c>
       <c r="C77">
+        <v>30</v>
+      </c>
+      <c r="D77">
+        <v>10</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78">
+        <v>50060</v>
+      </c>
+      <c r="B78">
+        <v>4010</v>
+      </c>
+      <c r="C78">
         <v>20</v>
       </c>
-      <c r="D77">
+      <c r="D78">
         <v>20</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E78" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79">
+        <v>50060</v>
+      </c>
+      <c r="B79">
+        <v>1010</v>
+      </c>
+      <c r="C79">
+        <v>4310</v>
+      </c>
+      <c r="D79">
+        <v>20</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>33</v>
       </c>
     </row>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="56">
   <si>
     <t>Id</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>特級指南書</t>
+  </si>
+  <si>
+    <t>クラスチェンジ</t>
   </si>
   <si>
     <t>Rankアップ</t>
@@ -187,9 +190,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -208,16 +211,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,29 +229,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -275,6 +265,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -284,54 +282,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -351,6 +301,59 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -361,25 +364,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -391,157 +544,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -552,54 +555,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -628,6 +583,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -644,6 +614,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -652,6 +631,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -660,16 +663,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -678,127 +681,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1128,7 +1131,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -1784,16 +1787,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>20010</v>
+        <v>14310</v>
       </c>
       <c r="B38">
-        <v>2010</v>
+        <v>1010</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>4310</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="s">
         <v>30</v>
@@ -1801,16 +1804,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>30010</v>
+        <v>20010</v>
       </c>
       <c r="B39">
-        <v>1010</v>
+        <v>2010</v>
       </c>
       <c r="C39">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" t="s">
         <v>31</v>
@@ -1818,30 +1821,30 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B40">
         <v>1010</v>
       </c>
       <c r="C40">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="D40">
         <v>1</v>
       </c>
       <c r="E40" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>40010</v>
+        <v>30020</v>
       </c>
       <c r="B41">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="C41">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -1852,52 +1855,52 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>40020</v>
+        <v>40010</v>
       </c>
       <c r="B42">
         <v>2020</v>
       </c>
       <c r="C42">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D42">
         <v>1</v>
       </c>
       <c r="E42" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>40030</v>
+        <v>40020</v>
       </c>
       <c r="B43">
         <v>2020</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D43">
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>50010</v>
+        <v>40030</v>
       </c>
       <c r="B44">
-        <v>4020</v>
+        <v>2020</v>
       </c>
       <c r="C44">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D44">
-        <v>10</v>
-      </c>
-      <c r="E44" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E44" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1909,13 +1912,13 @@
         <v>4020</v>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D45">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1923,33 +1926,33 @@
         <v>50010</v>
       </c>
       <c r="B46">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C46">
-        <v>4010</v>
+        <v>2</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47">
-        <v>50020</v>
+        <v>50010</v>
       </c>
       <c r="B47">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C47">
-        <v>10</v>
+        <v>4010</v>
       </c>
       <c r="D47">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1960,13 +1963,13 @@
         <v>4020</v>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D48">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1974,33 +1977,33 @@
         <v>50020</v>
       </c>
       <c r="B49">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C49">
-        <v>4010</v>
+        <v>2</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B50">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C50">
-        <v>10</v>
+        <v>4010</v>
       </c>
       <c r="D50">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2011,13 +2014,13 @@
         <v>4020</v>
       </c>
       <c r="C51">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D51">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2028,13 +2031,13 @@
         <v>4020</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D52">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2042,16 +2045,16 @@
         <v>50030</v>
       </c>
       <c r="B53">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C53">
-        <v>4010</v>
+        <v>2</v>
       </c>
       <c r="D53">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2062,13 +2065,13 @@
         <v>1010</v>
       </c>
       <c r="C54">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D54">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2076,33 +2079,33 @@
         <v>50030</v>
       </c>
       <c r="B55">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C55">
-        <v>20</v>
+        <v>4020</v>
       </c>
       <c r="D55">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B56">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="C56">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D56">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2113,13 +2116,13 @@
         <v>4020</v>
       </c>
       <c r="C57">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D57">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2130,13 +2133,13 @@
         <v>4020</v>
       </c>
       <c r="C58">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D58">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2144,16 +2147,16 @@
         <v>50040</v>
       </c>
       <c r="B59">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C59">
-        <v>4010</v>
+        <v>2</v>
       </c>
       <c r="D59">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2164,13 +2167,13 @@
         <v>1010</v>
       </c>
       <c r="C60">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D60">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2178,33 +2181,33 @@
         <v>50040</v>
       </c>
       <c r="B61">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C61">
-        <v>20</v>
+        <v>4020</v>
       </c>
       <c r="D61">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B62">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="C62">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D62">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2215,13 +2218,13 @@
         <v>4020</v>
       </c>
       <c r="C63">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D63">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2232,13 +2235,13 @@
         <v>4020</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D64">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2246,16 +2249,16 @@
         <v>50050</v>
       </c>
       <c r="B65">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C65">
-        <v>4010</v>
+        <v>2</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2266,13 +2269,13 @@
         <v>1010</v>
       </c>
       <c r="C66">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D66">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2283,13 +2286,13 @@
         <v>1010</v>
       </c>
       <c r="C67">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D67">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2297,16 +2300,16 @@
         <v>50050</v>
       </c>
       <c r="B68">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C68">
-        <v>30</v>
+        <v>4030</v>
       </c>
       <c r="D68">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2317,13 +2320,13 @@
         <v>4010</v>
       </c>
       <c r="C69">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D69">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2331,33 +2334,33 @@
         <v>50050</v>
       </c>
       <c r="B70">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C70">
-        <v>4310</v>
+        <v>20</v>
       </c>
       <c r="D70">
         <v>20</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B71">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C71">
-        <v>10</v>
+        <v>4310</v>
       </c>
       <c r="D71">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2368,13 +2371,13 @@
         <v>4020</v>
       </c>
       <c r="C72">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D72">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2385,13 +2388,13 @@
         <v>4020</v>
       </c>
       <c r="C73">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D73">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2399,16 +2402,16 @@
         <v>50060</v>
       </c>
       <c r="B74">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C74">
-        <v>4010</v>
+        <v>2</v>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2419,13 +2422,13 @@
         <v>1010</v>
       </c>
       <c r="C75">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D75">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2436,13 +2439,13 @@
         <v>1010</v>
       </c>
       <c r="C76">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D76">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2450,16 +2453,16 @@
         <v>50060</v>
       </c>
       <c r="B77">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C77">
-        <v>30</v>
+        <v>4030</v>
       </c>
       <c r="D77">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2470,13 +2473,13 @@
         <v>4010</v>
       </c>
       <c r="C78">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D78">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2484,16 +2487,33 @@
         <v>50060</v>
       </c>
       <c r="B79">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C79">
-        <v>4310</v>
+        <v>20</v>
       </c>
       <c r="D79">
         <v>20</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80">
+        <v>50060</v>
+      </c>
+      <c r="B80">
+        <v>1010</v>
+      </c>
+      <c r="C80">
+        <v>4310</v>
+      </c>
+      <c r="D80">
+        <v>20</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2511,7 +2531,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2519,7 +2539,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2527,7 +2547,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2535,7 +2555,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2543,7 +2563,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2559,7 +2579,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2567,7 +2587,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2575,7 +2595,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2583,7 +2603,7 @@
         <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2591,7 +2611,7 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2599,7 +2619,7 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2607,7 +2627,7 @@
         <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2615,7 +2635,7 @@
         <v>100</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2623,7 +2643,7 @@
         <v>101</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2631,7 +2651,7 @@
         <v>210</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2639,7 +2659,7 @@
         <v>1010</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2647,7 +2667,7 @@
         <v>2010</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2655,7 +2675,7 @@
         <v>2020</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2663,7 +2683,7 @@
         <v>2030</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2671,7 +2691,7 @@
         <v>4010</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2679,7 +2699,7 @@
         <v>4020</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="56">
   <si>
     <t>Id</t>
   </si>
@@ -191,9 +191,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -212,7 +212,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -221,38 +221,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -266,17 +235,18 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -296,7 +266,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,6 +295,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -318,9 +311,39 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -331,29 +354,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -364,19 +364,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -388,163 +430,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -558,25 +558,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -597,16 +588,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -615,8 +606,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -650,6 +641,15 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
@@ -663,145 +663,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1131,7 +1131,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -2011,13 +2011,13 @@
         <v>50030</v>
       </c>
       <c r="B51">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C51">
-        <v>10</v>
+        <v>5010</v>
       </c>
       <c r="D51">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>34</v>
@@ -2028,13 +2028,13 @@
         <v>50030</v>
       </c>
       <c r="B52">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C52">
-        <v>20</v>
+        <v>5020</v>
       </c>
       <c r="D52">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>34</v>
@@ -2048,10 +2048,10 @@
         <v>4020</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D53">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>34</v>
@@ -2062,13 +2062,13 @@
         <v>50030</v>
       </c>
       <c r="B54">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C54">
-        <v>4010</v>
+        <v>20</v>
       </c>
       <c r="D54">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>34</v>
@@ -2079,13 +2079,13 @@
         <v>50030</v>
       </c>
       <c r="B55">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C55">
-        <v>4020</v>
+        <v>2</v>
       </c>
       <c r="D55">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>34</v>
@@ -2096,13 +2096,13 @@
         <v>50030</v>
       </c>
       <c r="B56">
+        <v>1010</v>
+      </c>
+      <c r="C56">
         <v>4010</v>
       </c>
-      <c r="C56">
-        <v>20</v>
-      </c>
       <c r="D56">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>34</v>
@@ -2110,16 +2110,16 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B57">
+        <v>1010</v>
+      </c>
+      <c r="C57">
         <v>4020</v>
       </c>
-      <c r="C57">
-        <v>10</v>
-      </c>
       <c r="D57">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>34</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B58">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="C58">
         <v>20</v>
@@ -2147,13 +2147,13 @@
         <v>50040</v>
       </c>
       <c r="B59">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C59">
-        <v>2</v>
+        <v>5010</v>
       </c>
       <c r="D59">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>34</v>
@@ -2167,10 +2167,10 @@
         <v>1010</v>
       </c>
       <c r="C60">
-        <v>4010</v>
+        <v>5020</v>
       </c>
       <c r="D60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>34</v>
@@ -2181,13 +2181,13 @@
         <v>50040</v>
       </c>
       <c r="B61">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C61">
-        <v>4020</v>
+        <v>10</v>
       </c>
       <c r="D61">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>34</v>
@@ -2198,7 +2198,7 @@
         <v>50040</v>
       </c>
       <c r="B62">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="C62">
         <v>20</v>
@@ -2212,16 +2212,16 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B63">
         <v>4020</v>
       </c>
       <c r="C63">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D63">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>34</v>
@@ -2229,16 +2229,16 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B64">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C64">
-        <v>20</v>
+        <v>4010</v>
       </c>
       <c r="D64">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>34</v>
@@ -2246,16 +2246,16 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B65">
+        <v>1010</v>
+      </c>
+      <c r="C65">
         <v>4020</v>
       </c>
-      <c r="C65">
-        <v>2</v>
-      </c>
       <c r="D65">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>34</v>
@@ -2263,16 +2263,16 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B66">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C66">
-        <v>4010</v>
+        <v>20</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>34</v>
@@ -2286,10 +2286,10 @@
         <v>1010</v>
       </c>
       <c r="C67">
-        <v>4020</v>
+        <v>5010</v>
       </c>
       <c r="D67">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>34</v>
@@ -2303,10 +2303,10 @@
         <v>1010</v>
       </c>
       <c r="C68">
-        <v>4030</v>
+        <v>5020</v>
       </c>
       <c r="D68">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>34</v>
@@ -2317,10 +2317,10 @@
         <v>50050</v>
       </c>
       <c r="B69">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C69">
-        <v>30</v>
+        <v>5030</v>
       </c>
       <c r="D69">
         <v>10</v>
@@ -2334,13 +2334,13 @@
         <v>50050</v>
       </c>
       <c r="B70">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="C70">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D70">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>34</v>
@@ -2351,10 +2351,10 @@
         <v>50050</v>
       </c>
       <c r="B71">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="C71">
-        <v>4310</v>
+        <v>20</v>
       </c>
       <c r="D71">
         <v>20</v>
@@ -2365,16 +2365,16 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B72">
         <v>4020</v>
       </c>
       <c r="C72">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D72">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>34</v>
@@ -2382,16 +2382,16 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B73">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C73">
-        <v>20</v>
+        <v>4010</v>
       </c>
       <c r="D73">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>34</v>
@@ -2399,16 +2399,16 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B74">
+        <v>1010</v>
+      </c>
+      <c r="C74">
         <v>4020</v>
       </c>
-      <c r="C74">
-        <v>2</v>
-      </c>
       <c r="D74">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>34</v>
@@ -2416,16 +2416,16 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B75">
         <v>1010</v>
       </c>
       <c r="C75">
-        <v>4010</v>
+        <v>4030</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>34</v>
@@ -2433,16 +2433,16 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B76">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C76">
-        <v>4020</v>
+        <v>30</v>
       </c>
       <c r="D76">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>34</v>
@@ -2450,16 +2450,16 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B77">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C77">
-        <v>4030</v>
+        <v>20</v>
       </c>
       <c r="D77">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>34</v>
@@ -2467,16 +2467,16 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B78">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C78">
-        <v>30</v>
+        <v>4310</v>
       </c>
       <c r="D78">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>34</v>
@@ -2487,13 +2487,13 @@
         <v>50060</v>
       </c>
       <c r="B79">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C79">
-        <v>20</v>
+        <v>5010</v>
       </c>
       <c r="D79">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>34</v>
@@ -2507,12 +2507,182 @@
         <v>1010</v>
       </c>
       <c r="C80">
+        <v>5020</v>
+      </c>
+      <c r="D80">
+        <v>5</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81">
+        <v>50060</v>
+      </c>
+      <c r="B81">
+        <v>1010</v>
+      </c>
+      <c r="C81">
+        <v>5030</v>
+      </c>
+      <c r="D81">
+        <v>10</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82">
+        <v>50060</v>
+      </c>
+      <c r="B82">
+        <v>4020</v>
+      </c>
+      <c r="C82">
+        <v>10</v>
+      </c>
+      <c r="D82">
+        <v>10</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83">
+        <v>50060</v>
+      </c>
+      <c r="B83">
+        <v>4020</v>
+      </c>
+      <c r="C83">
+        <v>20</v>
+      </c>
+      <c r="D83">
+        <v>20</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84">
+        <v>50060</v>
+      </c>
+      <c r="B84">
+        <v>4020</v>
+      </c>
+      <c r="C84">
+        <v>2</v>
+      </c>
+      <c r="D84">
+        <v>15</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85">
+        <v>50060</v>
+      </c>
+      <c r="B85">
+        <v>1010</v>
+      </c>
+      <c r="C85">
+        <v>4010</v>
+      </c>
+      <c r="D85">
+        <v>4</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86">
+        <v>50060</v>
+      </c>
+      <c r="B86">
+        <v>1010</v>
+      </c>
+      <c r="C86">
+        <v>4020</v>
+      </c>
+      <c r="D86">
+        <v>8</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87">
+        <v>50060</v>
+      </c>
+      <c r="B87">
+        <v>1010</v>
+      </c>
+      <c r="C87">
+        <v>4030</v>
+      </c>
+      <c r="D87">
+        <v>12</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88">
+        <v>50060</v>
+      </c>
+      <c r="B88">
+        <v>4010</v>
+      </c>
+      <c r="C88">
+        <v>30</v>
+      </c>
+      <c r="D88">
+        <v>10</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89">
+        <v>50060</v>
+      </c>
+      <c r="B89">
+        <v>4010</v>
+      </c>
+      <c r="C89">
+        <v>20</v>
+      </c>
+      <c r="D89">
+        <v>20</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90">
+        <v>50060</v>
+      </c>
+      <c r="B90">
+        <v>1010</v>
+      </c>
+      <c r="C90">
         <v>4310</v>
       </c>
-      <c r="D80">
+      <c r="D90">
         <v>20</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="E90" s="1" t="s">
         <v>34</v>
       </c>
     </row>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="57">
   <si>
     <t>Id</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>クラスチェンジ</t>
+  </si>
+  <si>
+    <t>隠遁のヴェール</t>
   </si>
   <si>
     <t>Rankアップ</t>
@@ -190,10 +193,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -213,15 +216,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -236,17 +231,16 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -257,16 +251,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -275,21 +262,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -311,7 +283,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,8 +303,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -340,18 +351,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -364,13 +367,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -382,31 +505,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -418,133 +535,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -558,17 +561,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -584,41 +583,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -647,6 +611,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -655,6 +643,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -663,16 +666,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -681,127 +684,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1131,7 +1134,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -1804,16 +1807,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>20010</v>
+        <v>15040</v>
       </c>
       <c r="B39">
-        <v>2010</v>
+        <v>1010</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>5040</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" t="s">
         <v>31</v>
@@ -1821,16 +1824,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>30010</v>
+        <v>20010</v>
       </c>
       <c r="B40">
-        <v>1010</v>
+        <v>2010</v>
       </c>
       <c r="C40">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" t="s">
         <v>32</v>
@@ -1838,30 +1841,30 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B41">
         <v>1010</v>
       </c>
       <c r="C41">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="D41">
         <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>40010</v>
+        <v>30020</v>
       </c>
       <c r="B42">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="C42">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -1872,52 +1875,52 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>40020</v>
+        <v>40010</v>
       </c>
       <c r="B43">
         <v>2020</v>
       </c>
       <c r="C43">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D43">
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>40030</v>
+        <v>40020</v>
       </c>
       <c r="B44">
         <v>2020</v>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D44">
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>50010</v>
+        <v>40030</v>
       </c>
       <c r="B45">
-        <v>4020</v>
+        <v>2020</v>
       </c>
       <c r="C45">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D45">
-        <v>10</v>
-      </c>
-      <c r="E45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E45" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1926,16 +1929,16 @@
         <v>50010</v>
       </c>
       <c r="B46">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C46">
-        <v>2</v>
+        <v>1010</v>
       </c>
       <c r="D46">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1946,188 +1949,188 @@
         <v>1010</v>
       </c>
       <c r="C47">
-        <v>4010</v>
+        <v>1020</v>
       </c>
       <c r="D47">
         <v>4</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48">
-        <v>50020</v>
+        <v>50010</v>
       </c>
       <c r="B48">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C48">
-        <v>10</v>
+        <v>1030</v>
       </c>
       <c r="D48">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49">
-        <v>50020</v>
+        <v>50010</v>
       </c>
       <c r="B49">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>1040</v>
       </c>
       <c r="D49">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50">
-        <v>50020</v>
+        <v>50010</v>
       </c>
       <c r="B50">
         <v>1010</v>
       </c>
       <c r="C50">
-        <v>4010</v>
+        <v>1050</v>
       </c>
       <c r="D50">
         <v>4</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51">
-        <v>50030</v>
+        <v>50010</v>
       </c>
       <c r="B51">
         <v>1010</v>
       </c>
       <c r="C51">
-        <v>5010</v>
+        <v>4010</v>
       </c>
       <c r="D51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B52">
         <v>1010</v>
       </c>
       <c r="C52">
-        <v>5020</v>
+        <v>1010</v>
       </c>
       <c r="D52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B53">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C53">
-        <v>10</v>
+        <v>1020</v>
       </c>
       <c r="D53">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B54">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C54">
-        <v>20</v>
+        <v>1030</v>
       </c>
       <c r="D54">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B55">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>1040</v>
       </c>
       <c r="D55">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B56">
         <v>1010</v>
       </c>
       <c r="C56">
-        <v>4010</v>
+        <v>1050</v>
       </c>
       <c r="D56">
         <v>4</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B57">
         <v>1010</v>
       </c>
       <c r="C57">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D57">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B58">
         <v>4010</v>
@@ -2139,12 +2142,12 @@
         <v>20</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B59">
         <v>1010</v>
@@ -2156,12 +2159,12 @@
         <v>5</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B60">
         <v>1010</v>
@@ -2173,318 +2176,318 @@
         <v>5</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B61">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C61">
-        <v>10</v>
+        <v>1010</v>
       </c>
       <c r="D61">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B62">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C62">
-        <v>20</v>
+        <v>1020</v>
       </c>
       <c r="D62">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B63">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>1030</v>
       </c>
       <c r="D63">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B64">
         <v>1010</v>
       </c>
       <c r="C64">
-        <v>4010</v>
+        <v>1040</v>
       </c>
       <c r="D64">
         <v>4</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B65">
         <v>1010</v>
       </c>
       <c r="C65">
-        <v>4020</v>
+        <v>1050</v>
       </c>
       <c r="D65">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B66">
+        <v>1010</v>
+      </c>
+      <c r="C66">
         <v>4010</v>
       </c>
-      <c r="C66">
-        <v>20</v>
-      </c>
       <c r="D66">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>50050</v>
+        <v>50030</v>
       </c>
       <c r="B67">
         <v>1010</v>
       </c>
       <c r="C67">
-        <v>5010</v>
+        <v>4020</v>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>50050</v>
+        <v>50030</v>
       </c>
       <c r="B68">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C68">
-        <v>5020</v>
+        <v>20</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B69">
         <v>1010</v>
       </c>
       <c r="C69">
-        <v>5030</v>
+        <v>5010</v>
       </c>
       <c r="D69">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B70">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C70">
-        <v>10</v>
+        <v>5020</v>
       </c>
       <c r="D70">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B71">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C71">
-        <v>20</v>
+        <v>1110</v>
       </c>
       <c r="D71">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B72">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C72">
-        <v>2</v>
+        <v>1120</v>
       </c>
       <c r="D72">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B73">
         <v>1010</v>
       </c>
       <c r="C73">
-        <v>4010</v>
+        <v>1130</v>
       </c>
       <c r="D73">
         <v>4</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B74">
         <v>1010</v>
       </c>
       <c r="C74">
-        <v>4020</v>
+        <v>1140</v>
       </c>
       <c r="D74">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B75">
         <v>1010</v>
       </c>
       <c r="C75">
-        <v>4030</v>
+        <v>1150</v>
       </c>
       <c r="D75">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B76">
+        <v>1010</v>
+      </c>
+      <c r="C76">
         <v>4010</v>
       </c>
-      <c r="C76">
-        <v>30</v>
-      </c>
       <c r="D76">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B77">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C77">
-        <v>20</v>
+        <v>4020</v>
       </c>
       <c r="D77">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B78">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C78">
-        <v>4310</v>
+        <v>20</v>
       </c>
       <c r="D78">
         <v>20</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B79">
         <v>1010</v>
@@ -2496,12 +2499,12 @@
         <v>5</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B80">
         <v>1010</v>
@@ -2513,177 +2516,415 @@
         <v>5</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B81">
         <v>1010</v>
       </c>
       <c r="C81">
-        <v>5030</v>
+        <v>1110</v>
       </c>
       <c r="D81">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B82">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C82">
-        <v>10</v>
+        <v>1120</v>
       </c>
       <c r="D82">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B83">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C83">
-        <v>20</v>
+        <v>1130</v>
       </c>
       <c r="D83">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B84">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>1140</v>
       </c>
       <c r="D84">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B85">
         <v>1010</v>
       </c>
       <c r="C85">
-        <v>4010</v>
+        <v>1150</v>
       </c>
       <c r="D85">
         <v>4</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B86">
         <v>1010</v>
       </c>
       <c r="C86">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D86">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B87">
         <v>1010</v>
       </c>
       <c r="C87">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D87">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B88">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C88">
-        <v>30</v>
+        <v>4030</v>
       </c>
       <c r="D88">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B89">
         <v>4010</v>
       </c>
       <c r="C89">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D89">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B90">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C90">
-        <v>4310</v>
+        <v>20</v>
       </c>
       <c r="D90">
         <v>20</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91">
+        <v>50050</v>
+      </c>
+      <c r="B91">
+        <v>1010</v>
+      </c>
+      <c r="C91">
+        <v>4310</v>
+      </c>
+      <c r="D91">
+        <v>20</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92">
+        <v>50060</v>
+      </c>
+      <c r="B92">
+        <v>1010</v>
+      </c>
+      <c r="C92">
+        <v>5010</v>
+      </c>
+      <c r="D92">
+        <v>5</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93">
+        <v>50060</v>
+      </c>
+      <c r="B93">
+        <v>1010</v>
+      </c>
+      <c r="C93">
+        <v>5020</v>
+      </c>
+      <c r="D93">
+        <v>5</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94">
+        <v>50060</v>
+      </c>
+      <c r="B94">
+        <v>1010</v>
+      </c>
+      <c r="C94">
+        <v>1110</v>
+      </c>
+      <c r="D94">
+        <v>4</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95">
+        <v>50060</v>
+      </c>
+      <c r="B95">
+        <v>1010</v>
+      </c>
+      <c r="C95">
+        <v>1120</v>
+      </c>
+      <c r="D95">
+        <v>4</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96">
+        <v>50060</v>
+      </c>
+      <c r="B96">
+        <v>1010</v>
+      </c>
+      <c r="C96">
+        <v>1130</v>
+      </c>
+      <c r="D96">
+        <v>4</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97">
+        <v>50060</v>
+      </c>
+      <c r="B97">
+        <v>1010</v>
+      </c>
+      <c r="C97">
+        <v>1140</v>
+      </c>
+      <c r="D97">
+        <v>4</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98">
+        <v>50060</v>
+      </c>
+      <c r="B98">
+        <v>1010</v>
+      </c>
+      <c r="C98">
+        <v>1150</v>
+      </c>
+      <c r="D98">
+        <v>4</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99">
+        <v>50060</v>
+      </c>
+      <c r="B99">
+        <v>1010</v>
+      </c>
+      <c r="C99">
+        <v>4010</v>
+      </c>
+      <c r="D99">
+        <v>4</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100">
+        <v>50060</v>
+      </c>
+      <c r="B100">
+        <v>1010</v>
+      </c>
+      <c r="C100">
+        <v>4020</v>
+      </c>
+      <c r="D100">
+        <v>8</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101">
+        <v>50060</v>
+      </c>
+      <c r="B101">
+        <v>1010</v>
+      </c>
+      <c r="C101">
+        <v>4030</v>
+      </c>
+      <c r="D101">
+        <v>12</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102">
+        <v>50060</v>
+      </c>
+      <c r="B102">
+        <v>4010</v>
+      </c>
+      <c r="C102">
+        <v>30</v>
+      </c>
+      <c r="D102">
+        <v>10</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103">
+        <v>50060</v>
+      </c>
+      <c r="B103">
+        <v>4010</v>
+      </c>
+      <c r="C103">
+        <v>20</v>
+      </c>
+      <c r="D103">
+        <v>20</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104">
+        <v>50060</v>
+      </c>
+      <c r="B104">
+        <v>1010</v>
+      </c>
+      <c r="C104">
+        <v>4310</v>
+      </c>
+      <c r="D104">
+        <v>20</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2701,7 +2942,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2709,7 +2950,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2717,7 +2958,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2725,7 +2966,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2733,7 +2974,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2749,7 +2990,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2757,7 +2998,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2765,7 +3006,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2773,7 +3014,7 @@
         <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2781,7 +3022,7 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2789,7 +3030,7 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2797,7 +3038,7 @@
         <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2805,7 +3046,7 @@
         <v>100</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2813,7 +3054,7 @@
         <v>101</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2821,7 +3062,7 @@
         <v>210</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2829,7 +3070,7 @@
         <v>1010</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2837,7 +3078,7 @@
         <v>2010</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2845,7 +3086,7 @@
         <v>2020</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2853,7 +3094,7 @@
         <v>2030</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2861,7 +3102,7 @@
         <v>4010</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2869,7 +3110,7 @@
         <v>4020</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="57">
   <si>
     <t>Id</t>
   </si>
@@ -193,8 +193,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -216,7 +216,43 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -230,38 +266,32 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -276,21 +306,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -303,40 +327,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -357,6 +349,14 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -364,6 +364,48 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -379,13 +421,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -397,7 +433,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -409,13 +475,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -427,31 +499,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -463,7 +529,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -475,79 +547,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -558,17 +558,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -587,6 +576,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -598,15 +596,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -629,8 +618,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -658,6 +647,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -666,7 +666,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -675,7 +675,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -684,127 +684,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1134,7 +1134,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -1935,7 +1935,7 @@
         <v>1010</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>35</v>
@@ -1952,7 +1952,7 @@
         <v>1020</v>
       </c>
       <c r="D47">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>35</v>
@@ -1969,7 +1969,7 @@
         <v>1030</v>
       </c>
       <c r="D48">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>35</v>
@@ -1986,7 +1986,7 @@
         <v>1040</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>35</v>
@@ -2003,7 +2003,7 @@
         <v>1050</v>
       </c>
       <c r="D50">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>35</v>
@@ -2037,7 +2037,7 @@
         <v>1010</v>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>35</v>
@@ -2054,7 +2054,7 @@
         <v>1020</v>
       </c>
       <c r="D53">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>35</v>
@@ -2071,7 +2071,7 @@
         <v>1030</v>
       </c>
       <c r="D54">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>35</v>
@@ -2088,7 +2088,7 @@
         <v>1040</v>
       </c>
       <c r="D55">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>35</v>
@@ -2105,7 +2105,7 @@
         <v>1050</v>
       </c>
       <c r="D56">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>35</v>
@@ -2187,10 +2187,10 @@
         <v>1010</v>
       </c>
       <c r="C61">
-        <v>1010</v>
+        <v>5040</v>
       </c>
       <c r="D61">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>35</v>
@@ -2204,10 +2204,10 @@
         <v>1010</v>
       </c>
       <c r="C62">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="D62">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>35</v>
@@ -2221,10 +2221,10 @@
         <v>1010</v>
       </c>
       <c r="C63">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="D63">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>35</v>
@@ -2238,10 +2238,10 @@
         <v>1010</v>
       </c>
       <c r="C64">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>35</v>
@@ -2255,10 +2255,10 @@
         <v>1010</v>
       </c>
       <c r="C65">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>35</v>
@@ -2272,10 +2272,10 @@
         <v>1010</v>
       </c>
       <c r="C66">
-        <v>4010</v>
+        <v>1050</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>35</v>
@@ -2289,10 +2289,10 @@
         <v>1010</v>
       </c>
       <c r="C67">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D67">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>35</v>
@@ -2303,13 +2303,13 @@
         <v>50030</v>
       </c>
       <c r="B68">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C68">
-        <v>20</v>
+        <v>4020</v>
       </c>
       <c r="D68">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>35</v>
@@ -2317,16 +2317,16 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B69">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C69">
-        <v>5010</v>
+        <v>20</v>
       </c>
       <c r="D69">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>35</v>
@@ -2340,7 +2340,7 @@
         <v>1010</v>
       </c>
       <c r="C70">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="D70">
         <v>5</v>
@@ -2357,10 +2357,10 @@
         <v>1010</v>
       </c>
       <c r="C71">
-        <v>1110</v>
+        <v>5020</v>
       </c>
       <c r="D71">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>35</v>
@@ -2374,10 +2374,10 @@
         <v>1010</v>
       </c>
       <c r="C72">
-        <v>1120</v>
+        <v>5040</v>
       </c>
       <c r="D72">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>35</v>
@@ -2391,10 +2391,10 @@
         <v>1010</v>
       </c>
       <c r="C73">
-        <v>1130</v>
+        <v>1110</v>
       </c>
       <c r="D73">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>35</v>
@@ -2408,10 +2408,10 @@
         <v>1010</v>
       </c>
       <c r="C74">
-        <v>1140</v>
+        <v>1120</v>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>35</v>
@@ -2425,10 +2425,10 @@
         <v>1010</v>
       </c>
       <c r="C75">
-        <v>1150</v>
+        <v>1130</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>35</v>
@@ -2442,10 +2442,10 @@
         <v>1010</v>
       </c>
       <c r="C76">
-        <v>4010</v>
+        <v>1140</v>
       </c>
       <c r="D76">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>35</v>
@@ -2459,10 +2459,10 @@
         <v>1010</v>
       </c>
       <c r="C77">
-        <v>4020</v>
+        <v>1150</v>
       </c>
       <c r="D77">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>35</v>
@@ -2473,13 +2473,13 @@
         <v>50040</v>
       </c>
       <c r="B78">
+        <v>1010</v>
+      </c>
+      <c r="C78">
         <v>4010</v>
       </c>
-      <c r="C78">
-        <v>20</v>
-      </c>
       <c r="D78">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>35</v>
@@ -2487,16 +2487,16 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B79">
         <v>1010</v>
       </c>
       <c r="C79">
-        <v>5010</v>
+        <v>4020</v>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>35</v>
@@ -2504,16 +2504,16 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B80">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C80">
-        <v>5020</v>
+        <v>20</v>
       </c>
       <c r="D80">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>35</v>
@@ -2521,16 +2521,16 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B81">
         <v>1010</v>
       </c>
       <c r="C81">
-        <v>1110</v>
+        <v>4310</v>
       </c>
       <c r="D81">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>35</v>
@@ -2544,10 +2544,10 @@
         <v>1010</v>
       </c>
       <c r="C82">
-        <v>1120</v>
+        <v>5010</v>
       </c>
       <c r="D82">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>35</v>
@@ -2561,10 +2561,10 @@
         <v>1010</v>
       </c>
       <c r="C83">
-        <v>1130</v>
+        <v>5020</v>
       </c>
       <c r="D83">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>35</v>
@@ -2578,10 +2578,10 @@
         <v>1010</v>
       </c>
       <c r="C84">
-        <v>1140</v>
+        <v>5040</v>
       </c>
       <c r="D84">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>35</v>
@@ -2595,10 +2595,10 @@
         <v>1010</v>
       </c>
       <c r="C85">
-        <v>1150</v>
+        <v>1110</v>
       </c>
       <c r="D85">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>35</v>
@@ -2612,10 +2612,10 @@
         <v>1010</v>
       </c>
       <c r="C86">
-        <v>4010</v>
+        <v>1120</v>
       </c>
       <c r="D86">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>35</v>
@@ -2629,10 +2629,10 @@
         <v>1010</v>
       </c>
       <c r="C87">
-        <v>4020</v>
+        <v>1130</v>
       </c>
       <c r="D87">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>35</v>
@@ -2646,10 +2646,10 @@
         <v>1010</v>
       </c>
       <c r="C88">
-        <v>4030</v>
+        <v>1140</v>
       </c>
       <c r="D88">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>35</v>
@@ -2660,13 +2660,13 @@
         <v>50050</v>
       </c>
       <c r="B89">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C89">
-        <v>30</v>
+        <v>1150</v>
       </c>
       <c r="D89">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>35</v>
@@ -2677,13 +2677,13 @@
         <v>50050</v>
       </c>
       <c r="B90">
+        <v>1010</v>
+      </c>
+      <c r="C90">
         <v>4010</v>
       </c>
-      <c r="C90">
-        <v>20</v>
-      </c>
       <c r="D90">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>35</v>
@@ -2697,10 +2697,10 @@
         <v>1010</v>
       </c>
       <c r="C91">
-        <v>4310</v>
+        <v>4020</v>
       </c>
       <c r="D91">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>35</v>
@@ -2708,16 +2708,16 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B92">
         <v>1010</v>
       </c>
       <c r="C92">
-        <v>5010</v>
+        <v>4030</v>
       </c>
       <c r="D92">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>35</v>
@@ -2725,16 +2725,16 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B93">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C93">
-        <v>5020</v>
+        <v>30</v>
       </c>
       <c r="D93">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>35</v>
@@ -2742,16 +2742,16 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B94">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C94">
-        <v>1110</v>
+        <v>20</v>
       </c>
       <c r="D94">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>35</v>
@@ -2759,16 +2759,16 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B95">
         <v>1010</v>
       </c>
       <c r="C95">
-        <v>1120</v>
+        <v>4310</v>
       </c>
       <c r="D95">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>35</v>
@@ -2782,10 +2782,10 @@
         <v>1010</v>
       </c>
       <c r="C96">
-        <v>1130</v>
+        <v>5010</v>
       </c>
       <c r="D96">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>35</v>
@@ -2799,10 +2799,10 @@
         <v>1010</v>
       </c>
       <c r="C97">
-        <v>1140</v>
+        <v>5020</v>
       </c>
       <c r="D97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>35</v>
@@ -2816,10 +2816,10 @@
         <v>1010</v>
       </c>
       <c r="C98">
-        <v>1150</v>
+        <v>5040</v>
       </c>
       <c r="D98">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>35</v>
@@ -2833,10 +2833,10 @@
         <v>1010</v>
       </c>
       <c r="C99">
-        <v>4010</v>
+        <v>1110</v>
       </c>
       <c r="D99">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>35</v>
@@ -2850,10 +2850,10 @@
         <v>1010</v>
       </c>
       <c r="C100">
-        <v>4020</v>
+        <v>1120</v>
       </c>
       <c r="D100">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>35</v>
@@ -2867,10 +2867,10 @@
         <v>1010</v>
       </c>
       <c r="C101">
-        <v>4030</v>
+        <v>1130</v>
       </c>
       <c r="D101">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>35</v>
@@ -2881,13 +2881,13 @@
         <v>50060</v>
       </c>
       <c r="B102">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C102">
-        <v>30</v>
+        <v>1140</v>
       </c>
       <c r="D102">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>35</v>
@@ -2898,13 +2898,13 @@
         <v>50060</v>
       </c>
       <c r="B103">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C103">
-        <v>20</v>
+        <v>1150</v>
       </c>
       <c r="D103">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>35</v>
@@ -2918,12 +2918,97 @@
         <v>1010</v>
       </c>
       <c r="C104">
+        <v>4010</v>
+      </c>
+      <c r="D104">
+        <v>4</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105">
+        <v>50060</v>
+      </c>
+      <c r="B105">
+        <v>1010</v>
+      </c>
+      <c r="C105">
+        <v>4020</v>
+      </c>
+      <c r="D105">
+        <v>8</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106">
+        <v>50060</v>
+      </c>
+      <c r="B106">
+        <v>1010</v>
+      </c>
+      <c r="C106">
+        <v>4030</v>
+      </c>
+      <c r="D106">
+        <v>12</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107">
+        <v>50060</v>
+      </c>
+      <c r="B107">
+        <v>4010</v>
+      </c>
+      <c r="C107">
+        <v>30</v>
+      </c>
+      <c r="D107">
+        <v>10</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108">
+        <v>50060</v>
+      </c>
+      <c r="B108">
+        <v>4010</v>
+      </c>
+      <c r="C108">
+        <v>20</v>
+      </c>
+      <c r="D108">
+        <v>20</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109">
+        <v>50060</v>
+      </c>
+      <c r="B109">
+        <v>1010</v>
+      </c>
+      <c r="C109">
         <v>4310</v>
       </c>
-      <c r="D104">
-        <v>20</v>
-      </c>
-      <c r="E104" s="1" t="s">
+      <c r="D109">
+        <v>30</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>35</v>
       </c>
     </row>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -193,10 +193,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -214,17 +214,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -244,10 +235,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -259,39 +267,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -306,7 +282,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -320,23 +312,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -357,6 +350,13 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -367,13 +367,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -391,67 +499,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -463,91 +547,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -576,15 +576,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -596,6 +587,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -618,8 +618,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -666,145 +666,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2204,10 +2204,10 @@
         <v>1010</v>
       </c>
       <c r="C62">
-        <v>1010</v>
+        <v>1110</v>
       </c>
       <c r="D62">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>35</v>
@@ -2221,10 +2221,10 @@
         <v>1010</v>
       </c>
       <c r="C63">
-        <v>1020</v>
+        <v>1120</v>
       </c>
       <c r="D63">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>35</v>
@@ -2238,10 +2238,10 @@
         <v>1010</v>
       </c>
       <c r="C64">
-        <v>1030</v>
+        <v>1130</v>
       </c>
       <c r="D64">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>35</v>
@@ -2255,10 +2255,10 @@
         <v>1010</v>
       </c>
       <c r="C65">
-        <v>1040</v>
+        <v>1140</v>
       </c>
       <c r="D65">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>35</v>
@@ -2272,10 +2272,10 @@
         <v>1010</v>
       </c>
       <c r="C66">
-        <v>1050</v>
+        <v>1150</v>
       </c>
       <c r="D66">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>35</v>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="57">
   <si>
     <t>Id</t>
   </si>
@@ -214,8 +214,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -228,8 +243,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -243,9 +274,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -260,14 +312,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -276,29 +321,6 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -313,6 +335,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -321,38 +351,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -367,7 +367,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -379,37 +481,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -421,55 +523,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -481,73 +547,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -558,6 +558,32 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -576,17 +602,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,15 +639,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
@@ -647,17 +658,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -666,7 +666,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -675,7 +675,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -684,127 +684,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1134,7 +1134,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F109"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -2153,10 +2153,10 @@
         <v>1010</v>
       </c>
       <c r="C59">
-        <v>5010</v>
+        <v>1110</v>
       </c>
       <c r="D59">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>35</v>
@@ -2170,10 +2170,10 @@
         <v>1010</v>
       </c>
       <c r="C60">
-        <v>5020</v>
+        <v>1120</v>
       </c>
       <c r="D60">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>35</v>
@@ -2187,10 +2187,10 @@
         <v>1010</v>
       </c>
       <c r="C61">
-        <v>5040</v>
+        <v>1130</v>
       </c>
       <c r="D61">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>35</v>
@@ -2204,7 +2204,7 @@
         <v>1010</v>
       </c>
       <c r="C62">
-        <v>1110</v>
+        <v>1140</v>
       </c>
       <c r="D62">
         <v>15</v>
@@ -2221,7 +2221,7 @@
         <v>1010</v>
       </c>
       <c r="C63">
-        <v>1120</v>
+        <v>1150</v>
       </c>
       <c r="D63">
         <v>15</v>
@@ -2238,10 +2238,10 @@
         <v>1010</v>
       </c>
       <c r="C64">
-        <v>1130</v>
+        <v>4010</v>
       </c>
       <c r="D64">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>35</v>
@@ -2255,10 +2255,10 @@
         <v>1010</v>
       </c>
       <c r="C65">
-        <v>1140</v>
+        <v>4020</v>
       </c>
       <c r="D65">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>35</v>
@@ -2269,13 +2269,13 @@
         <v>50030</v>
       </c>
       <c r="B66">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C66">
-        <v>1150</v>
+        <v>20</v>
       </c>
       <c r="D66">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>35</v>
@@ -2289,10 +2289,10 @@
         <v>1010</v>
       </c>
       <c r="C67">
-        <v>4010</v>
+        <v>5010</v>
       </c>
       <c r="D67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>35</v>
@@ -2306,10 +2306,10 @@
         <v>1010</v>
       </c>
       <c r="C68">
-        <v>4020</v>
+        <v>5020</v>
       </c>
       <c r="D68">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>35</v>
@@ -2317,16 +2317,16 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>50030</v>
+        <v>50040</v>
       </c>
       <c r="B69">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C69">
-        <v>20</v>
+        <v>1110</v>
       </c>
       <c r="D69">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>35</v>
@@ -2340,10 +2340,10 @@
         <v>1010</v>
       </c>
       <c r="C70">
-        <v>5010</v>
+        <v>1120</v>
       </c>
       <c r="D70">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>35</v>
@@ -2357,10 +2357,10 @@
         <v>1010</v>
       </c>
       <c r="C71">
-        <v>5020</v>
+        <v>1130</v>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>35</v>
@@ -2374,10 +2374,10 @@
         <v>1010</v>
       </c>
       <c r="C72">
-        <v>5040</v>
+        <v>1140</v>
       </c>
       <c r="D72">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>35</v>
@@ -2391,7 +2391,7 @@
         <v>1010</v>
       </c>
       <c r="C73">
-        <v>1110</v>
+        <v>1150</v>
       </c>
       <c r="D73">
         <v>15</v>
@@ -2408,10 +2408,10 @@
         <v>1010</v>
       </c>
       <c r="C74">
-        <v>1120</v>
+        <v>4010</v>
       </c>
       <c r="D74">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>35</v>
@@ -2425,10 +2425,10 @@
         <v>1010</v>
       </c>
       <c r="C75">
-        <v>1130</v>
+        <v>4020</v>
       </c>
       <c r="D75">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>35</v>
@@ -2442,10 +2442,10 @@
         <v>1010</v>
       </c>
       <c r="C76">
-        <v>1140</v>
+        <v>4020</v>
       </c>
       <c r="D76">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>35</v>
@@ -2456,13 +2456,13 @@
         <v>50040</v>
       </c>
       <c r="B77">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C77">
-        <v>1150</v>
+        <v>20</v>
       </c>
       <c r="D77">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>35</v>
@@ -2476,10 +2476,10 @@
         <v>1010</v>
       </c>
       <c r="C78">
-        <v>4010</v>
+        <v>5010</v>
       </c>
       <c r="D78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>35</v>
@@ -2493,10 +2493,10 @@
         <v>1010</v>
       </c>
       <c r="C79">
-        <v>4020</v>
+        <v>5020</v>
       </c>
       <c r="D79">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>35</v>
@@ -2507,13 +2507,13 @@
         <v>50040</v>
       </c>
       <c r="B80">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C80">
-        <v>20</v>
+        <v>5040</v>
       </c>
       <c r="D80">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>35</v>
@@ -2544,10 +2544,10 @@
         <v>1010</v>
       </c>
       <c r="C82">
-        <v>5010</v>
+        <v>1110</v>
       </c>
       <c r="D82">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>35</v>
@@ -2561,10 +2561,10 @@
         <v>1010</v>
       </c>
       <c r="C83">
-        <v>5020</v>
+        <v>1120</v>
       </c>
       <c r="D83">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>35</v>
@@ -2578,10 +2578,10 @@
         <v>1010</v>
       </c>
       <c r="C84">
-        <v>5040</v>
+        <v>1130</v>
       </c>
       <c r="D84">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>35</v>
@@ -2595,7 +2595,7 @@
         <v>1010</v>
       </c>
       <c r="C85">
-        <v>1110</v>
+        <v>1140</v>
       </c>
       <c r="D85">
         <v>15</v>
@@ -2612,7 +2612,7 @@
         <v>1010</v>
       </c>
       <c r="C86">
-        <v>1120</v>
+        <v>1150</v>
       </c>
       <c r="D86">
         <v>15</v>
@@ -2629,10 +2629,10 @@
         <v>1010</v>
       </c>
       <c r="C87">
-        <v>1130</v>
+        <v>4010</v>
       </c>
       <c r="D87">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>35</v>
@@ -2646,10 +2646,10 @@
         <v>1010</v>
       </c>
       <c r="C88">
-        <v>1140</v>
+        <v>4020</v>
       </c>
       <c r="D88">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>35</v>
@@ -2663,10 +2663,10 @@
         <v>1010</v>
       </c>
       <c r="C89">
-        <v>1150</v>
+        <v>4020</v>
       </c>
       <c r="D89">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>35</v>
@@ -2680,10 +2680,10 @@
         <v>1010</v>
       </c>
       <c r="C90">
-        <v>4010</v>
+        <v>4030</v>
       </c>
       <c r="D90">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>35</v>
@@ -2694,13 +2694,13 @@
         <v>50050</v>
       </c>
       <c r="B91">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C91">
-        <v>4020</v>
+        <v>30</v>
       </c>
       <c r="D91">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>35</v>
@@ -2711,13 +2711,13 @@
         <v>50050</v>
       </c>
       <c r="B92">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C92">
-        <v>4030</v>
+        <v>20</v>
       </c>
       <c r="D92">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>35</v>
@@ -2728,13 +2728,13 @@
         <v>50050</v>
       </c>
       <c r="B93">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C93">
+        <v>4310</v>
+      </c>
+      <c r="D93">
         <v>30</v>
-      </c>
-      <c r="D93">
-        <v>10</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>35</v>
@@ -2745,13 +2745,13 @@
         <v>50050</v>
       </c>
       <c r="B94">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C94">
-        <v>20</v>
+        <v>5010</v>
       </c>
       <c r="D94">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>35</v>
@@ -2765,10 +2765,10 @@
         <v>1010</v>
       </c>
       <c r="C95">
-        <v>4310</v>
+        <v>5020</v>
       </c>
       <c r="D95">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>35</v>
@@ -2776,16 +2776,16 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B96">
         <v>1010</v>
       </c>
       <c r="C96">
-        <v>5010</v>
+        <v>5040</v>
       </c>
       <c r="D96">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>35</v>
@@ -2799,10 +2799,10 @@
         <v>1010</v>
       </c>
       <c r="C97">
-        <v>5020</v>
+        <v>1110</v>
       </c>
       <c r="D97">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>35</v>
@@ -2816,10 +2816,10 @@
         <v>1010</v>
       </c>
       <c r="C98">
-        <v>5040</v>
+        <v>1120</v>
       </c>
       <c r="D98">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>35</v>
@@ -2833,7 +2833,7 @@
         <v>1010</v>
       </c>
       <c r="C99">
-        <v>1110</v>
+        <v>1130</v>
       </c>
       <c r="D99">
         <v>15</v>
@@ -2850,7 +2850,7 @@
         <v>1010</v>
       </c>
       <c r="C100">
-        <v>1120</v>
+        <v>1140</v>
       </c>
       <c r="D100">
         <v>15</v>
@@ -2867,7 +2867,7 @@
         <v>1010</v>
       </c>
       <c r="C101">
-        <v>1130</v>
+        <v>1150</v>
       </c>
       <c r="D101">
         <v>15</v>
@@ -2884,10 +2884,10 @@
         <v>1010</v>
       </c>
       <c r="C102">
-        <v>1140</v>
+        <v>4010</v>
       </c>
       <c r="D102">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>35</v>
@@ -2901,10 +2901,10 @@
         <v>1010</v>
       </c>
       <c r="C103">
-        <v>1150</v>
+        <v>4020</v>
       </c>
       <c r="D103">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>35</v>
@@ -2918,10 +2918,10 @@
         <v>1010</v>
       </c>
       <c r="C104">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="D104">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>35</v>
@@ -2935,10 +2935,10 @@
         <v>1010</v>
       </c>
       <c r="C105">
-        <v>4020</v>
+        <v>4030</v>
       </c>
       <c r="D105">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>35</v>
@@ -3009,6 +3009,57 @@
         <v>30</v>
       </c>
       <c r="E109" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110">
+        <v>50060</v>
+      </c>
+      <c r="B110">
+        <v>1010</v>
+      </c>
+      <c r="C110">
+        <v>5010</v>
+      </c>
+      <c r="D110">
+        <v>5</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111">
+        <v>50060</v>
+      </c>
+      <c r="B111">
+        <v>1010</v>
+      </c>
+      <c r="C111">
+        <v>5020</v>
+      </c>
+      <c r="D111">
+        <v>5</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112">
+        <v>50060</v>
+      </c>
+      <c r="B112">
+        <v>1010</v>
+      </c>
+      <c r="C112">
+        <v>5040</v>
+      </c>
+      <c r="D112">
+        <v>10</v>
+      </c>
+      <c r="E112" s="1" t="s">
         <v>35</v>
       </c>
     </row>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="56">
   <si>
     <t>Id</t>
   </si>
@@ -80,6 +80,9 @@
     <t>招聘コマンド回数+1</t>
   </si>
   <si>
+    <t>回復薬回数+1</t>
+  </si>
+  <si>
     <t>炎の精霊石x1</t>
   </si>
   <si>
@@ -149,15 +152,6 @@
     <t>Regene</t>
   </si>
   <si>
-    <t>バトルボーナス</t>
-  </si>
-  <si>
-    <t>Nu獲得量アップ</t>
-  </si>
-  <si>
-    <t>敵Lvアップ</t>
-  </si>
-  <si>
     <t>SelectRelic</t>
   </si>
   <si>
@@ -180,6 +174,9 @@
   </si>
   <si>
     <t>招聘コマンド回数</t>
+  </si>
+  <si>
+    <t>回復薬最大数</t>
   </si>
   <si>
     <t>取引用・ランダムアイテム</t>
@@ -194,8 +191,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -214,11 +211,47 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -230,14 +263,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -252,7 +278,31 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -266,23 +316,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -296,65 +347,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -367,7 +364,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -379,31 +508,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -415,103 +526,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -523,31 +544,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -561,27 +558,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -604,8 +584,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -635,11 +617,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -658,6 +646,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -666,7 +663,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -675,7 +672,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -684,127 +681,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1134,7 +1131,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F113"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -1550,32 +1547,33 @@
       </c>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:6">
       <c r="A24">
-        <v>10010</v>
+        <v>1110</v>
       </c>
       <c r="B24">
-        <v>1010</v>
+        <v>2040</v>
       </c>
       <c r="C24">
-        <v>1010</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="s">
         <v>21</v>
       </c>
+      <c r="F24" s="1"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>10020</v>
+        <v>10010</v>
       </c>
       <c r="B25">
         <v>1010</v>
       </c>
       <c r="C25">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1586,13 +1584,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>10030</v>
+        <v>10020</v>
       </c>
       <c r="B26">
         <v>1010</v>
       </c>
       <c r="C26">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1603,13 +1601,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>10040</v>
+        <v>10030</v>
       </c>
       <c r="B27">
         <v>1010</v>
       </c>
       <c r="C27">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1620,13 +1618,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>10050</v>
+        <v>10040</v>
       </c>
       <c r="B28">
         <v>1010</v>
       </c>
       <c r="C28">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -1637,30 +1635,30 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>11010</v>
+        <v>10050</v>
       </c>
       <c r="B29">
         <v>1010</v>
       </c>
       <c r="C29">
-        <v>1110</v>
+        <v>1050</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>11020</v>
+        <v>11010</v>
       </c>
       <c r="B30">
         <v>1010</v>
       </c>
       <c r="C30">
-        <v>1120</v>
+        <v>1110</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1671,13 +1669,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>11030</v>
+        <v>11020</v>
       </c>
       <c r="B31">
         <v>1010</v>
       </c>
       <c r="C31">
-        <v>1130</v>
+        <v>1120</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1688,13 +1686,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>11040</v>
+        <v>11030</v>
       </c>
       <c r="B32">
         <v>1010</v>
       </c>
       <c r="C32">
-        <v>1140</v>
+        <v>1130</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -1705,13 +1703,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>11050</v>
+        <v>11040</v>
       </c>
       <c r="B33">
         <v>1010</v>
       </c>
       <c r="C33">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1722,13 +1720,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>14010</v>
+        <v>11050</v>
       </c>
       <c r="B34">
         <v>1010</v>
       </c>
       <c r="C34">
-        <v>4010</v>
+        <v>1150</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1739,13 +1737,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>14020</v>
+        <v>14010</v>
       </c>
       <c r="B35">
         <v>1010</v>
       </c>
       <c r="C35">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1756,13 +1754,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>14030</v>
+        <v>14020</v>
       </c>
       <c r="B36">
         <v>1010</v>
       </c>
       <c r="C36">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1773,13 +1771,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>14040</v>
+        <v>14030</v>
       </c>
       <c r="B37">
         <v>1010</v>
       </c>
       <c r="C37">
-        <v>4040</v>
+        <v>4030</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1790,13 +1788,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>14310</v>
+        <v>14040</v>
       </c>
       <c r="B38">
         <v>1010</v>
       </c>
       <c r="C38">
-        <v>4310</v>
+        <v>4040</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -1807,13 +1805,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>15040</v>
+        <v>14310</v>
       </c>
       <c r="B39">
         <v>1010</v>
       </c>
       <c r="C39">
-        <v>5040</v>
+        <v>4310</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1824,16 +1822,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>20010</v>
+        <v>15040</v>
       </c>
       <c r="B40">
-        <v>2010</v>
+        <v>1010</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>5040</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" t="s">
         <v>32</v>
@@ -1841,16 +1839,16 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>30010</v>
+        <v>20010</v>
       </c>
       <c r="B41">
-        <v>1010</v>
+        <v>2010</v>
       </c>
       <c r="C41">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="s">
         <v>33</v>
@@ -1858,30 +1856,30 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B42">
         <v>1010</v>
       </c>
       <c r="C42">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="D42">
         <v>1</v>
       </c>
       <c r="E42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>40010</v>
+        <v>30020</v>
       </c>
       <c r="B43">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="C43">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -1892,52 +1890,52 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>40020</v>
+        <v>40010</v>
       </c>
       <c r="B44">
         <v>2020</v>
       </c>
       <c r="C44">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D44">
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>40030</v>
+        <v>40020</v>
       </c>
       <c r="B45">
         <v>2020</v>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
       <c r="E45" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46">
-        <v>50010</v>
+        <v>40030</v>
       </c>
       <c r="B46">
-        <v>1010</v>
+        <v>2020</v>
       </c>
       <c r="C46">
-        <v>1010</v>
+        <v>5</v>
       </c>
       <c r="D46">
-        <v>10</v>
-      </c>
-      <c r="E46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E46" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1949,13 +1947,13 @@
         <v>1010</v>
       </c>
       <c r="C47">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="D47">
         <v>10</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1966,13 +1964,13 @@
         <v>1010</v>
       </c>
       <c r="C48">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="D48">
         <v>10</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1983,13 +1981,13 @@
         <v>1010</v>
       </c>
       <c r="C49">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="D49">
         <v>10</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2000,13 +1998,13 @@
         <v>1010</v>
       </c>
       <c r="C50">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="D50">
         <v>10</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2017,30 +2015,30 @@
         <v>1010</v>
       </c>
       <c r="C51">
-        <v>4010</v>
+        <v>1050</v>
       </c>
       <c r="D51">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52">
-        <v>50020</v>
+        <v>50010</v>
       </c>
       <c r="B52">
         <v>1010</v>
       </c>
       <c r="C52">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="D52">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2051,13 +2049,13 @@
         <v>1010</v>
       </c>
       <c r="C53">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="D53">
         <v>10</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2068,13 +2066,13 @@
         <v>1010</v>
       </c>
       <c r="C54">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="D54">
         <v>10</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2085,13 +2083,13 @@
         <v>1010</v>
       </c>
       <c r="C55">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="D55">
         <v>10</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2102,13 +2100,13 @@
         <v>1010</v>
       </c>
       <c r="C56">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="D56">
         <v>10</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2119,13 +2117,13 @@
         <v>1010</v>
       </c>
       <c r="C57">
-        <v>4010</v>
+        <v>1050</v>
       </c>
       <c r="D57">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2133,33 +2131,33 @@
         <v>50020</v>
       </c>
       <c r="B58">
+        <v>1010</v>
+      </c>
+      <c r="C58">
         <v>4010</v>
       </c>
-      <c r="C58">
-        <v>20</v>
-      </c>
       <c r="D58">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B59">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C59">
-        <v>1110</v>
+        <v>20</v>
       </c>
       <c r="D59">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2170,13 +2168,13 @@
         <v>1010</v>
       </c>
       <c r="C60">
-        <v>1120</v>
+        <v>1110</v>
       </c>
       <c r="D60">
         <v>15</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2187,13 +2185,13 @@
         <v>1010</v>
       </c>
       <c r="C61">
-        <v>1130</v>
+        <v>1120</v>
       </c>
       <c r="D61">
         <v>15</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2204,13 +2202,13 @@
         <v>1010</v>
       </c>
       <c r="C62">
-        <v>1140</v>
+        <v>1130</v>
       </c>
       <c r="D62">
         <v>15</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2221,13 +2219,13 @@
         <v>1010</v>
       </c>
       <c r="C63">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="D63">
         <v>15</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2238,13 +2236,13 @@
         <v>1010</v>
       </c>
       <c r="C64">
-        <v>4010</v>
+        <v>1150</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2255,13 +2253,13 @@
         <v>1010</v>
       </c>
       <c r="C65">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D65">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2269,16 +2267,16 @@
         <v>50030</v>
       </c>
       <c r="B66">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C66">
-        <v>20</v>
+        <v>4020</v>
       </c>
       <c r="D66">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2286,16 +2284,16 @@
         <v>50030</v>
       </c>
       <c r="B67">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C67">
-        <v>5010</v>
+        <v>20</v>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2306,30 +2304,30 @@
         <v>1010</v>
       </c>
       <c r="C68">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="D68">
         <v>5</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B69">
         <v>1010</v>
       </c>
       <c r="C69">
-        <v>1110</v>
+        <v>5020</v>
       </c>
       <c r="D69">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2340,13 +2338,13 @@
         <v>1010</v>
       </c>
       <c r="C70">
-        <v>1120</v>
+        <v>1110</v>
       </c>
       <c r="D70">
         <v>15</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2357,13 +2355,13 @@
         <v>1010</v>
       </c>
       <c r="C71">
-        <v>1130</v>
+        <v>1120</v>
       </c>
       <c r="D71">
         <v>15</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2374,13 +2372,13 @@
         <v>1010</v>
       </c>
       <c r="C72">
-        <v>1140</v>
+        <v>1130</v>
       </c>
       <c r="D72">
         <v>15</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2391,13 +2389,13 @@
         <v>1010</v>
       </c>
       <c r="C73">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="D73">
         <v>15</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2408,13 +2406,13 @@
         <v>1010</v>
       </c>
       <c r="C74">
-        <v>4010</v>
+        <v>1150</v>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2425,13 +2423,13 @@
         <v>1010</v>
       </c>
       <c r="C75">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D75">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2448,7 +2446,7 @@
         <v>8</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2456,16 +2454,16 @@
         <v>50040</v>
       </c>
       <c r="B77">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C77">
-        <v>20</v>
+        <v>4020</v>
       </c>
       <c r="D77">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2473,16 +2471,16 @@
         <v>50040</v>
       </c>
       <c r="B78">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C78">
-        <v>5010</v>
+        <v>20</v>
       </c>
       <c r="D78">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2493,13 +2491,13 @@
         <v>1010</v>
       </c>
       <c r="C79">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="D79">
         <v>5</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2510,13 +2508,13 @@
         <v>1010</v>
       </c>
       <c r="C80">
-        <v>5040</v>
+        <v>5020</v>
       </c>
       <c r="D80">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2527,30 +2525,30 @@
         <v>1010</v>
       </c>
       <c r="C81">
-        <v>4310</v>
+        <v>5040</v>
       </c>
       <c r="D81">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B82">
         <v>1010</v>
       </c>
       <c r="C82">
-        <v>1110</v>
+        <v>4310</v>
       </c>
       <c r="D82">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2561,13 +2559,13 @@
         <v>1010</v>
       </c>
       <c r="C83">
-        <v>1120</v>
+        <v>1110</v>
       </c>
       <c r="D83">
         <v>15</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2578,13 +2576,13 @@
         <v>1010</v>
       </c>
       <c r="C84">
-        <v>1130</v>
+        <v>1120</v>
       </c>
       <c r="D84">
         <v>15</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2595,13 +2593,13 @@
         <v>1010</v>
       </c>
       <c r="C85">
-        <v>1140</v>
+        <v>1130</v>
       </c>
       <c r="D85">
         <v>15</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2612,13 +2610,13 @@
         <v>1010</v>
       </c>
       <c r="C86">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="D86">
         <v>15</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2629,13 +2627,13 @@
         <v>1010</v>
       </c>
       <c r="C87">
-        <v>4010</v>
+        <v>1150</v>
       </c>
       <c r="D87">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2646,13 +2644,13 @@
         <v>1010</v>
       </c>
       <c r="C88">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D88">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2669,7 +2667,7 @@
         <v>8</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2680,13 +2678,13 @@
         <v>1010</v>
       </c>
       <c r="C90">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D90">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2694,16 +2692,16 @@
         <v>50050</v>
       </c>
       <c r="B91">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C91">
-        <v>30</v>
+        <v>4030</v>
       </c>
       <c r="D91">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2714,13 +2712,13 @@
         <v>4010</v>
       </c>
       <c r="C92">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D92">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2728,16 +2726,16 @@
         <v>50050</v>
       </c>
       <c r="B93">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C93">
-        <v>4310</v>
+        <v>20</v>
       </c>
       <c r="D93">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2748,13 +2746,13 @@
         <v>1010</v>
       </c>
       <c r="C94">
-        <v>5010</v>
+        <v>4310</v>
       </c>
       <c r="D94">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2765,13 +2763,13 @@
         <v>1010</v>
       </c>
       <c r="C95">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="D95">
         <v>5</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2782,30 +2780,30 @@
         <v>1010</v>
       </c>
       <c r="C96">
-        <v>5040</v>
+        <v>5020</v>
       </c>
       <c r="D96">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B97">
         <v>1010</v>
       </c>
       <c r="C97">
-        <v>1110</v>
+        <v>5040</v>
       </c>
       <c r="D97">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2816,13 +2814,13 @@
         <v>1010</v>
       </c>
       <c r="C98">
-        <v>1120</v>
+        <v>1110</v>
       </c>
       <c r="D98">
         <v>15</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2833,13 +2831,13 @@
         <v>1010</v>
       </c>
       <c r="C99">
-        <v>1130</v>
+        <v>1120</v>
       </c>
       <c r="D99">
         <v>15</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2850,13 +2848,13 @@
         <v>1010</v>
       </c>
       <c r="C100">
-        <v>1140</v>
+        <v>1130</v>
       </c>
       <c r="D100">
         <v>15</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2867,13 +2865,13 @@
         <v>1010</v>
       </c>
       <c r="C101">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="D101">
         <v>15</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2884,13 +2882,13 @@
         <v>1010</v>
       </c>
       <c r="C102">
-        <v>4010</v>
+        <v>1150</v>
       </c>
       <c r="D102">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2901,13 +2899,13 @@
         <v>1010</v>
       </c>
       <c r="C103">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D103">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2924,7 +2922,7 @@
         <v>8</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2935,13 +2933,13 @@
         <v>1010</v>
       </c>
       <c r="C105">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D105">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2958,7 +2956,7 @@
         <v>12</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2966,16 +2964,16 @@
         <v>50060</v>
       </c>
       <c r="B107">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C107">
-        <v>30</v>
+        <v>4030</v>
       </c>
       <c r="D107">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2986,13 +2984,13 @@
         <v>4010</v>
       </c>
       <c r="C108">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D108">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -3000,16 +2998,16 @@
         <v>50060</v>
       </c>
       <c r="B109">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C109">
-        <v>4310</v>
+        <v>20</v>
       </c>
       <c r="D109">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -3020,13 +3018,13 @@
         <v>1010</v>
       </c>
       <c r="C110">
-        <v>5010</v>
+        <v>4310</v>
       </c>
       <c r="D110">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -3037,13 +3035,13 @@
         <v>1010</v>
       </c>
       <c r="C111">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="D111">
         <v>5</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -3054,13 +3052,30 @@
         <v>1010</v>
       </c>
       <c r="C112">
+        <v>5020</v>
+      </c>
+      <c r="D112">
+        <v>5</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113">
+        <v>50060</v>
+      </c>
+      <c r="B113">
+        <v>1010</v>
+      </c>
+      <c r="C113">
         <v>5040</v>
       </c>
-      <c r="D112">
+      <c r="D113">
         <v>10</v>
       </c>
-      <c r="E112" s="1" t="s">
-        <v>35</v>
+      <c r="E113" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -3073,12 +3088,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3086,7 +3101,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3094,7 +3109,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3102,7 +3117,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3110,7 +3125,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3126,7 +3141,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3134,7 +3149,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3142,111 +3157,95 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>62</v>
-      </c>
-      <c r="B11" t="s">
-        <v>45</v>
+        <v>100</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>71</v>
+        <v>210</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>100</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>48</v>
+        <v>1010</v>
+      </c>
+      <c r="B14" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>101</v>
+        <v>2010</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>210</v>
+        <v>2020</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>1010</v>
+        <v>2030</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>2010</v>
+        <v>2040</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>2020</v>
+        <v>4010</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>2030</v>
+        <v>4020</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21">
-        <v>4010</v>
-      </c>
-      <c r="B21" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22">
-        <v>4020</v>
-      </c>
-      <c r="B22" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="56">
   <si>
     <t>Id</t>
   </si>
@@ -190,9 +190,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -211,15 +211,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,31 +234,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -269,38 +248,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -316,9 +263,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,10 +286,34 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -348,10 +326,32 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -364,7 +364,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -376,13 +502,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -394,84 +520,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -484,43 +532,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -532,19 +544,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -562,7 +562,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -584,20 +584,35 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -617,17 +632,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -646,15 +655,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -663,145 +663,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1131,7 +1131,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F113"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -1947,10 +1947,10 @@
         <v>1010</v>
       </c>
       <c r="C47">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="D47">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>36</v>
@@ -1964,10 +1964,10 @@
         <v>1010</v>
       </c>
       <c r="C48">
-        <v>1020</v>
+        <v>5050</v>
       </c>
       <c r="D48">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>36</v>
@@ -1975,16 +1975,16 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49">
-        <v>50010</v>
+        <v>50020</v>
       </c>
       <c r="B49">
         <v>1010</v>
       </c>
       <c r="C49">
-        <v>1030</v>
+        <v>4010</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>36</v>
@@ -1992,16 +1992,16 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50">
-        <v>50010</v>
+        <v>50020</v>
       </c>
       <c r="B50">
         <v>1010</v>
       </c>
       <c r="C50">
-        <v>1040</v>
+        <v>5050</v>
       </c>
       <c r="D50">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>36</v>
@@ -2009,16 +2009,16 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51">
-        <v>50010</v>
+        <v>50020</v>
       </c>
       <c r="B51">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C51">
-        <v>1050</v>
+        <v>20</v>
       </c>
       <c r="D51">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>36</v>
@@ -2026,16 +2026,16 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52">
-        <v>50010</v>
+        <v>50030</v>
       </c>
       <c r="B52">
         <v>1010</v>
       </c>
       <c r="C52">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>36</v>
@@ -2043,16 +2043,16 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53">
-        <v>50020</v>
+        <v>50030</v>
       </c>
       <c r="B53">
         <v>1010</v>
       </c>
       <c r="C53">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="D53">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>36</v>
@@ -2060,16 +2060,16 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>50020</v>
+        <v>50030</v>
       </c>
       <c r="B54">
         <v>1010</v>
       </c>
       <c r="C54">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="D54">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>36</v>
@@ -2077,16 +2077,16 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>50020</v>
+        <v>50030</v>
       </c>
       <c r="B55">
         <v>1010</v>
       </c>
       <c r="C55">
-        <v>1030</v>
+        <v>1040</v>
       </c>
       <c r="D55">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>36</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56">
-        <v>50020</v>
+        <v>50030</v>
       </c>
       <c r="B56">
         <v>1010</v>
       </c>
       <c r="C56">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="D56">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>36</v>
@@ -2111,16 +2111,16 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57">
-        <v>50020</v>
+        <v>50030</v>
       </c>
       <c r="B57">
         <v>1010</v>
       </c>
       <c r="C57">
-        <v>1050</v>
+        <v>4010</v>
       </c>
       <c r="D57">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>36</v>
@@ -2128,16 +2128,16 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58">
-        <v>50020</v>
+        <v>50030</v>
       </c>
       <c r="B58">
         <v>1010</v>
       </c>
       <c r="C58">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>36</v>
@@ -2145,7 +2145,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>50020</v>
+        <v>50030</v>
       </c>
       <c r="B59">
         <v>4010</v>
@@ -2168,10 +2168,10 @@
         <v>1010</v>
       </c>
       <c r="C60">
-        <v>1110</v>
+        <v>5010</v>
       </c>
       <c r="D60">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>36</v>
@@ -2185,10 +2185,10 @@
         <v>1010</v>
       </c>
       <c r="C61">
-        <v>1120</v>
+        <v>5020</v>
       </c>
       <c r="D61">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>36</v>
@@ -2196,13 +2196,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62">
-        <v>50030</v>
+        <v>50040</v>
       </c>
       <c r="B62">
         <v>1010</v>
       </c>
       <c r="C62">
-        <v>1130</v>
+        <v>1110</v>
       </c>
       <c r="D62">
         <v>15</v>
@@ -2213,13 +2213,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>50030</v>
+        <v>50040</v>
       </c>
       <c r="B63">
         <v>1010</v>
       </c>
       <c r="C63">
-        <v>1140</v>
+        <v>1120</v>
       </c>
       <c r="D63">
         <v>15</v>
@@ -2230,13 +2230,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>50030</v>
+        <v>50040</v>
       </c>
       <c r="B64">
         <v>1010</v>
       </c>
       <c r="C64">
-        <v>1150</v>
+        <v>1130</v>
       </c>
       <c r="D64">
         <v>15</v>
@@ -2247,16 +2247,16 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>50030</v>
+        <v>50040</v>
       </c>
       <c r="B65">
         <v>1010</v>
       </c>
       <c r="C65">
-        <v>4010</v>
+        <v>1140</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>36</v>
@@ -2264,16 +2264,16 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>50030</v>
+        <v>50040</v>
       </c>
       <c r="B66">
         <v>1010</v>
       </c>
       <c r="C66">
-        <v>4020</v>
+        <v>1150</v>
       </c>
       <c r="D66">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>36</v>
@@ -2281,16 +2281,16 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>50030</v>
+        <v>50040</v>
       </c>
       <c r="B67">
+        <v>1010</v>
+      </c>
+      <c r="C67">
         <v>4010</v>
       </c>
-      <c r="C67">
-        <v>20</v>
-      </c>
       <c r="D67">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>36</v>
@@ -2298,16 +2298,16 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>50030</v>
+        <v>50040</v>
       </c>
       <c r="B68">
         <v>1010</v>
       </c>
       <c r="C68">
-        <v>5010</v>
+        <v>4020</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>36</v>
@@ -2315,16 +2315,16 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>50030</v>
+        <v>50040</v>
       </c>
       <c r="B69">
         <v>1010</v>
       </c>
       <c r="C69">
-        <v>5020</v>
+        <v>4020</v>
       </c>
       <c r="D69">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>36</v>
@@ -2335,13 +2335,13 @@
         <v>50040</v>
       </c>
       <c r="B70">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C70">
-        <v>1110</v>
+        <v>20</v>
       </c>
       <c r="D70">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>36</v>
@@ -2355,10 +2355,10 @@
         <v>1010</v>
       </c>
       <c r="C71">
-        <v>1120</v>
+        <v>5010</v>
       </c>
       <c r="D71">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>36</v>
@@ -2372,10 +2372,10 @@
         <v>1010</v>
       </c>
       <c r="C72">
-        <v>1130</v>
+        <v>5020</v>
       </c>
       <c r="D72">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>36</v>
@@ -2389,10 +2389,10 @@
         <v>1010</v>
       </c>
       <c r="C73">
-        <v>1140</v>
+        <v>5040</v>
       </c>
       <c r="D73">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>36</v>
@@ -2406,10 +2406,10 @@
         <v>1010</v>
       </c>
       <c r="C74">
-        <v>1150</v>
+        <v>4310</v>
       </c>
       <c r="D74">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>36</v>
@@ -2417,16 +2417,16 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75">
-        <v>50040</v>
+        <v>50050</v>
       </c>
       <c r="B75">
         <v>1010</v>
       </c>
       <c r="C75">
-        <v>4010</v>
+        <v>1110</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>36</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76">
-        <v>50040</v>
+        <v>50050</v>
       </c>
       <c r="B76">
         <v>1010</v>
       </c>
       <c r="C76">
-        <v>4020</v>
+        <v>1120</v>
       </c>
       <c r="D76">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>36</v>
@@ -2451,16 +2451,16 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77">
-        <v>50040</v>
+        <v>50050</v>
       </c>
       <c r="B77">
         <v>1010</v>
       </c>
       <c r="C77">
-        <v>4020</v>
+        <v>1130</v>
       </c>
       <c r="D77">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>36</v>
@@ -2468,16 +2468,16 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78">
-        <v>50040</v>
+        <v>50050</v>
       </c>
       <c r="B78">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C78">
-        <v>20</v>
+        <v>1140</v>
       </c>
       <c r="D78">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>36</v>
@@ -2485,16 +2485,16 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79">
-        <v>50040</v>
+        <v>50050</v>
       </c>
       <c r="B79">
         <v>1010</v>
       </c>
       <c r="C79">
-        <v>5010</v>
+        <v>1150</v>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>36</v>
@@ -2502,16 +2502,16 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80">
-        <v>50040</v>
+        <v>50050</v>
       </c>
       <c r="B80">
         <v>1010</v>
       </c>
       <c r="C80">
-        <v>5020</v>
+        <v>4010</v>
       </c>
       <c r="D80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>36</v>
@@ -2519,16 +2519,16 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81">
-        <v>50040</v>
+        <v>50050</v>
       </c>
       <c r="B81">
         <v>1010</v>
       </c>
       <c r="C81">
-        <v>5040</v>
+        <v>4020</v>
       </c>
       <c r="D81">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>36</v>
@@ -2536,16 +2536,16 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82">
-        <v>50040</v>
+        <v>50050</v>
       </c>
       <c r="B82">
         <v>1010</v>
       </c>
       <c r="C82">
-        <v>4310</v>
+        <v>4020</v>
       </c>
       <c r="D82">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>36</v>
@@ -2559,10 +2559,10 @@
         <v>1010</v>
       </c>
       <c r="C83">
-        <v>1110</v>
+        <v>4030</v>
       </c>
       <c r="D83">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>36</v>
@@ -2573,13 +2573,13 @@
         <v>50050</v>
       </c>
       <c r="B84">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C84">
-        <v>1120</v>
+        <v>30</v>
       </c>
       <c r="D84">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>36</v>
@@ -2590,13 +2590,13 @@
         <v>50050</v>
       </c>
       <c r="B85">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C85">
-        <v>1130</v>
+        <v>20</v>
       </c>
       <c r="D85">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>36</v>
@@ -2610,10 +2610,10 @@
         <v>1010</v>
       </c>
       <c r="C86">
-        <v>1140</v>
+        <v>4310</v>
       </c>
       <c r="D86">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>36</v>
@@ -2627,10 +2627,10 @@
         <v>1010</v>
       </c>
       <c r="C87">
-        <v>1150</v>
+        <v>5010</v>
       </c>
       <c r="D87">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>36</v>
@@ -2644,10 +2644,10 @@
         <v>1010</v>
       </c>
       <c r="C88">
-        <v>4010</v>
+        <v>5020</v>
       </c>
       <c r="D88">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>36</v>
@@ -2661,10 +2661,10 @@
         <v>1010</v>
       </c>
       <c r="C89">
-        <v>4020</v>
+        <v>5040</v>
       </c>
       <c r="D89">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>36</v>
@@ -2672,16 +2672,16 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>50050</v>
+        <v>50060</v>
       </c>
       <c r="B90">
         <v>1010</v>
       </c>
       <c r="C90">
-        <v>4020</v>
+        <v>1110</v>
       </c>
       <c r="D90">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>36</v>
@@ -2689,16 +2689,16 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>50050</v>
+        <v>50060</v>
       </c>
       <c r="B91">
         <v>1010</v>
       </c>
       <c r="C91">
-        <v>4030</v>
+        <v>1120</v>
       </c>
       <c r="D91">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>36</v>
@@ -2706,16 +2706,16 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>50050</v>
+        <v>50060</v>
       </c>
       <c r="B92">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C92">
-        <v>30</v>
+        <v>1130</v>
       </c>
       <c r="D92">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>36</v>
@@ -2723,16 +2723,16 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>50050</v>
+        <v>50060</v>
       </c>
       <c r="B93">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C93">
-        <v>20</v>
+        <v>1140</v>
       </c>
       <c r="D93">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>36</v>
@@ -2740,16 +2740,16 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94">
-        <v>50050</v>
+        <v>50060</v>
       </c>
       <c r="B94">
         <v>1010</v>
       </c>
       <c r="C94">
-        <v>4310</v>
+        <v>1150</v>
       </c>
       <c r="D94">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>36</v>
@@ -2757,16 +2757,16 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95">
-        <v>50050</v>
+        <v>50060</v>
       </c>
       <c r="B95">
         <v>1010</v>
       </c>
       <c r="C95">
-        <v>5010</v>
+        <v>4010</v>
       </c>
       <c r="D95">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>36</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96">
-        <v>50050</v>
+        <v>50060</v>
       </c>
       <c r="B96">
         <v>1010</v>
       </c>
       <c r="C96">
-        <v>5020</v>
+        <v>4020</v>
       </c>
       <c r="D96">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>36</v>
@@ -2791,16 +2791,16 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
-        <v>50050</v>
+        <v>50060</v>
       </c>
       <c r="B97">
         <v>1010</v>
       </c>
       <c r="C97">
-        <v>5040</v>
+        <v>4020</v>
       </c>
       <c r="D97">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>36</v>
@@ -2814,10 +2814,10 @@
         <v>1010</v>
       </c>
       <c r="C98">
-        <v>1110</v>
+        <v>4030</v>
       </c>
       <c r="D98">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>36</v>
@@ -2831,10 +2831,10 @@
         <v>1010</v>
       </c>
       <c r="C99">
-        <v>1120</v>
+        <v>4030</v>
       </c>
       <c r="D99">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>36</v>
@@ -2845,13 +2845,13 @@
         <v>50060</v>
       </c>
       <c r="B100">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C100">
-        <v>1130</v>
+        <v>30</v>
       </c>
       <c r="D100">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>36</v>
@@ -2862,13 +2862,13 @@
         <v>50060</v>
       </c>
       <c r="B101">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C101">
-        <v>1140</v>
+        <v>20</v>
       </c>
       <c r="D101">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>36</v>
@@ -2882,10 +2882,10 @@
         <v>1010</v>
       </c>
       <c r="C102">
-        <v>1150</v>
+        <v>4310</v>
       </c>
       <c r="D102">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>36</v>
@@ -2899,10 +2899,10 @@
         <v>1010</v>
       </c>
       <c r="C103">
-        <v>4010</v>
+        <v>5010</v>
       </c>
       <c r="D103">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>36</v>
@@ -2916,10 +2916,10 @@
         <v>1010</v>
       </c>
       <c r="C104">
-        <v>4020</v>
+        <v>5020</v>
       </c>
       <c r="D104">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>36</v>
@@ -2933,148 +2933,12 @@
         <v>1010</v>
       </c>
       <c r="C105">
-        <v>4020</v>
+        <v>5040</v>
       </c>
       <c r="D105">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
-      <c r="A106">
-        <v>50060</v>
-      </c>
-      <c r="B106">
-        <v>1010</v>
-      </c>
-      <c r="C106">
-        <v>4030</v>
-      </c>
-      <c r="D106">
-        <v>12</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
-      <c r="A107">
-        <v>50060</v>
-      </c>
-      <c r="B107">
-        <v>1010</v>
-      </c>
-      <c r="C107">
-        <v>4030</v>
-      </c>
-      <c r="D107">
-        <v>12</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
-      <c r="A108">
-        <v>50060</v>
-      </c>
-      <c r="B108">
-        <v>4010</v>
-      </c>
-      <c r="C108">
-        <v>30</v>
-      </c>
-      <c r="D108">
-        <v>10</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
-      <c r="A109">
-        <v>50060</v>
-      </c>
-      <c r="B109">
-        <v>4010</v>
-      </c>
-      <c r="C109">
-        <v>20</v>
-      </c>
-      <c r="D109">
-        <v>20</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
-      <c r="A110">
-        <v>50060</v>
-      </c>
-      <c r="B110">
-        <v>1010</v>
-      </c>
-      <c r="C110">
-        <v>4310</v>
-      </c>
-      <c r="D110">
-        <v>30</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
-      <c r="A111">
-        <v>50060</v>
-      </c>
-      <c r="B111">
-        <v>1010</v>
-      </c>
-      <c r="C111">
-        <v>5010</v>
-      </c>
-      <c r="D111">
-        <v>5</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
-      <c r="A112">
-        <v>50060</v>
-      </c>
-      <c r="B112">
-        <v>1010</v>
-      </c>
-      <c r="C112">
-        <v>5020</v>
-      </c>
-      <c r="D112">
-        <v>5</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
-      <c r="A113">
-        <v>50060</v>
-      </c>
-      <c r="B113">
-        <v>1010</v>
-      </c>
-      <c r="C113">
-        <v>5040</v>
-      </c>
-      <c r="D113">
-        <v>10</v>
-      </c>
-      <c r="E113" s="1" t="s">
         <v>36</v>
       </c>
     </row>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="57">
   <si>
     <t>Id</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>隠遁のヴェール</t>
+  </si>
+  <si>
+    <t>ポーション</t>
   </si>
   <si>
     <t>Rankアップ</t>
@@ -213,6 +216,104 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -228,51 +329,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,42 +343,10 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -332,28 +357,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -361,6 +364,66 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -370,7 +433,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -382,43 +475,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -430,25 +493,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -460,91 +535,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -560,24 +563,35 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,37 +620,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -655,6 +649,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -663,7 +666,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -672,7 +675,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -681,127 +684,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1131,7 +1134,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -1839,16 +1842,16 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>20010</v>
+        <v>15050</v>
       </c>
       <c r="B41">
-        <v>2010</v>
+        <v>1010</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>5050</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" t="s">
         <v>33</v>
@@ -1856,16 +1859,16 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>30010</v>
+        <v>20010</v>
       </c>
       <c r="B42">
-        <v>1010</v>
+        <v>2010</v>
       </c>
       <c r="C42">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" t="s">
         <v>34</v>
@@ -1873,30 +1876,30 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B43">
         <v>1010</v>
       </c>
       <c r="C43">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="D43">
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>40010</v>
+        <v>30020</v>
       </c>
       <c r="B44">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="C44">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -1907,52 +1910,52 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>40020</v>
+        <v>40010</v>
       </c>
       <c r="B45">
         <v>2020</v>
       </c>
       <c r="C45">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
       <c r="E45" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46">
-        <v>40030</v>
+        <v>40020</v>
       </c>
       <c r="B46">
         <v>2020</v>
       </c>
       <c r="C46">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D46">
         <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47">
-        <v>50010</v>
+        <v>40030</v>
       </c>
       <c r="B47">
-        <v>1010</v>
+        <v>2020</v>
       </c>
       <c r="C47">
-        <v>4010</v>
+        <v>5</v>
       </c>
       <c r="D47">
-        <v>4</v>
-      </c>
-      <c r="E47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E47" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1964,30 +1967,30 @@
         <v>1010</v>
       </c>
       <c r="C48">
-        <v>5050</v>
+        <v>4010</v>
       </c>
       <c r="D48">
         <v>4</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49">
-        <v>50020</v>
+        <v>50010</v>
       </c>
       <c r="B49">
         <v>1010</v>
       </c>
       <c r="C49">
-        <v>4010</v>
+        <v>5050</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1998,13 +2001,13 @@
         <v>1010</v>
       </c>
       <c r="C50">
-        <v>5050</v>
+        <v>4010</v>
       </c>
       <c r="D50">
         <v>4</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2012,50 +2015,50 @@
         <v>50020</v>
       </c>
       <c r="B51">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C51">
-        <v>20</v>
+        <v>4020</v>
       </c>
       <c r="D51">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B52">
         <v>1010</v>
       </c>
       <c r="C52">
-        <v>1010</v>
+        <v>5050</v>
       </c>
       <c r="D52">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B53">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C53">
-        <v>1020</v>
+        <v>20</v>
       </c>
       <c r="D53">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2066,13 +2069,13 @@
         <v>1010</v>
       </c>
       <c r="C54">
-        <v>1030</v>
+        <v>4010</v>
       </c>
       <c r="D54">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2083,13 +2086,13 @@
         <v>1010</v>
       </c>
       <c r="C55">
-        <v>1040</v>
+        <v>4020</v>
       </c>
       <c r="D55">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2100,13 +2103,13 @@
         <v>1010</v>
       </c>
       <c r="C56">
-        <v>1050</v>
+        <v>5050</v>
       </c>
       <c r="D56">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2117,13 +2120,13 @@
         <v>1010</v>
       </c>
       <c r="C57">
-        <v>4010</v>
+        <v>5060</v>
       </c>
       <c r="D57">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2131,16 +2134,16 @@
         <v>50030</v>
       </c>
       <c r="B58">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C58">
-        <v>4020</v>
+        <v>20</v>
       </c>
       <c r="D58">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2148,16 +2151,16 @@
         <v>50030</v>
       </c>
       <c r="B59">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C59">
-        <v>20</v>
+        <v>1010</v>
       </c>
       <c r="D59">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2168,13 +2171,13 @@
         <v>1010</v>
       </c>
       <c r="C60">
-        <v>5010</v>
+        <v>1020</v>
       </c>
       <c r="D60">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2185,47 +2188,47 @@
         <v>1010</v>
       </c>
       <c r="C61">
-        <v>5020</v>
+        <v>1030</v>
       </c>
       <c r="D61">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B62">
         <v>1010</v>
       </c>
       <c r="C62">
-        <v>1110</v>
+        <v>1040</v>
       </c>
       <c r="D62">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B63">
         <v>1010</v>
       </c>
       <c r="C63">
-        <v>1120</v>
+        <v>1050</v>
       </c>
       <c r="D63">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2236,13 +2239,13 @@
         <v>1010</v>
       </c>
       <c r="C64">
-        <v>1130</v>
+        <v>4010</v>
       </c>
       <c r="D64">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2253,13 +2256,13 @@
         <v>1010</v>
       </c>
       <c r="C65">
-        <v>1140</v>
+        <v>4020</v>
       </c>
       <c r="D65">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2270,13 +2273,13 @@
         <v>1010</v>
       </c>
       <c r="C66">
-        <v>1150</v>
+        <v>5050</v>
       </c>
       <c r="D66">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2287,13 +2290,13 @@
         <v>1010</v>
       </c>
       <c r="C67">
-        <v>4010</v>
+        <v>5060</v>
       </c>
       <c r="D67">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2301,16 +2304,16 @@
         <v>50040</v>
       </c>
       <c r="B68">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C68">
-        <v>4020</v>
+        <v>20</v>
       </c>
       <c r="D68">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2321,13 +2324,13 @@
         <v>1010</v>
       </c>
       <c r="C69">
-        <v>4020</v>
+        <v>4310</v>
       </c>
       <c r="D69">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2335,16 +2338,16 @@
         <v>50040</v>
       </c>
       <c r="B70">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C70">
-        <v>20</v>
+        <v>1010</v>
       </c>
       <c r="D70">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2355,13 +2358,13 @@
         <v>1010</v>
       </c>
       <c r="C71">
-        <v>5010</v>
+        <v>1020</v>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2372,13 +2375,13 @@
         <v>1010</v>
       </c>
       <c r="C72">
-        <v>5020</v>
+        <v>1030</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2389,13 +2392,13 @@
         <v>1010</v>
       </c>
       <c r="C73">
-        <v>5040</v>
+        <v>1040</v>
       </c>
       <c r="D73">
         <v>10</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2406,13 +2409,13 @@
         <v>1010</v>
       </c>
       <c r="C74">
-        <v>4310</v>
+        <v>1050</v>
       </c>
       <c r="D74">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2429,7 +2432,7 @@
         <v>15</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2446,7 +2449,7 @@
         <v>15</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2463,7 +2466,7 @@
         <v>15</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2480,7 +2483,7 @@
         <v>15</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2497,7 +2500,7 @@
         <v>15</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2514,7 +2517,7 @@
         <v>4</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2531,7 +2534,7 @@
         <v>8</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2548,7 +2551,7 @@
         <v>8</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2565,7 +2568,7 @@
         <v>12</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2582,7 +2585,7 @@
         <v>10</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2599,7 +2602,7 @@
         <v>20</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2616,7 +2619,7 @@
         <v>30</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2633,7 +2636,7 @@
         <v>5</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2650,24 +2653,24 @@
         <v>5</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89">
-        <v>50050</v>
+        <v>50060</v>
       </c>
       <c r="B89">
         <v>1010</v>
       </c>
       <c r="C89">
-        <v>5040</v>
+        <v>1110</v>
       </c>
       <c r="D89">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2678,13 +2681,13 @@
         <v>1010</v>
       </c>
       <c r="C90">
-        <v>1110</v>
+        <v>1120</v>
       </c>
       <c r="D90">
         <v>15</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2695,13 +2698,13 @@
         <v>1010</v>
       </c>
       <c r="C91">
-        <v>1120</v>
+        <v>1130</v>
       </c>
       <c r="D91">
         <v>15</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2712,13 +2715,13 @@
         <v>1010</v>
       </c>
       <c r="C92">
-        <v>1130</v>
+        <v>1140</v>
       </c>
       <c r="D92">
         <v>15</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2729,13 +2732,13 @@
         <v>1010</v>
       </c>
       <c r="C93">
-        <v>1140</v>
+        <v>1150</v>
       </c>
       <c r="D93">
         <v>15</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2746,13 +2749,13 @@
         <v>1010</v>
       </c>
       <c r="C94">
-        <v>1150</v>
+        <v>4010</v>
       </c>
       <c r="D94">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2763,13 +2766,13 @@
         <v>1010</v>
       </c>
       <c r="C95">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="D95">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2786,7 +2789,7 @@
         <v>8</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2797,13 +2800,13 @@
         <v>1010</v>
       </c>
       <c r="C97">
-        <v>4020</v>
+        <v>4030</v>
       </c>
       <c r="D97">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2820,7 +2823,7 @@
         <v>12</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2828,16 +2831,16 @@
         <v>50060</v>
       </c>
       <c r="B99">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C99">
-        <v>4030</v>
+        <v>30</v>
       </c>
       <c r="D99">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2848,13 +2851,13 @@
         <v>4010</v>
       </c>
       <c r="C100">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D100">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2862,16 +2865,16 @@
         <v>50060</v>
       </c>
       <c r="B101">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C101">
-        <v>20</v>
+        <v>4310</v>
       </c>
       <c r="D101">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2882,13 +2885,13 @@
         <v>1010</v>
       </c>
       <c r="C102">
-        <v>4310</v>
+        <v>5010</v>
       </c>
       <c r="D102">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2899,47 +2902,13 @@
         <v>1010</v>
       </c>
       <c r="C103">
-        <v>5010</v>
+        <v>5020</v>
       </c>
       <c r="D103">
         <v>5</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
-      <c r="A104">
-        <v>50060</v>
-      </c>
-      <c r="B104">
-        <v>1010</v>
-      </c>
-      <c r="C104">
-        <v>5020</v>
-      </c>
-      <c r="D104">
-        <v>5</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="A105">
-        <v>50060</v>
-      </c>
-      <c r="B105">
-        <v>1010</v>
-      </c>
-      <c r="C105">
-        <v>5040</v>
-      </c>
-      <c r="D105">
-        <v>10</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2957,7 +2926,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2965,7 +2934,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2973,7 +2942,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2981,7 +2950,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2989,7 +2958,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3005,7 +2974,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3013,7 +2982,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3021,7 +2990,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3029,7 +2998,7 @@
         <v>71</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3037,7 +3006,7 @@
         <v>100</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3045,7 +3014,7 @@
         <v>101</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3053,7 +3022,7 @@
         <v>210</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3061,7 +3030,7 @@
         <v>1010</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3069,7 +3038,7 @@
         <v>2010</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3077,7 +3046,7 @@
         <v>2020</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3085,7 +3054,7 @@
         <v>2030</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3093,7 +3062,7 @@
         <v>2040</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3101,7 +3070,7 @@
         <v>4010</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3109,7 +3078,7 @@
         <v>4020</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="58">
   <si>
     <t>Id</t>
   </si>
@@ -117,6 +117,9 @@
   </si>
   <si>
     <t>ポーション</t>
+  </si>
+  <si>
+    <t>ハイポーション</t>
   </si>
   <si>
     <t>Rankアップ</t>
@@ -193,10 +196,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -214,7 +217,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -222,17 +224,38 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -254,21 +277,45 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -283,29 +330,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -320,28 +345,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -352,7 +355,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -367,7 +370,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -379,55 +526,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -439,115 +550,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -558,26 +561,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -592,6 +575,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -620,17 +618,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -658,6 +650,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -666,145 +669,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1134,7 +1137,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -1859,16 +1862,16 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>20010</v>
+        <v>15060</v>
       </c>
       <c r="B42">
-        <v>2010</v>
+        <v>1010</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>5060</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="s">
         <v>34</v>
@@ -1876,16 +1879,16 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>30010</v>
+        <v>20010</v>
       </c>
       <c r="B43">
-        <v>1010</v>
+        <v>2010</v>
       </c>
       <c r="C43">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="s">
         <v>35</v>
@@ -1893,30 +1896,30 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B44">
         <v>1010</v>
       </c>
       <c r="C44">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="D44">
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>40010</v>
+        <v>30020</v>
       </c>
       <c r="B45">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="C45">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -1927,52 +1930,52 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46">
-        <v>40020</v>
+        <v>40010</v>
       </c>
       <c r="B46">
         <v>2020</v>
       </c>
       <c r="C46">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D46">
         <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47">
-        <v>40030</v>
+        <v>40020</v>
       </c>
       <c r="B47">
         <v>2020</v>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D47">
         <v>1</v>
       </c>
       <c r="E47" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48">
-        <v>50010</v>
+        <v>40030</v>
       </c>
       <c r="B48">
-        <v>1010</v>
+        <v>2020</v>
       </c>
       <c r="C48">
-        <v>4010</v>
+        <v>5</v>
       </c>
       <c r="D48">
-        <v>4</v>
-      </c>
-      <c r="E48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E48" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1984,30 +1987,30 @@
         <v>1010</v>
       </c>
       <c r="C49">
-        <v>5050</v>
+        <v>4010</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50">
-        <v>50020</v>
+        <v>50010</v>
       </c>
       <c r="B50">
         <v>1010</v>
       </c>
       <c r="C50">
-        <v>4010</v>
+        <v>5050</v>
       </c>
       <c r="D50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2018,13 +2021,13 @@
         <v>1010</v>
       </c>
       <c r="C51">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D51">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2035,13 +2038,13 @@
         <v>1010</v>
       </c>
       <c r="C52">
-        <v>5050</v>
+        <v>4020</v>
       </c>
       <c r="D52">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2049,33 +2052,33 @@
         <v>50020</v>
       </c>
       <c r="B53">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C53">
-        <v>20</v>
+        <v>5050</v>
       </c>
       <c r="D53">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B54">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C54">
-        <v>4010</v>
+        <v>20</v>
       </c>
       <c r="D54">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2086,13 +2089,13 @@
         <v>1010</v>
       </c>
       <c r="C55">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D55">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2103,13 +2106,13 @@
         <v>1010</v>
       </c>
       <c r="C56">
-        <v>5050</v>
+        <v>4020</v>
       </c>
       <c r="D56">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2120,13 +2123,13 @@
         <v>1010</v>
       </c>
       <c r="C57">
-        <v>5060</v>
+        <v>5050</v>
       </c>
       <c r="D57">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2134,16 +2137,16 @@
         <v>50030</v>
       </c>
       <c r="B58">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C58">
-        <v>20</v>
+        <v>5060</v>
       </c>
       <c r="D58">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2151,16 +2154,16 @@
         <v>50030</v>
       </c>
       <c r="B59">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C59">
-        <v>1010</v>
+        <v>20</v>
       </c>
       <c r="D59">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2171,13 +2174,13 @@
         <v>1010</v>
       </c>
       <c r="C60">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="D60">
         <v>10</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2188,13 +2191,13 @@
         <v>1010</v>
       </c>
       <c r="C61">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="D61">
         <v>10</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2205,13 +2208,13 @@
         <v>1010</v>
       </c>
       <c r="C62">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="D62">
         <v>10</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2222,30 +2225,30 @@
         <v>1010</v>
       </c>
       <c r="C63">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="D63">
         <v>10</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B64">
         <v>1010</v>
       </c>
       <c r="C64">
-        <v>4010</v>
+        <v>1050</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2256,13 +2259,13 @@
         <v>1010</v>
       </c>
       <c r="C65">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D65">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2273,13 +2276,13 @@
         <v>1010</v>
       </c>
       <c r="C66">
-        <v>5050</v>
+        <v>4020</v>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2290,13 +2293,13 @@
         <v>1010</v>
       </c>
       <c r="C67">
-        <v>5060</v>
+        <v>5050</v>
       </c>
       <c r="D67">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2304,16 +2307,16 @@
         <v>50040</v>
       </c>
       <c r="B68">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C68">
-        <v>20</v>
+        <v>5060</v>
       </c>
       <c r="D68">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2321,16 +2324,16 @@
         <v>50040</v>
       </c>
       <c r="B69">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C69">
-        <v>4310</v>
+        <v>20</v>
       </c>
       <c r="D69">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2341,13 +2344,13 @@
         <v>1010</v>
       </c>
       <c r="C70">
-        <v>1010</v>
+        <v>4310</v>
       </c>
       <c r="D70">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2358,13 +2361,13 @@
         <v>1010</v>
       </c>
       <c r="C71">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="D71">
         <v>10</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2375,13 +2378,13 @@
         <v>1010</v>
       </c>
       <c r="C72">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="D72">
         <v>10</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2392,13 +2395,13 @@
         <v>1010</v>
       </c>
       <c r="C73">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="D73">
         <v>10</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2409,30 +2412,30 @@
         <v>1010</v>
       </c>
       <c r="C74">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="D74">
         <v>10</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B75">
         <v>1010</v>
       </c>
       <c r="C75">
-        <v>1110</v>
+        <v>1050</v>
       </c>
       <c r="D75">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2443,13 +2446,13 @@
         <v>1010</v>
       </c>
       <c r="C76">
-        <v>1120</v>
+        <v>1110</v>
       </c>
       <c r="D76">
         <v>15</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2460,13 +2463,13 @@
         <v>1010</v>
       </c>
       <c r="C77">
-        <v>1130</v>
+        <v>1120</v>
       </c>
       <c r="D77">
         <v>15</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2477,13 +2480,13 @@
         <v>1010</v>
       </c>
       <c r="C78">
-        <v>1140</v>
+        <v>1130</v>
       </c>
       <c r="D78">
         <v>15</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2494,13 +2497,13 @@
         <v>1010</v>
       </c>
       <c r="C79">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="D79">
         <v>15</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2511,13 +2514,13 @@
         <v>1010</v>
       </c>
       <c r="C80">
-        <v>4010</v>
+        <v>1150</v>
       </c>
       <c r="D80">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2528,13 +2531,13 @@
         <v>1010</v>
       </c>
       <c r="C81">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D81">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2551,7 +2554,7 @@
         <v>8</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2562,13 +2565,13 @@
         <v>1010</v>
       </c>
       <c r="C83">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D83">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2576,16 +2579,16 @@
         <v>50050</v>
       </c>
       <c r="B84">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C84">
-        <v>30</v>
+        <v>4030</v>
       </c>
       <c r="D84">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2596,13 +2599,13 @@
         <v>4010</v>
       </c>
       <c r="C85">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D85">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2610,16 +2613,16 @@
         <v>50050</v>
       </c>
       <c r="B86">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C86">
-        <v>4310</v>
+        <v>20</v>
       </c>
       <c r="D86">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2630,13 +2633,13 @@
         <v>1010</v>
       </c>
       <c r="C87">
-        <v>5010</v>
+        <v>4310</v>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2647,30 +2650,30 @@
         <v>1010</v>
       </c>
       <c r="C88">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="D88">
         <v>5</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B89">
         <v>1010</v>
       </c>
       <c r="C89">
-        <v>1110</v>
+        <v>5020</v>
       </c>
       <c r="D89">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2681,13 +2684,13 @@
         <v>1010</v>
       </c>
       <c r="C90">
-        <v>1120</v>
+        <v>1110</v>
       </c>
       <c r="D90">
         <v>15</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2698,13 +2701,13 @@
         <v>1010</v>
       </c>
       <c r="C91">
-        <v>1130</v>
+        <v>1120</v>
       </c>
       <c r="D91">
         <v>15</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2715,13 +2718,13 @@
         <v>1010</v>
       </c>
       <c r="C92">
-        <v>1140</v>
+        <v>1130</v>
       </c>
       <c r="D92">
         <v>15</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2732,13 +2735,13 @@
         <v>1010</v>
       </c>
       <c r="C93">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="D93">
         <v>15</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2749,13 +2752,13 @@
         <v>1010</v>
       </c>
       <c r="C94">
-        <v>4010</v>
+        <v>1150</v>
       </c>
       <c r="D94">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2766,13 +2769,13 @@
         <v>1010</v>
       </c>
       <c r="C95">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D95">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2789,7 +2792,7 @@
         <v>8</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2800,13 +2803,13 @@
         <v>1010</v>
       </c>
       <c r="C97">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D97">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2823,7 +2826,7 @@
         <v>12</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2831,16 +2834,16 @@
         <v>50060</v>
       </c>
       <c r="B99">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C99">
-        <v>30</v>
+        <v>4030</v>
       </c>
       <c r="D99">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2851,13 +2854,13 @@
         <v>4010</v>
       </c>
       <c r="C100">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D100">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2865,16 +2868,16 @@
         <v>50060</v>
       </c>
       <c r="B101">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C101">
-        <v>4310</v>
+        <v>20</v>
       </c>
       <c r="D101">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2885,13 +2888,13 @@
         <v>1010</v>
       </c>
       <c r="C102">
-        <v>5010</v>
+        <v>4310</v>
       </c>
       <c r="D102">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2902,13 +2905,30 @@
         <v>1010</v>
       </c>
       <c r="C103">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="D103">
         <v>5</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104">
+        <v>50060</v>
+      </c>
+      <c r="B104">
+        <v>1010</v>
+      </c>
+      <c r="C104">
+        <v>5020</v>
+      </c>
+      <c r="D104">
+        <v>5</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -2926,7 +2946,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2934,7 +2954,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2942,7 +2962,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2950,7 +2970,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2958,7 +2978,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2974,7 +2994,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2982,7 +3002,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2990,7 +3010,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2998,7 +3018,7 @@
         <v>71</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3006,7 +3026,7 @@
         <v>100</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3014,7 +3034,7 @@
         <v>101</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3022,7 +3042,7 @@
         <v>210</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3030,7 +3050,7 @@
         <v>1010</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3038,7 +3058,7 @@
         <v>2010</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3046,7 +3066,7 @@
         <v>2020</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3054,7 +3074,7 @@
         <v>2030</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3062,7 +3082,7 @@
         <v>2040</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3070,7 +3090,7 @@
         <v>4010</v>
       </c>
       <c r="B19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3078,7 +3098,7 @@
         <v>4020</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="59">
   <si>
     <t>Id</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>取引用</t>
+  </si>
+  <si>
+    <t>交戦ドロップ</t>
   </si>
   <si>
     <t>GetItemType</t>
@@ -196,9 +199,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -217,6 +220,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -224,16 +257,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -246,14 +280,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -261,10 +287,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -283,15 +318,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -299,23 +328,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -329,33 +357,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -370,7 +373,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -382,175 +553,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -564,17 +567,44 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -596,9 +626,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -617,50 +664,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -669,145 +672,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1137,7 +1140,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -2929,6 +2932,40 @@
       </c>
       <c r="E104" s="1" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105">
+        <v>60010</v>
+      </c>
+      <c r="B105">
+        <v>2020</v>
+      </c>
+      <c r="C105">
+        <v>5</v>
+      </c>
+      <c r="D105">
+        <v>1</v>
+      </c>
+      <c r="E105" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106">
+        <v>60010</v>
+      </c>
+      <c r="B106">
+        <v>2</v>
+      </c>
+      <c r="C106">
+        <v>5</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2946,7 +2983,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2954,7 +2991,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2962,7 +2999,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2970,7 +3007,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2978,7 +3015,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2994,7 +3031,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3002,7 +3039,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3010,7 +3047,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3018,7 +3055,7 @@
         <v>71</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3026,7 +3063,7 @@
         <v>100</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3034,7 +3071,7 @@
         <v>101</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3042,7 +3079,7 @@
         <v>210</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3050,7 +3087,7 @@
         <v>1010</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3058,7 +3095,7 @@
         <v>2010</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3066,7 +3103,7 @@
         <v>2020</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3074,7 +3111,7 @@
         <v>2030</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3082,7 +3119,7 @@
         <v>2040</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3090,7 +3127,7 @@
         <v>4010</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3098,7 +3135,7 @@
         <v>4020</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8410"/>
   </bookViews>
   <sheets>
     <sheet name="PrizeSets" sheetId="1" r:id="rId1"/>
@@ -201,8 +201,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -220,31 +220,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -258,30 +242,15 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -296,23 +265,23 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -320,30 +289,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -357,8 +303,62 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -373,7 +373,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -391,7 +397,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -403,13 +445,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -421,13 +511,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -439,31 +529,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -475,79 +547,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,44 +567,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -626,11 +593,48 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -650,17 +654,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -672,7 +672,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -681,7 +681,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -690,127 +690,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -199,10 +199,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -227,43 +227,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -273,15 +236,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,49 +250,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -358,7 +275,90 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -373,7 +373,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -385,7 +385,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -397,12 +409,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -415,7 +421,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -433,49 +487,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -487,43 +529,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -535,25 +553,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -564,6 +564,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -576,17 +591,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -609,16 +620,31 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -638,32 +664,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -672,145 +672,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410"/>
+    <workbookView windowWidth="19200" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="PrizeSets" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="67">
   <si>
     <t>Id</t>
   </si>
@@ -83,6 +83,9 @@
     <t>回復薬回数+1</t>
   </si>
   <si>
+    <t>虹の指南書(見習い)</t>
+  </si>
+  <si>
     <t>炎の精霊石x1</t>
   </si>
   <si>
@@ -98,15 +101,39 @@
     <t>闇の精霊石</t>
   </si>
   <si>
+    <t>虹の指南書(精通)</t>
+  </si>
+  <si>
+    <t>虹の指南書(熟練者)</t>
+  </si>
+  <si>
     <t>初級指南書</t>
   </si>
   <si>
+    <t>初級指南書x3</t>
+  </si>
+  <si>
+    <t>初級指南書x5</t>
+  </si>
+  <si>
     <t>中級指南書</t>
   </si>
   <si>
+    <t>中級指南書xx3</t>
+  </si>
+  <si>
+    <t>中級指南書x5</t>
+  </si>
+  <si>
     <t>上級指南書</t>
   </si>
   <si>
+    <t>上級指南書x3</t>
+  </si>
+  <si>
+    <t>上級指南書x5</t>
+  </si>
+  <si>
     <t>特級指南書</t>
   </si>
   <si>
@@ -123,9 +150,6 @@
   </si>
   <si>
     <t>Rankアップ</t>
-  </si>
-  <si>
-    <t>魔晶石セット</t>
   </si>
   <si>
     <t>評価値</t>
@@ -200,9 +224,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -220,36 +244,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -259,38 +253,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -299,50 +263,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -358,7 +278,111 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -373,7 +397,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -385,37 +517,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -427,31 +565,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -463,97 +577,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -564,6 +588,45 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -586,51 +649,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -650,17 +669,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -672,145 +696,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -830,12 +854,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -1140,10 +1164,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
-    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="5" max="5" width="19.2727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1576,13 +1600,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>10010</v>
+        <v>10000</v>
       </c>
       <c r="B25">
         <v>1010</v>
       </c>
       <c r="C25">
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1593,738 +1617,738 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>10020</v>
+        <v>10002</v>
       </c>
       <c r="B26">
         <v>1010</v>
       </c>
       <c r="C26">
-        <v>1020</v>
+        <v>1000</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>10030</v>
+        <v>10010</v>
       </c>
       <c r="B27">
         <v>1010</v>
       </c>
       <c r="C27">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>10040</v>
+        <v>10020</v>
       </c>
       <c r="B28">
         <v>1010</v>
       </c>
       <c r="C28">
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>10050</v>
+        <v>10030</v>
       </c>
       <c r="B29">
         <v>1010</v>
       </c>
       <c r="C29">
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>11010</v>
+        <v>10040</v>
       </c>
       <c r="B30">
         <v>1010</v>
       </c>
       <c r="C30">
-        <v>1110</v>
+        <v>1040</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>11020</v>
+        <v>10050</v>
       </c>
       <c r="B31">
         <v>1010</v>
       </c>
       <c r="C31">
-        <v>1120</v>
+        <v>1050</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>11030</v>
+        <v>11000</v>
       </c>
       <c r="B32">
         <v>1010</v>
       </c>
       <c r="C32">
-        <v>1130</v>
+        <v>1100</v>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>11040</v>
+        <v>11002</v>
       </c>
       <c r="B33">
         <v>1010</v>
       </c>
       <c r="C33">
-        <v>1140</v>
+        <v>1100</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>11050</v>
+        <v>11010</v>
       </c>
       <c r="B34">
         <v>1010</v>
       </c>
       <c r="C34">
-        <v>1150</v>
+        <v>1110</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>14010</v>
+        <v>11020</v>
       </c>
       <c r="B35">
         <v>1010</v>
       </c>
       <c r="C35">
-        <v>4010</v>
+        <v>1120</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>14020</v>
+        <v>11030</v>
       </c>
       <c r="B36">
         <v>1010</v>
       </c>
       <c r="C36">
-        <v>4020</v>
+        <v>1130</v>
       </c>
       <c r="D36">
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>14030</v>
+        <v>11040</v>
       </c>
       <c r="B37">
         <v>1010</v>
       </c>
       <c r="C37">
-        <v>4030</v>
+        <v>1140</v>
       </c>
       <c r="D37">
         <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>14040</v>
+        <v>11050</v>
       </c>
       <c r="B38">
         <v>1010</v>
       </c>
       <c r="C38">
-        <v>4040</v>
+        <v>1150</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>14310</v>
+        <v>12000</v>
       </c>
       <c r="B39">
         <v>1010</v>
       </c>
       <c r="C39">
-        <v>4310</v>
+        <v>1100</v>
       </c>
       <c r="D39">
         <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>15040</v>
+        <v>12002</v>
       </c>
       <c r="B40">
         <v>1010</v>
       </c>
       <c r="C40">
-        <v>5040</v>
+        <v>1200</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>15050</v>
+        <v>12010</v>
       </c>
       <c r="B41">
         <v>1010</v>
       </c>
       <c r="C41">
-        <v>5050</v>
+        <v>1210</v>
       </c>
       <c r="D41">
         <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>15060</v>
+        <v>12020</v>
       </c>
       <c r="B42">
         <v>1010</v>
       </c>
       <c r="C42">
-        <v>5060</v>
+        <v>1220</v>
       </c>
       <c r="D42">
         <v>1</v>
       </c>
       <c r="E42" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>20010</v>
+        <v>12030</v>
       </c>
       <c r="B43">
-        <v>2010</v>
+        <v>1010</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>1230</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>30010</v>
+        <v>12040</v>
       </c>
       <c r="B44">
         <v>1010</v>
       </c>
       <c r="C44">
-        <v>1100</v>
+        <v>1240</v>
       </c>
       <c r="D44">
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>30020</v>
+        <v>12050</v>
       </c>
       <c r="B45">
         <v>1010</v>
       </c>
       <c r="C45">
-        <v>1000</v>
+        <v>1250</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
       <c r="E45" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46">
-        <v>40010</v>
+        <v>14010</v>
       </c>
       <c r="B46">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="C46">
-        <v>15</v>
+        <v>4010</v>
       </c>
       <c r="D46">
         <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47">
-        <v>40020</v>
+        <v>14013</v>
       </c>
       <c r="B47">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="C47">
-        <v>10</v>
+        <v>4010</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E47" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48">
-        <v>40030</v>
+        <v>14015</v>
       </c>
       <c r="B48">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="C48">
+        <v>4010</v>
+      </c>
+      <c r="D48">
         <v>5</v>
       </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
       <c r="E48" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49">
-        <v>50010</v>
+        <v>14020</v>
       </c>
       <c r="B49">
         <v>1010</v>
       </c>
       <c r="C49">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="D49">
-        <v>4</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
+      </c>
+      <c r="E49" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50">
-        <v>50010</v>
+        <v>14023</v>
       </c>
       <c r="B50">
         <v>1010</v>
       </c>
       <c r="C50">
-        <v>5050</v>
+        <v>4020</v>
       </c>
       <c r="D50">
-        <v>5</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>38</v>
+        <v>3</v>
+      </c>
+      <c r="E50" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51">
-        <v>50020</v>
+        <v>14025</v>
       </c>
       <c r="B51">
         <v>1010</v>
       </c>
       <c r="C51">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="D51">
-        <v>4</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
+      </c>
+      <c r="E51" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52">
-        <v>50020</v>
+        <v>14030</v>
       </c>
       <c r="B52">
         <v>1010</v>
       </c>
       <c r="C52">
-        <v>4020</v>
+        <v>4030</v>
       </c>
       <c r="D52">
-        <v>8</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
+      </c>
+      <c r="E52" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53">
-        <v>50020</v>
+        <v>14033</v>
       </c>
       <c r="B53">
         <v>1010</v>
       </c>
       <c r="C53">
-        <v>5050</v>
+        <v>4030</v>
       </c>
       <c r="D53">
-        <v>5</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>38</v>
+        <v>3</v>
+      </c>
+      <c r="E53" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>50020</v>
+        <v>14035</v>
       </c>
       <c r="B54">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C54">
-        <v>20</v>
+        <v>4030</v>
       </c>
       <c r="D54">
-        <v>20</v>
-      </c>
-      <c r="E54" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E54" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>50030</v>
+        <v>14040</v>
       </c>
       <c r="B55">
         <v>1010</v>
       </c>
       <c r="C55">
-        <v>4010</v>
+        <v>4040</v>
       </c>
       <c r="D55">
-        <v>4</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
+      </c>
+      <c r="E55" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56">
-        <v>50030</v>
+        <v>14310</v>
       </c>
       <c r="B56">
         <v>1010</v>
       </c>
       <c r="C56">
-        <v>4020</v>
+        <v>4310</v>
       </c>
       <c r="D56">
-        <v>8</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
+      </c>
+      <c r="E56" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57">
-        <v>50030</v>
+        <v>15040</v>
       </c>
       <c r="B57">
         <v>1010</v>
       </c>
       <c r="C57">
-        <v>5050</v>
+        <v>5040</v>
       </c>
       <c r="D57">
-        <v>5</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
+      </c>
+      <c r="E57" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58">
-        <v>50030</v>
+        <v>15050</v>
       </c>
       <c r="B58">
         <v>1010</v>
       </c>
       <c r="C58">
-        <v>5060</v>
+        <v>5050</v>
       </c>
       <c r="D58">
-        <v>8</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
+      </c>
+      <c r="E58" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>50030</v>
+        <v>15060</v>
       </c>
       <c r="B59">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C59">
-        <v>20</v>
+        <v>5060</v>
       </c>
       <c r="D59">
-        <v>20</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
+      </c>
+      <c r="E59" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60">
-        <v>50030</v>
+        <v>20010</v>
       </c>
       <c r="B60">
-        <v>1010</v>
+        <v>2010</v>
       </c>
       <c r="C60">
-        <v>1010</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>10</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>38</v>
+        <v>0</v>
+      </c>
+      <c r="E60" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61">
-        <v>50030</v>
+        <v>40010</v>
       </c>
       <c r="B61">
-        <v>1010</v>
+        <v>2020</v>
       </c>
       <c r="C61">
-        <v>1020</v>
+        <v>15</v>
       </c>
       <c r="D61">
-        <v>10</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
+      </c>
+      <c r="E61" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62">
-        <v>50030</v>
+        <v>40020</v>
       </c>
       <c r="B62">
-        <v>1010</v>
+        <v>2020</v>
       </c>
       <c r="C62">
-        <v>1030</v>
+        <v>10</v>
       </c>
       <c r="D62">
-        <v>10</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
+      </c>
+      <c r="E62" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>50030</v>
+        <v>40030</v>
       </c>
       <c r="B63">
-        <v>1010</v>
+        <v>2020</v>
       </c>
       <c r="C63">
-        <v>1040</v>
+        <v>5</v>
       </c>
       <c r="D63">
-        <v>10</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
+      </c>
+      <c r="E63" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>50030</v>
+        <v>50010</v>
       </c>
       <c r="B64">
         <v>1010</v>
       </c>
       <c r="C64">
-        <v>1050</v>
+        <v>4010</v>
       </c>
       <c r="D64">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>50040</v>
+        <v>50010</v>
       </c>
       <c r="B65">
         <v>1010</v>
       </c>
       <c r="C65">
-        <v>4010</v>
+        <v>5050</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>50040</v>
+        <v>50020</v>
       </c>
       <c r="B66">
         <v>1010</v>
       </c>
       <c r="C66">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D66">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>50040</v>
+        <v>50020</v>
       </c>
       <c r="B67">
         <v>1010</v>
       </c>
       <c r="C67">
-        <v>5050</v>
+        <v>4020</v>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>50040</v>
+        <v>50020</v>
       </c>
       <c r="B68">
         <v>1010</v>
       </c>
       <c r="C68">
-        <v>5060</v>
+        <v>5050</v>
       </c>
       <c r="D68">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>50040</v>
+        <v>50020</v>
       </c>
       <c r="B69">
         <v>4010</v>
@@ -2336,471 +2360,471 @@
         <v>20</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B70">
         <v>1010</v>
       </c>
       <c r="C70">
-        <v>4310</v>
+        <v>4010</v>
       </c>
       <c r="D70">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B71">
         <v>1010</v>
       </c>
       <c r="C71">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="D71">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B72">
         <v>1010</v>
       </c>
       <c r="C72">
-        <v>1020</v>
+        <v>5050</v>
       </c>
       <c r="D72">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B73">
         <v>1010</v>
       </c>
       <c r="C73">
-        <v>1030</v>
+        <v>5060</v>
       </c>
       <c r="D73">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B74">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C74">
-        <v>1040</v>
+        <v>20</v>
       </c>
       <c r="D74">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B75">
         <v>1010</v>
       </c>
       <c r="C75">
-        <v>1050</v>
+        <v>1010</v>
       </c>
       <c r="D75">
         <v>10</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76">
-        <v>50050</v>
+        <v>50030</v>
       </c>
       <c r="B76">
         <v>1010</v>
       </c>
       <c r="C76">
-        <v>1110</v>
+        <v>1020</v>
       </c>
       <c r="D76">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77">
-        <v>50050</v>
+        <v>50030</v>
       </c>
       <c r="B77">
         <v>1010</v>
       </c>
       <c r="C77">
-        <v>1120</v>
+        <v>1030</v>
       </c>
       <c r="D77">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78">
-        <v>50050</v>
+        <v>50030</v>
       </c>
       <c r="B78">
         <v>1010</v>
       </c>
       <c r="C78">
-        <v>1130</v>
+        <v>1040</v>
       </c>
       <c r="D78">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79">
-        <v>50050</v>
+        <v>50030</v>
       </c>
       <c r="B79">
         <v>1010</v>
       </c>
       <c r="C79">
-        <v>1140</v>
+        <v>1050</v>
       </c>
       <c r="D79">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B80">
         <v>1010</v>
       </c>
       <c r="C80">
-        <v>1150</v>
+        <v>4010</v>
       </c>
       <c r="D80">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B81">
         <v>1010</v>
       </c>
       <c r="C81">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="D81">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B82">
         <v>1010</v>
       </c>
       <c r="C82">
-        <v>4020</v>
+        <v>5050</v>
       </c>
       <c r="D82">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B83">
         <v>1010</v>
       </c>
       <c r="C83">
-        <v>4020</v>
+        <v>5060</v>
       </c>
       <c r="D83">
         <v>8</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B84">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C84">
-        <v>4030</v>
+        <v>20</v>
       </c>
       <c r="D84">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B85">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C85">
+        <v>4310</v>
+      </c>
+      <c r="D85">
         <v>30</v>
       </c>
-      <c r="D85">
-        <v>10</v>
-      </c>
       <c r="E85" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B86">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C86">
-        <v>20</v>
+        <v>1010</v>
       </c>
       <c r="D86">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B87">
         <v>1010</v>
       </c>
       <c r="C87">
-        <v>4310</v>
+        <v>1020</v>
       </c>
       <c r="D87">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B88">
         <v>1010</v>
       </c>
       <c r="C88">
-        <v>5010</v>
+        <v>1030</v>
       </c>
       <c r="D88">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B89">
         <v>1010</v>
       </c>
       <c r="C89">
-        <v>5020</v>
+        <v>1040</v>
       </c>
       <c r="D89">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>50060</v>
+        <v>50040</v>
       </c>
       <c r="B90">
         <v>1010</v>
       </c>
       <c r="C90">
-        <v>1110</v>
+        <v>1050</v>
       </c>
       <c r="D90">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B91">
         <v>1010</v>
       </c>
       <c r="C91">
-        <v>1120</v>
+        <v>1110</v>
       </c>
       <c r="D91">
         <v>15</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B92">
         <v>1010</v>
       </c>
       <c r="C92">
-        <v>1130</v>
+        <v>1120</v>
       </c>
       <c r="D92">
         <v>15</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B93">
         <v>1010</v>
       </c>
       <c r="C93">
-        <v>1140</v>
+        <v>1130</v>
       </c>
       <c r="D93">
         <v>15</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B94">
         <v>1010</v>
       </c>
       <c r="C94">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="D94">
         <v>15</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B95">
         <v>1010</v>
       </c>
       <c r="C95">
-        <v>4010</v>
+        <v>1150</v>
       </c>
       <c r="D95">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B96">
         <v>1010</v>
       </c>
       <c r="C96">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D96">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B97">
         <v>1010</v>
@@ -2812,29 +2836,29 @@
         <v>8</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B98">
         <v>1010</v>
       </c>
       <c r="C98">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D98">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B99">
         <v>1010</v>
@@ -2846,12 +2870,12 @@
         <v>12</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B100">
         <v>4010</v>
@@ -2863,12 +2887,12 @@
         <v>10</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B101">
         <v>4010</v>
@@ -2880,12 +2904,12 @@
         <v>20</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B102">
         <v>1010</v>
@@ -2897,12 +2921,12 @@
         <v>30</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B103">
         <v>1010</v>
@@ -2914,12 +2938,12 @@
         <v>5</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B104">
         <v>1010</v>
@@ -2931,40 +2955,295 @@
         <v>5</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105">
-        <v>60010</v>
+        <v>50060</v>
       </c>
       <c r="B105">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="C105">
-        <v>5</v>
+        <v>1110</v>
       </c>
       <c r="D105">
-        <v>1</v>
-      </c>
-      <c r="E105" t="s">
-        <v>39</v>
+        <v>15</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106">
+        <v>50060</v>
+      </c>
+      <c r="B106">
+        <v>1010</v>
+      </c>
+      <c r="C106">
+        <v>1120</v>
+      </c>
+      <c r="D106">
+        <v>15</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107">
+        <v>50060</v>
+      </c>
+      <c r="B107">
+        <v>1010</v>
+      </c>
+      <c r="C107">
+        <v>1130</v>
+      </c>
+      <c r="D107">
+        <v>15</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108">
+        <v>50060</v>
+      </c>
+      <c r="B108">
+        <v>1010</v>
+      </c>
+      <c r="C108">
+        <v>1140</v>
+      </c>
+      <c r="D108">
+        <v>15</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109">
+        <v>50060</v>
+      </c>
+      <c r="B109">
+        <v>1010</v>
+      </c>
+      <c r="C109">
+        <v>1150</v>
+      </c>
+      <c r="D109">
+        <v>15</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110">
+        <v>50060</v>
+      </c>
+      <c r="B110">
+        <v>1010</v>
+      </c>
+      <c r="C110">
+        <v>4010</v>
+      </c>
+      <c r="D110">
+        <v>4</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111">
+        <v>50060</v>
+      </c>
+      <c r="B111">
+        <v>1010</v>
+      </c>
+      <c r="C111">
+        <v>4020</v>
+      </c>
+      <c r="D111">
+        <v>8</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112">
+        <v>50060</v>
+      </c>
+      <c r="B112">
+        <v>1010</v>
+      </c>
+      <c r="C112">
+        <v>4020</v>
+      </c>
+      <c r="D112">
+        <v>8</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113">
+        <v>50060</v>
+      </c>
+      <c r="B113">
+        <v>1010</v>
+      </c>
+      <c r="C113">
+        <v>4030</v>
+      </c>
+      <c r="D113">
+        <v>12</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114">
+        <v>50060</v>
+      </c>
+      <c r="B114">
+        <v>1010</v>
+      </c>
+      <c r="C114">
+        <v>4030</v>
+      </c>
+      <c r="D114">
+        <v>12</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115">
+        <v>50060</v>
+      </c>
+      <c r="B115">
+        <v>4010</v>
+      </c>
+      <c r="C115">
+        <v>30</v>
+      </c>
+      <c r="D115">
+        <v>10</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116">
+        <v>50060</v>
+      </c>
+      <c r="B116">
+        <v>4010</v>
+      </c>
+      <c r="C116">
+        <v>20</v>
+      </c>
+      <c r="D116">
+        <v>20</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117">
+        <v>50060</v>
+      </c>
+      <c r="B117">
+        <v>1010</v>
+      </c>
+      <c r="C117">
+        <v>4310</v>
+      </c>
+      <c r="D117">
+        <v>30</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118">
+        <v>50060</v>
+      </c>
+      <c r="B118">
+        <v>1010</v>
+      </c>
+      <c r="C118">
+        <v>5010</v>
+      </c>
+      <c r="D118">
+        <v>5</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119">
+        <v>50060</v>
+      </c>
+      <c r="B119">
+        <v>1010</v>
+      </c>
+      <c r="C119">
+        <v>5020</v>
+      </c>
+      <c r="D119">
+        <v>5</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120">
         <v>60010</v>
       </c>
-      <c r="B106">
+      <c r="B120">
+        <v>2020</v>
+      </c>
+      <c r="C120">
+        <v>5</v>
+      </c>
+      <c r="D120">
+        <v>1</v>
+      </c>
+      <c r="E120" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121">
+        <v>60010</v>
+      </c>
+      <c r="B121">
         <v>2</v>
       </c>
-      <c r="C106">
+      <c r="C121">
         <v>5</v>
       </c>
-      <c r="D106">
+      <c r="D121">
         <v>0</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E121" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2983,7 +3262,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2991,7 +3270,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2999,7 +3278,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3007,7 +3286,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3015,7 +3294,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3031,7 +3310,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3039,7 +3318,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3047,7 +3326,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3055,7 +3334,7 @@
         <v>71</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3063,7 +3342,7 @@
         <v>100</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3071,7 +3350,7 @@
         <v>101</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3079,7 +3358,7 @@
         <v>210</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3087,7 +3366,7 @@
         <v>1010</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3095,7 +3374,7 @@
         <v>2010</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3103,7 +3382,7 @@
         <v>2020</v>
       </c>
       <c r="B16" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3111,7 +3390,7 @@
         <v>2030</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3119,7 +3398,7 @@
         <v>2040</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3127,7 +3406,7 @@
         <v>4010</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3135,7 +3414,7 @@
         <v>4020</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="PrizeSets" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="70">
   <si>
     <t>Id</t>
   </si>
@@ -152,6 +152,12 @@
     <t>Rankアップ</t>
   </si>
   <si>
+    <t>アミィ</t>
+  </si>
+  <si>
+    <t>ハウレス</t>
+  </si>
+  <si>
     <t>評価値</t>
   </si>
   <si>
@@ -198,6 +204,9 @@
   </si>
   <si>
     <t>Item</t>
+  </si>
+  <si>
+    <t>Equipment</t>
   </si>
   <si>
     <t>RankUp</t>
@@ -223,10 +232,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -244,17 +253,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -268,6 +282,52 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -278,7 +338,30 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -293,82 +376,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -381,10 +389,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -397,13 +406,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -421,103 +550,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -535,24 +568,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -565,19 +580,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -606,6 +615,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -626,6 +646,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,21 +689,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -677,17 +697,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -696,145 +705,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1164,7 +1173,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F123"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="19.2727272727273" customWidth="1"/>
@@ -2212,16 +2221,16 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61">
-        <v>40010</v>
+        <v>31010</v>
       </c>
       <c r="B61">
-        <v>2020</v>
+        <v>1020</v>
       </c>
       <c r="C61">
-        <v>15</v>
+        <v>1010</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" t="s">
         <v>45</v>
@@ -2229,75 +2238,75 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62">
-        <v>40020</v>
+        <v>31020</v>
       </c>
       <c r="B62">
-        <v>2020</v>
+        <v>1020</v>
       </c>
       <c r="C62">
-        <v>10</v>
+        <v>1020</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>40030</v>
+        <v>40010</v>
       </c>
       <c r="B63">
         <v>2020</v>
       </c>
       <c r="C63">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D63">
         <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>50010</v>
+        <v>40020</v>
       </c>
       <c r="B64">
-        <v>1010</v>
+        <v>2020</v>
       </c>
       <c r="C64">
-        <v>4010</v>
+        <v>10</v>
       </c>
       <c r="D64">
-        <v>4</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>46</v>
+        <v>1</v>
+      </c>
+      <c r="E64" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>50010</v>
+        <v>40030</v>
       </c>
       <c r="B65">
-        <v>1010</v>
+        <v>2020</v>
       </c>
       <c r="C65">
-        <v>5050</v>
+        <v>5</v>
       </c>
       <c r="D65">
-        <v>5</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>46</v>
+        <v>1</v>
+      </c>
+      <c r="E65" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>50020</v>
+        <v>50010</v>
       </c>
       <c r="B66">
         <v>1010</v>
@@ -2309,24 +2318,24 @@
         <v>4</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>50020</v>
+        <v>50010</v>
       </c>
       <c r="B67">
         <v>1010</v>
       </c>
       <c r="C67">
-        <v>4020</v>
+        <v>5050</v>
       </c>
       <c r="D67">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2337,13 +2346,13 @@
         <v>1010</v>
       </c>
       <c r="C68">
-        <v>5050</v>
+        <v>4010</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2351,50 +2360,50 @@
         <v>50020</v>
       </c>
       <c r="B69">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C69">
-        <v>20</v>
+        <v>4020</v>
       </c>
       <c r="D69">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B70">
         <v>1010</v>
       </c>
       <c r="C70">
-        <v>4010</v>
+        <v>5050</v>
       </c>
       <c r="D70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B71">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C71">
-        <v>4020</v>
+        <v>20</v>
       </c>
       <c r="D71">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2405,13 +2414,13 @@
         <v>1010</v>
       </c>
       <c r="C72">
-        <v>5050</v>
+        <v>4010</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2422,13 +2431,13 @@
         <v>1010</v>
       </c>
       <c r="C73">
-        <v>5060</v>
+        <v>4020</v>
       </c>
       <c r="D73">
         <v>8</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2436,16 +2445,16 @@
         <v>50030</v>
       </c>
       <c r="B74">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C74">
-        <v>20</v>
+        <v>5050</v>
       </c>
       <c r="D74">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2456,13 +2465,13 @@
         <v>1010</v>
       </c>
       <c r="C75">
-        <v>1010</v>
+        <v>5060</v>
       </c>
       <c r="D75">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2470,16 +2479,16 @@
         <v>50030</v>
       </c>
       <c r="B76">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C76">
-        <v>1020</v>
+        <v>20</v>
       </c>
       <c r="D76">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2490,13 +2499,13 @@
         <v>1010</v>
       </c>
       <c r="C77">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="D77">
         <v>10</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2507,13 +2516,13 @@
         <v>1010</v>
       </c>
       <c r="C78">
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="D78">
         <v>10</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2524,47 +2533,47 @@
         <v>1010</v>
       </c>
       <c r="C79">
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="D79">
         <v>10</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B80">
         <v>1010</v>
       </c>
       <c r="C80">
-        <v>4010</v>
+        <v>1040</v>
       </c>
       <c r="D80">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B81">
         <v>1010</v>
       </c>
       <c r="C81">
-        <v>4020</v>
+        <v>1050</v>
       </c>
       <c r="D81">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2575,13 +2584,13 @@
         <v>1010</v>
       </c>
       <c r="C82">
-        <v>5050</v>
+        <v>4010</v>
       </c>
       <c r="D82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2592,13 +2601,13 @@
         <v>1010</v>
       </c>
       <c r="C83">
-        <v>5060</v>
+        <v>4020</v>
       </c>
       <c r="D83">
         <v>8</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2606,16 +2615,16 @@
         <v>50040</v>
       </c>
       <c r="B84">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C84">
-        <v>20</v>
+        <v>5050</v>
       </c>
       <c r="D84">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2626,13 +2635,13 @@
         <v>1010</v>
       </c>
       <c r="C85">
-        <v>4310</v>
+        <v>5060</v>
       </c>
       <c r="D85">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2640,16 +2649,16 @@
         <v>50040</v>
       </c>
       <c r="B86">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C86">
-        <v>1010</v>
+        <v>20</v>
       </c>
       <c r="D86">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2660,13 +2669,13 @@
         <v>1010</v>
       </c>
       <c r="C87">
-        <v>1020</v>
+        <v>4310</v>
       </c>
       <c r="D87">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2677,13 +2686,13 @@
         <v>1010</v>
       </c>
       <c r="C88">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="D88">
         <v>10</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2694,13 +2703,13 @@
         <v>1010</v>
       </c>
       <c r="C89">
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="D89">
         <v>10</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2711,47 +2720,47 @@
         <v>1010</v>
       </c>
       <c r="C90">
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="D90">
         <v>10</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B91">
         <v>1010</v>
       </c>
       <c r="C91">
-        <v>1110</v>
+        <v>1040</v>
       </c>
       <c r="D91">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B92">
         <v>1010</v>
       </c>
       <c r="C92">
-        <v>1120</v>
+        <v>1050</v>
       </c>
       <c r="D92">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2762,13 +2771,13 @@
         <v>1010</v>
       </c>
       <c r="C93">
-        <v>1130</v>
+        <v>1110</v>
       </c>
       <c r="D93">
         <v>15</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2779,13 +2788,13 @@
         <v>1010</v>
       </c>
       <c r="C94">
-        <v>1140</v>
+        <v>1120</v>
       </c>
       <c r="D94">
         <v>15</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2796,13 +2805,13 @@
         <v>1010</v>
       </c>
       <c r="C95">
-        <v>1150</v>
+        <v>1130</v>
       </c>
       <c r="D95">
         <v>15</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2813,13 +2822,13 @@
         <v>1010</v>
       </c>
       <c r="C96">
-        <v>4010</v>
+        <v>1140</v>
       </c>
       <c r="D96">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2830,13 +2839,13 @@
         <v>1010</v>
       </c>
       <c r="C97">
-        <v>4020</v>
+        <v>1150</v>
       </c>
       <c r="D97">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2847,13 +2856,13 @@
         <v>1010</v>
       </c>
       <c r="C98">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D98">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2864,13 +2873,13 @@
         <v>1010</v>
       </c>
       <c r="C99">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D99">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2878,16 +2887,16 @@
         <v>50050</v>
       </c>
       <c r="B100">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C100">
-        <v>30</v>
+        <v>4020</v>
       </c>
       <c r="D100">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2895,16 +2904,16 @@
         <v>50050</v>
       </c>
       <c r="B101">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C101">
-        <v>20</v>
+        <v>4030</v>
       </c>
       <c r="D101">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2912,16 +2921,16 @@
         <v>50050</v>
       </c>
       <c r="B102">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C102">
-        <v>4310</v>
+        <v>30</v>
       </c>
       <c r="D102">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2929,16 +2938,16 @@
         <v>50050</v>
       </c>
       <c r="B103">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C103">
-        <v>5010</v>
+        <v>20</v>
       </c>
       <c r="D103">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2949,47 +2958,47 @@
         <v>1010</v>
       </c>
       <c r="C104">
-        <v>5020</v>
+        <v>4310</v>
       </c>
       <c r="D104">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B105">
         <v>1010</v>
       </c>
       <c r="C105">
-        <v>1110</v>
+        <v>5010</v>
       </c>
       <c r="D105">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B106">
         <v>1010</v>
       </c>
       <c r="C106">
-        <v>1120</v>
+        <v>5020</v>
       </c>
       <c r="D106">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -3000,13 +3009,13 @@
         <v>1010</v>
       </c>
       <c r="C107">
-        <v>1130</v>
+        <v>1110</v>
       </c>
       <c r="D107">
         <v>15</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -3017,13 +3026,13 @@
         <v>1010</v>
       </c>
       <c r="C108">
-        <v>1140</v>
+        <v>1120</v>
       </c>
       <c r="D108">
         <v>15</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -3034,13 +3043,13 @@
         <v>1010</v>
       </c>
       <c r="C109">
-        <v>1150</v>
+        <v>1130</v>
       </c>
       <c r="D109">
         <v>15</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -3051,13 +3060,13 @@
         <v>1010</v>
       </c>
       <c r="C110">
-        <v>4010</v>
+        <v>1140</v>
       </c>
       <c r="D110">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -3068,13 +3077,13 @@
         <v>1010</v>
       </c>
       <c r="C111">
-        <v>4020</v>
+        <v>1150</v>
       </c>
       <c r="D111">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -3085,13 +3094,13 @@
         <v>1010</v>
       </c>
       <c r="C112">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D112">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -3102,13 +3111,13 @@
         <v>1010</v>
       </c>
       <c r="C113">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D113">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -3119,13 +3128,13 @@
         <v>1010</v>
       </c>
       <c r="C114">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D114">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -3133,16 +3142,16 @@
         <v>50060</v>
       </c>
       <c r="B115">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C115">
-        <v>30</v>
+        <v>4030</v>
       </c>
       <c r="D115">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -3150,16 +3159,16 @@
         <v>50060</v>
       </c>
       <c r="B116">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C116">
-        <v>20</v>
+        <v>4030</v>
       </c>
       <c r="D116">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -3167,16 +3176,16 @@
         <v>50060</v>
       </c>
       <c r="B117">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C117">
-        <v>4310</v>
+        <v>30</v>
       </c>
       <c r="D117">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -3184,16 +3193,16 @@
         <v>50060</v>
       </c>
       <c r="B118">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C118">
-        <v>5010</v>
+        <v>20</v>
       </c>
       <c r="D118">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -3204,46 +3213,80 @@
         <v>1010</v>
       </c>
       <c r="C119">
-        <v>5020</v>
+        <v>4310</v>
       </c>
       <c r="D119">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120">
-        <v>60010</v>
+        <v>50060</v>
       </c>
       <c r="B120">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="C120">
+        <v>5010</v>
+      </c>
+      <c r="D120">
         <v>5</v>
       </c>
-      <c r="D120">
-        <v>1</v>
-      </c>
-      <c r="E120" t="s">
-        <v>47</v>
+      <c r="E120" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121">
+        <v>50060</v>
+      </c>
+      <c r="B121">
+        <v>1010</v>
+      </c>
+      <c r="C121">
+        <v>5020</v>
+      </c>
+      <c r="D121">
+        <v>5</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122">
         <v>60010</v>
       </c>
-      <c r="B121">
+      <c r="B122">
+        <v>2020</v>
+      </c>
+      <c r="C122">
+        <v>5</v>
+      </c>
+      <c r="D122">
+        <v>1</v>
+      </c>
+      <c r="E122" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123">
+        <v>60010</v>
+      </c>
+      <c r="B123">
         <v>2</v>
       </c>
-      <c r="C121">
+      <c r="C123">
         <v>5</v>
       </c>
-      <c r="D121">
+      <c r="D123">
         <v>0</v>
       </c>
-      <c r="E121" t="s">
+      <c r="E123" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3257,12 +3300,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3270,7 +3313,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3278,7 +3321,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3286,7 +3329,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3294,7 +3337,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3310,7 +3353,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3318,7 +3361,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3326,7 +3369,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3334,7 +3377,7 @@
         <v>71</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3342,7 +3385,7 @@
         <v>100</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3350,7 +3393,7 @@
         <v>101</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3358,7 +3401,7 @@
         <v>210</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3366,55 +3409,63 @@
         <v>1010</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>2010</v>
+        <v>1020</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>4010</v>
+        <v>2040</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
+        <v>4010</v>
+      </c>
+      <c r="B20" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
         <v>4020</v>
       </c>
-      <c r="B20" t="s">
-        <v>66</v>
+      <c r="B21" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -233,8 +233,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -253,8 +253,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -268,37 +277,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -321,22 +307,6 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -344,24 +314,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -376,7 +331,44 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -390,7 +382,15 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -406,13 +406,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -424,13 +418,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -448,72 +532,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -526,31 +544,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -562,7 +568,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,19 +586,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -617,11 +617,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -641,15 +639,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -661,6 +650,35 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -679,24 +697,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -705,145 +705,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="70">
   <si>
     <t>Id</t>
   </si>
@@ -233,9 +233,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -253,8 +253,83 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -269,8 +344,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -283,16 +366,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -306,94 +390,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -412,7 +412,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -430,7 +442,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -442,13 +496,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -460,61 +568,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -526,67 +580,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -618,8 +618,32 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,46 +663,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -697,6 +686,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -705,22 +705,22 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -729,121 +729,121 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1173,7 +1173,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="19.2727272727273" customWidth="1"/>
@@ -2340,16 +2340,16 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>50020</v>
+        <v>50010</v>
       </c>
       <c r="B68">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="C68">
-        <v>4010</v>
+        <v>6010</v>
       </c>
       <c r="D68">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>48</v>
@@ -2363,10 +2363,10 @@
         <v>1010</v>
       </c>
       <c r="C69">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D69">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>48</v>
@@ -2380,10 +2380,10 @@
         <v>1010</v>
       </c>
       <c r="C70">
-        <v>5050</v>
+        <v>4020</v>
       </c>
       <c r="D70">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>48</v>
@@ -2394,13 +2394,13 @@
         <v>50020</v>
       </c>
       <c r="B71">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C71">
-        <v>20</v>
+        <v>5050</v>
       </c>
       <c r="D71">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>48</v>
@@ -2408,16 +2408,16 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B72">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C72">
-        <v>4010</v>
+        <v>20</v>
       </c>
       <c r="D72">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>48</v>
@@ -2431,10 +2431,10 @@
         <v>1010</v>
       </c>
       <c r="C73">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D73">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>48</v>
@@ -2448,10 +2448,10 @@
         <v>1010</v>
       </c>
       <c r="C74">
-        <v>5050</v>
+        <v>4020</v>
       </c>
       <c r="D74">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>48</v>
@@ -2465,10 +2465,10 @@
         <v>1010</v>
       </c>
       <c r="C75">
-        <v>5060</v>
+        <v>5050</v>
       </c>
       <c r="D75">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>48</v>
@@ -2479,13 +2479,13 @@
         <v>50030</v>
       </c>
       <c r="B76">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C76">
-        <v>20</v>
+        <v>5060</v>
       </c>
       <c r="D76">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>48</v>
@@ -2496,13 +2496,13 @@
         <v>50030</v>
       </c>
       <c r="B77">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C77">
-        <v>1010</v>
+        <v>20</v>
       </c>
       <c r="D77">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>48</v>
@@ -2516,7 +2516,7 @@
         <v>1010</v>
       </c>
       <c r="C78">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="D78">
         <v>10</v>
@@ -2533,7 +2533,7 @@
         <v>1010</v>
       </c>
       <c r="C79">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="D79">
         <v>10</v>
@@ -2550,7 +2550,7 @@
         <v>1010</v>
       </c>
       <c r="C80">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="D80">
         <v>10</v>
@@ -2567,7 +2567,7 @@
         <v>1010</v>
       </c>
       <c r="C81">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="D81">
         <v>10</v>
@@ -2578,16 +2578,16 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B82">
         <v>1010</v>
       </c>
       <c r="C82">
-        <v>4010</v>
+        <v>1050</v>
       </c>
       <c r="D82">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>48</v>
@@ -2601,10 +2601,10 @@
         <v>1010</v>
       </c>
       <c r="C83">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D83">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>48</v>
@@ -2618,10 +2618,10 @@
         <v>1010</v>
       </c>
       <c r="C84">
-        <v>5050</v>
+        <v>4020</v>
       </c>
       <c r="D84">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>48</v>
@@ -2635,10 +2635,10 @@
         <v>1010</v>
       </c>
       <c r="C85">
-        <v>5060</v>
+        <v>5050</v>
       </c>
       <c r="D85">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>48</v>
@@ -2649,13 +2649,13 @@
         <v>50040</v>
       </c>
       <c r="B86">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C86">
-        <v>20</v>
+        <v>5060</v>
       </c>
       <c r="D86">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>48</v>
@@ -2666,13 +2666,13 @@
         <v>50040</v>
       </c>
       <c r="B87">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C87">
-        <v>4310</v>
+        <v>20</v>
       </c>
       <c r="D87">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>48</v>
@@ -2686,10 +2686,10 @@
         <v>1010</v>
       </c>
       <c r="C88">
-        <v>1010</v>
+        <v>4310</v>
       </c>
       <c r="D88">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>48</v>
@@ -2703,7 +2703,7 @@
         <v>1010</v>
       </c>
       <c r="C89">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="D89">
         <v>10</v>
@@ -2720,7 +2720,7 @@
         <v>1010</v>
       </c>
       <c r="C90">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="D90">
         <v>10</v>
@@ -2737,7 +2737,7 @@
         <v>1010</v>
       </c>
       <c r="C91">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="D91">
         <v>10</v>
@@ -2754,7 +2754,7 @@
         <v>1010</v>
       </c>
       <c r="C92">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="D92">
         <v>10</v>
@@ -2765,16 +2765,16 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B93">
         <v>1010</v>
       </c>
       <c r="C93">
-        <v>1110</v>
+        <v>1050</v>
       </c>
       <c r="D93">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>48</v>
@@ -2788,7 +2788,7 @@
         <v>1010</v>
       </c>
       <c r="C94">
-        <v>1120</v>
+        <v>1110</v>
       </c>
       <c r="D94">
         <v>15</v>
@@ -2805,7 +2805,7 @@
         <v>1010</v>
       </c>
       <c r="C95">
-        <v>1130</v>
+        <v>1120</v>
       </c>
       <c r="D95">
         <v>15</v>
@@ -2822,7 +2822,7 @@
         <v>1010</v>
       </c>
       <c r="C96">
-        <v>1140</v>
+        <v>1130</v>
       </c>
       <c r="D96">
         <v>15</v>
@@ -2839,7 +2839,7 @@
         <v>1010</v>
       </c>
       <c r="C97">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="D97">
         <v>15</v>
@@ -2856,10 +2856,10 @@
         <v>1010</v>
       </c>
       <c r="C98">
-        <v>4010</v>
+        <v>1150</v>
       </c>
       <c r="D98">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>48</v>
@@ -2873,10 +2873,10 @@
         <v>1010</v>
       </c>
       <c r="C99">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D99">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>48</v>
@@ -2907,10 +2907,10 @@
         <v>1010</v>
       </c>
       <c r="C101">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D101">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>48</v>
@@ -2921,13 +2921,13 @@
         <v>50050</v>
       </c>
       <c r="B102">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C102">
-        <v>30</v>
+        <v>4030</v>
       </c>
       <c r="D102">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>48</v>
@@ -2941,10 +2941,10 @@
         <v>4010</v>
       </c>
       <c r="C103">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D103">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>48</v>
@@ -2955,13 +2955,13 @@
         <v>50050</v>
       </c>
       <c r="B104">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C104">
-        <v>4310</v>
+        <v>20</v>
       </c>
       <c r="D104">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>48</v>
@@ -2975,10 +2975,10 @@
         <v>1010</v>
       </c>
       <c r="C105">
-        <v>5010</v>
+        <v>4310</v>
       </c>
       <c r="D105">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>48</v>
@@ -2992,7 +2992,7 @@
         <v>1010</v>
       </c>
       <c r="C106">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="D106">
         <v>5</v>
@@ -3003,16 +3003,16 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B107">
         <v>1010</v>
       </c>
       <c r="C107">
-        <v>1110</v>
+        <v>5020</v>
       </c>
       <c r="D107">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>48</v>
@@ -3026,7 +3026,7 @@
         <v>1010</v>
       </c>
       <c r="C108">
-        <v>1120</v>
+        <v>1110</v>
       </c>
       <c r="D108">
         <v>15</v>
@@ -3043,7 +3043,7 @@
         <v>1010</v>
       </c>
       <c r="C109">
-        <v>1130</v>
+        <v>1120</v>
       </c>
       <c r="D109">
         <v>15</v>
@@ -3060,7 +3060,7 @@
         <v>1010</v>
       </c>
       <c r="C110">
-        <v>1140</v>
+        <v>1130</v>
       </c>
       <c r="D110">
         <v>15</v>
@@ -3077,7 +3077,7 @@
         <v>1010</v>
       </c>
       <c r="C111">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="D111">
         <v>15</v>
@@ -3094,10 +3094,10 @@
         <v>1010</v>
       </c>
       <c r="C112">
-        <v>4010</v>
+        <v>1150</v>
       </c>
       <c r="D112">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>48</v>
@@ -3111,10 +3111,10 @@
         <v>1010</v>
       </c>
       <c r="C113">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D113">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>48</v>
@@ -3145,10 +3145,10 @@
         <v>1010</v>
       </c>
       <c r="C115">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D115">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>48</v>
@@ -3176,13 +3176,13 @@
         <v>50060</v>
       </c>
       <c r="B117">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C117">
-        <v>30</v>
+        <v>4030</v>
       </c>
       <c r="D117">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>48</v>
@@ -3196,10 +3196,10 @@
         <v>4010</v>
       </c>
       <c r="C118">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D118">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>48</v>
@@ -3210,13 +3210,13 @@
         <v>50060</v>
       </c>
       <c r="B119">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C119">
-        <v>4310</v>
+        <v>20</v>
       </c>
       <c r="D119">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>48</v>
@@ -3230,10 +3230,10 @@
         <v>1010</v>
       </c>
       <c r="C120">
-        <v>5010</v>
+        <v>4310</v>
       </c>
       <c r="D120">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>48</v>
@@ -3247,7 +3247,7 @@
         <v>1010</v>
       </c>
       <c r="C121">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="D121">
         <v>5</v>
@@ -3258,19 +3258,19 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122">
-        <v>60010</v>
+        <v>50060</v>
       </c>
       <c r="B122">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="C122">
+        <v>5020</v>
+      </c>
+      <c r="D122">
         <v>5</v>
       </c>
-      <c r="D122">
-        <v>1</v>
-      </c>
-      <c r="E122" t="s">
-        <v>49</v>
+      <c r="E122" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -3278,15 +3278,32 @@
         <v>60010</v>
       </c>
       <c r="B123">
-        <v>2</v>
+        <v>2020</v>
       </c>
       <c r="C123">
         <v>5</v>
       </c>
       <c r="D123">
+        <v>1</v>
+      </c>
+      <c r="E123" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124">
+        <v>60010</v>
+      </c>
+      <c r="B124">
+        <v>2</v>
+      </c>
+      <c r="C124">
+        <v>5</v>
+      </c>
+      <c r="D124">
         <v>0</v>
       </c>
-      <c r="E123" t="s">
+      <c r="E124" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="70">
   <si>
     <t>Id</t>
   </si>
@@ -232,10 +232,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -253,9 +253,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -271,58 +285,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -344,23 +307,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,9 +322,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -384,7 +339,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -392,6 +362,36 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -406,13 +406,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -424,7 +448,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -436,13 +466,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -454,25 +496,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -490,13 +526,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -508,7 +538,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -520,19 +556,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -550,43 +586,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -597,6 +597,17 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -611,39 +622,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -672,6 +650,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -687,13 +674,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -705,145 +705,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1173,7 +1173,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="19.2727272727273" customWidth="1"/>
@@ -2309,13 +2309,13 @@
         <v>50010</v>
       </c>
       <c r="B66">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="C66">
-        <v>4010</v>
+        <v>6010</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>48</v>
@@ -2329,10 +2329,10 @@
         <v>1010</v>
       </c>
       <c r="C67">
-        <v>5050</v>
+        <v>4010</v>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>48</v>
@@ -2343,13 +2343,13 @@
         <v>50010</v>
       </c>
       <c r="B68">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="C68">
-        <v>6010</v>
+        <v>5050</v>
       </c>
       <c r="D68">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>48</v>
@@ -2360,13 +2360,13 @@
         <v>50020</v>
       </c>
       <c r="B69">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="C69">
-        <v>4010</v>
+        <v>6010</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>48</v>
@@ -2380,10 +2380,10 @@
         <v>1010</v>
       </c>
       <c r="C70">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D70">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>48</v>
@@ -2397,10 +2397,10 @@
         <v>1010</v>
       </c>
       <c r="C71">
-        <v>5050</v>
+        <v>4020</v>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>48</v>
@@ -2411,13 +2411,13 @@
         <v>50020</v>
       </c>
       <c r="B72">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C72">
-        <v>20</v>
+        <v>5050</v>
       </c>
       <c r="D72">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>48</v>
@@ -2425,16 +2425,16 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B73">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C73">
-        <v>4010</v>
+        <v>20</v>
       </c>
       <c r="D73">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>48</v>
@@ -2448,10 +2448,10 @@
         <v>1010</v>
       </c>
       <c r="C74">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D74">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>48</v>
@@ -2465,10 +2465,10 @@
         <v>1010</v>
       </c>
       <c r="C75">
-        <v>5050</v>
+        <v>4020</v>
       </c>
       <c r="D75">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>48</v>
@@ -2482,10 +2482,10 @@
         <v>1010</v>
       </c>
       <c r="C76">
-        <v>5060</v>
+        <v>5050</v>
       </c>
       <c r="D76">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>48</v>
@@ -2496,13 +2496,13 @@
         <v>50030</v>
       </c>
       <c r="B77">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C77">
-        <v>20</v>
+        <v>5060</v>
       </c>
       <c r="D77">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>48</v>
@@ -2513,13 +2513,13 @@
         <v>50030</v>
       </c>
       <c r="B78">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C78">
-        <v>1010</v>
+        <v>20</v>
       </c>
       <c r="D78">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>48</v>
@@ -2533,7 +2533,7 @@
         <v>1010</v>
       </c>
       <c r="C79">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="D79">
         <v>10</v>
@@ -2550,7 +2550,7 @@
         <v>1010</v>
       </c>
       <c r="C80">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="D80">
         <v>10</v>
@@ -2567,7 +2567,7 @@
         <v>1010</v>
       </c>
       <c r="C81">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="D81">
         <v>10</v>
@@ -2584,7 +2584,7 @@
         <v>1010</v>
       </c>
       <c r="C82">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="D82">
         <v>10</v>
@@ -2595,16 +2595,16 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B83">
         <v>1010</v>
       </c>
       <c r="C83">
-        <v>4010</v>
+        <v>1050</v>
       </c>
       <c r="D83">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>48</v>
@@ -2618,10 +2618,10 @@
         <v>1010</v>
       </c>
       <c r="C84">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D84">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>48</v>
@@ -2635,10 +2635,10 @@
         <v>1010</v>
       </c>
       <c r="C85">
-        <v>5050</v>
+        <v>4020</v>
       </c>
       <c r="D85">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>48</v>
@@ -2652,10 +2652,10 @@
         <v>1010</v>
       </c>
       <c r="C86">
-        <v>5060</v>
+        <v>5050</v>
       </c>
       <c r="D86">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>48</v>
@@ -2666,13 +2666,13 @@
         <v>50040</v>
       </c>
       <c r="B87">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C87">
-        <v>20</v>
+        <v>5060</v>
       </c>
       <c r="D87">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>48</v>
@@ -2683,13 +2683,13 @@
         <v>50040</v>
       </c>
       <c r="B88">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C88">
-        <v>4310</v>
+        <v>20</v>
       </c>
       <c r="D88">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>48</v>
@@ -2703,10 +2703,10 @@
         <v>1010</v>
       </c>
       <c r="C89">
-        <v>1010</v>
+        <v>4310</v>
       </c>
       <c r="D89">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>48</v>
@@ -2720,7 +2720,7 @@
         <v>1010</v>
       </c>
       <c r="C90">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="D90">
         <v>10</v>
@@ -2737,7 +2737,7 @@
         <v>1010</v>
       </c>
       <c r="C91">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="D91">
         <v>10</v>
@@ -2754,7 +2754,7 @@
         <v>1010</v>
       </c>
       <c r="C92">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="D92">
         <v>10</v>
@@ -2771,7 +2771,7 @@
         <v>1010</v>
       </c>
       <c r="C93">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="D93">
         <v>10</v>
@@ -2782,16 +2782,16 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B94">
         <v>1010</v>
       </c>
       <c r="C94">
-        <v>1110</v>
+        <v>1050</v>
       </c>
       <c r="D94">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>48</v>
@@ -2805,7 +2805,7 @@
         <v>1010</v>
       </c>
       <c r="C95">
-        <v>1120</v>
+        <v>1110</v>
       </c>
       <c r="D95">
         <v>15</v>
@@ -2822,7 +2822,7 @@
         <v>1010</v>
       </c>
       <c r="C96">
-        <v>1130</v>
+        <v>1120</v>
       </c>
       <c r="D96">
         <v>15</v>
@@ -2839,7 +2839,7 @@
         <v>1010</v>
       </c>
       <c r="C97">
-        <v>1140</v>
+        <v>1130</v>
       </c>
       <c r="D97">
         <v>15</v>
@@ -2856,7 +2856,7 @@
         <v>1010</v>
       </c>
       <c r="C98">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="D98">
         <v>15</v>
@@ -2873,10 +2873,10 @@
         <v>1010</v>
       </c>
       <c r="C99">
-        <v>4010</v>
+        <v>1150</v>
       </c>
       <c r="D99">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>48</v>
@@ -2890,10 +2890,10 @@
         <v>1010</v>
       </c>
       <c r="C100">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D100">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>48</v>
@@ -2924,10 +2924,10 @@
         <v>1010</v>
       </c>
       <c r="C102">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D102">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>48</v>
@@ -2938,13 +2938,13 @@
         <v>50050</v>
       </c>
       <c r="B103">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C103">
-        <v>30</v>
+        <v>4030</v>
       </c>
       <c r="D103">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>48</v>
@@ -2958,10 +2958,10 @@
         <v>4010</v>
       </c>
       <c r="C104">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D104">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>48</v>
@@ -2972,13 +2972,13 @@
         <v>50050</v>
       </c>
       <c r="B105">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C105">
-        <v>4310</v>
+        <v>20</v>
       </c>
       <c r="D105">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>48</v>
@@ -2992,10 +2992,10 @@
         <v>1010</v>
       </c>
       <c r="C106">
-        <v>5010</v>
+        <v>4310</v>
       </c>
       <c r="D106">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>48</v>
@@ -3009,7 +3009,7 @@
         <v>1010</v>
       </c>
       <c r="C107">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="D107">
         <v>5</v>
@@ -3020,16 +3020,16 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B108">
         <v>1010</v>
       </c>
       <c r="C108">
-        <v>1110</v>
+        <v>5020</v>
       </c>
       <c r="D108">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>48</v>
@@ -3043,7 +3043,7 @@
         <v>1010</v>
       </c>
       <c r="C109">
-        <v>1120</v>
+        <v>1110</v>
       </c>
       <c r="D109">
         <v>15</v>
@@ -3060,7 +3060,7 @@
         <v>1010</v>
       </c>
       <c r="C110">
-        <v>1130</v>
+        <v>1120</v>
       </c>
       <c r="D110">
         <v>15</v>
@@ -3077,7 +3077,7 @@
         <v>1010</v>
       </c>
       <c r="C111">
-        <v>1140</v>
+        <v>1130</v>
       </c>
       <c r="D111">
         <v>15</v>
@@ -3094,7 +3094,7 @@
         <v>1010</v>
       </c>
       <c r="C112">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -3111,10 +3111,10 @@
         <v>1010</v>
       </c>
       <c r="C113">
-        <v>4010</v>
+        <v>1150</v>
       </c>
       <c r="D113">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>48</v>
@@ -3128,10 +3128,10 @@
         <v>1010</v>
       </c>
       <c r="C114">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D114">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>48</v>
@@ -3162,10 +3162,10 @@
         <v>1010</v>
       </c>
       <c r="C116">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D116">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>48</v>
@@ -3193,13 +3193,13 @@
         <v>50060</v>
       </c>
       <c r="B118">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C118">
-        <v>30</v>
+        <v>4030</v>
       </c>
       <c r="D118">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>48</v>
@@ -3213,10 +3213,10 @@
         <v>4010</v>
       </c>
       <c r="C119">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D119">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>48</v>
@@ -3227,13 +3227,13 @@
         <v>50060</v>
       </c>
       <c r="B120">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C120">
-        <v>4310</v>
+        <v>20</v>
       </c>
       <c r="D120">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>48</v>
@@ -3247,10 +3247,10 @@
         <v>1010</v>
       </c>
       <c r="C121">
-        <v>5010</v>
+        <v>4310</v>
       </c>
       <c r="D121">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>48</v>
@@ -3264,7 +3264,7 @@
         <v>1010</v>
       </c>
       <c r="C122">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="D122">
         <v>5</v>
@@ -3275,19 +3275,19 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123">
-        <v>60010</v>
+        <v>50060</v>
       </c>
       <c r="B123">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="C123">
+        <v>5020</v>
+      </c>
+      <c r="D123">
         <v>5</v>
       </c>
-      <c r="D123">
-        <v>1</v>
-      </c>
-      <c r="E123" t="s">
-        <v>49</v>
+      <c r="E123" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -3295,15 +3295,32 @@
         <v>60010</v>
       </c>
       <c r="B124">
-        <v>2</v>
+        <v>2020</v>
       </c>
       <c r="C124">
         <v>5</v>
       </c>
       <c r="D124">
+        <v>1</v>
+      </c>
+      <c r="E124" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125">
+        <v>60010</v>
+      </c>
+      <c r="B125">
+        <v>2</v>
+      </c>
+      <c r="C125">
+        <v>5</v>
+      </c>
+      <c r="D125">
         <v>0</v>
       </c>
-      <c r="E124" t="s">
+      <c r="E125" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -164,7 +164,7 @@
     <t>取引用</t>
   </si>
   <si>
-    <t>交戦ドロップ</t>
+    <t>交戦ドロップ評価+50</t>
   </si>
   <si>
     <t>GetItemType</t>
@@ -232,10 +232,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -254,7 +254,128 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -268,130 +389,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -406,7 +406,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -418,55 +520,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -484,79 +550,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -568,25 +568,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -600,13 +600,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -626,17 +630,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -646,30 +644,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -691,6 +665,32 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
@@ -705,25 +705,25 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -732,118 +732,118 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3298,7 +3298,7 @@
         <v>2020</v>
       </c>
       <c r="C124">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -3315,13 +3315,13 @@
         <v>2</v>
       </c>
       <c r="C125">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D125">
         <v>0</v>
       </c>
       <c r="E125" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -232,10 +232,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -254,9 +254,32 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -268,6 +291,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -276,10 +329,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -297,66 +367,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -365,17 +375,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -389,9 +390,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -403,6 +403,12 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -424,7 +430,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -436,7 +466,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -448,19 +478,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -478,61 +544,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -544,13 +568,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -562,31 +586,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -597,6 +597,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -633,17 +642,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -659,17 +659,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -692,8 +681,19 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -705,145 +705,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2536,7 +2536,7 @@
         <v>1010</v>
       </c>
       <c r="D79">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>48</v>
@@ -2553,7 +2553,7 @@
         <v>1020</v>
       </c>
       <c r="D80">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>48</v>
@@ -2570,7 +2570,7 @@
         <v>1030</v>
       </c>
       <c r="D81">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>48</v>
@@ -2587,7 +2587,7 @@
         <v>1040</v>
       </c>
       <c r="D82">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>48</v>
@@ -2604,7 +2604,7 @@
         <v>1050</v>
       </c>
       <c r="D83">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>48</v>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="70">
   <si>
     <t>Id</t>
   </si>
@@ -232,8 +232,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -260,34 +260,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -298,24 +274,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -329,47 +289,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -390,10 +311,89 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -406,7 +406,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -418,37 +532,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -460,133 +580,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -600,11 +600,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -624,17 +630,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -643,22 +645,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -687,13 +674,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -705,145 +705,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1173,7 +1173,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="19.2727272727273" customWidth="1"/>
@@ -2434,7 +2434,7 @@
         <v>20</v>
       </c>
       <c r="D73">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>48</v>
@@ -2519,7 +2519,7 @@
         <v>20</v>
       </c>
       <c r="D78">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>48</v>
@@ -2527,16 +2527,16 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79">
-        <v>50030</v>
+        <v>50040</v>
       </c>
       <c r="B79">
         <v>1010</v>
       </c>
       <c r="C79">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="D79">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>48</v>
@@ -2544,16 +2544,16 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80">
-        <v>50030</v>
+        <v>50040</v>
       </c>
       <c r="B80">
         <v>1010</v>
       </c>
       <c r="C80">
-        <v>1020</v>
+        <v>4020</v>
       </c>
       <c r="D80">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>48</v>
@@ -2561,16 +2561,16 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81">
-        <v>50030</v>
+        <v>50040</v>
       </c>
       <c r="B81">
         <v>1010</v>
       </c>
       <c r="C81">
-        <v>1030</v>
+        <v>5050</v>
       </c>
       <c r="D81">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>48</v>
@@ -2578,16 +2578,16 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82">
-        <v>50030</v>
+        <v>50040</v>
       </c>
       <c r="B82">
         <v>1010</v>
       </c>
       <c r="C82">
-        <v>1040</v>
+        <v>5060</v>
       </c>
       <c r="D82">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>48</v>
@@ -2595,16 +2595,16 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83">
-        <v>50030</v>
+        <v>50040</v>
       </c>
       <c r="B83">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C83">
-        <v>1050</v>
+        <v>20</v>
       </c>
       <c r="D83">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>48</v>
@@ -2618,10 +2618,10 @@
         <v>1010</v>
       </c>
       <c r="C84">
-        <v>4010</v>
+        <v>4310</v>
       </c>
       <c r="D84">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>48</v>
@@ -2635,10 +2635,10 @@
         <v>1010</v>
       </c>
       <c r="C85">
-        <v>4020</v>
+        <v>1010</v>
       </c>
       <c r="D85">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>48</v>
@@ -2652,10 +2652,10 @@
         <v>1010</v>
       </c>
       <c r="C86">
-        <v>5050</v>
+        <v>1020</v>
       </c>
       <c r="D86">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>48</v>
@@ -2669,10 +2669,10 @@
         <v>1010</v>
       </c>
       <c r="C87">
-        <v>5060</v>
+        <v>1030</v>
       </c>
       <c r="D87">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>48</v>
@@ -2683,13 +2683,13 @@
         <v>50040</v>
       </c>
       <c r="B88">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C88">
-        <v>20</v>
+        <v>1040</v>
       </c>
       <c r="D88">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>48</v>
@@ -2703,10 +2703,10 @@
         <v>1010</v>
       </c>
       <c r="C89">
-        <v>4310</v>
+        <v>1050</v>
       </c>
       <c r="D89">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>48</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>50040</v>
+        <v>50050</v>
       </c>
       <c r="B90">
         <v>1010</v>
       </c>
       <c r="C90">
-        <v>1010</v>
+        <v>1110</v>
       </c>
       <c r="D90">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>48</v>
@@ -2731,16 +2731,16 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>50040</v>
+        <v>50050</v>
       </c>
       <c r="B91">
         <v>1010</v>
       </c>
       <c r="C91">
-        <v>1020</v>
+        <v>1120</v>
       </c>
       <c r="D91">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>48</v>
@@ -2748,16 +2748,16 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>50040</v>
+        <v>50050</v>
       </c>
       <c r="B92">
         <v>1010</v>
       </c>
       <c r="C92">
-        <v>1030</v>
+        <v>1130</v>
       </c>
       <c r="D92">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>48</v>
@@ -2765,16 +2765,16 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>50040</v>
+        <v>50050</v>
       </c>
       <c r="B93">
         <v>1010</v>
       </c>
       <c r="C93">
-        <v>1040</v>
+        <v>1140</v>
       </c>
       <c r="D93">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>48</v>
@@ -2782,16 +2782,16 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94">
-        <v>50040</v>
+        <v>50050</v>
       </c>
       <c r="B94">
         <v>1010</v>
       </c>
       <c r="C94">
-        <v>1050</v>
+        <v>1150</v>
       </c>
       <c r="D94">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>48</v>
@@ -2805,10 +2805,10 @@
         <v>1010</v>
       </c>
       <c r="C95">
-        <v>1110</v>
+        <v>4010</v>
       </c>
       <c r="D95">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>48</v>
@@ -2822,10 +2822,10 @@
         <v>1010</v>
       </c>
       <c r="C96">
-        <v>1120</v>
+        <v>4020</v>
       </c>
       <c r="D96">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>48</v>
@@ -2839,10 +2839,10 @@
         <v>1010</v>
       </c>
       <c r="C97">
-        <v>1130</v>
+        <v>4020</v>
       </c>
       <c r="D97">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>48</v>
@@ -2856,10 +2856,10 @@
         <v>1010</v>
       </c>
       <c r="C98">
-        <v>1140</v>
+        <v>4030</v>
       </c>
       <c r="D98">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>48</v>
@@ -2870,13 +2870,13 @@
         <v>50050</v>
       </c>
       <c r="B99">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C99">
-        <v>1150</v>
+        <v>30</v>
       </c>
       <c r="D99">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>48</v>
@@ -2887,13 +2887,13 @@
         <v>50050</v>
       </c>
       <c r="B100">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C100">
-        <v>4010</v>
+        <v>20</v>
       </c>
       <c r="D100">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>48</v>
@@ -2907,10 +2907,10 @@
         <v>1010</v>
       </c>
       <c r="C101">
-        <v>4020</v>
+        <v>4310</v>
       </c>
       <c r="D101">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>48</v>
@@ -2924,10 +2924,10 @@
         <v>1010</v>
       </c>
       <c r="C102">
-        <v>4020</v>
+        <v>5010</v>
       </c>
       <c r="D102">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>48</v>
@@ -2941,10 +2941,10 @@
         <v>1010</v>
       </c>
       <c r="C103">
-        <v>4030</v>
+        <v>5020</v>
       </c>
       <c r="D103">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>48</v>
@@ -2952,16 +2952,16 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104">
-        <v>50050</v>
+        <v>50060</v>
       </c>
       <c r="B104">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C104">
-        <v>30</v>
+        <v>1110</v>
       </c>
       <c r="D104">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>48</v>
@@ -2969,16 +2969,16 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105">
-        <v>50050</v>
+        <v>50060</v>
       </c>
       <c r="B105">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C105">
-        <v>20</v>
+        <v>1120</v>
       </c>
       <c r="D105">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>48</v>
@@ -2986,16 +2986,16 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106">
-        <v>50050</v>
+        <v>50060</v>
       </c>
       <c r="B106">
         <v>1010</v>
       </c>
       <c r="C106">
-        <v>4310</v>
+        <v>1130</v>
       </c>
       <c r="D106">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>48</v>
@@ -3003,16 +3003,16 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107">
-        <v>50050</v>
+        <v>50060</v>
       </c>
       <c r="B107">
         <v>1010</v>
       </c>
       <c r="C107">
-        <v>5010</v>
+        <v>1140</v>
       </c>
       <c r="D107">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>48</v>
@@ -3020,16 +3020,16 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108">
-        <v>50050</v>
+        <v>50060</v>
       </c>
       <c r="B108">
         <v>1010</v>
       </c>
       <c r="C108">
-        <v>5020</v>
+        <v>1150</v>
       </c>
       <c r="D108">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>48</v>
@@ -3043,10 +3043,10 @@
         <v>1010</v>
       </c>
       <c r="C109">
-        <v>1110</v>
+        <v>4010</v>
       </c>
       <c r="D109">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>48</v>
@@ -3060,10 +3060,10 @@
         <v>1010</v>
       </c>
       <c r="C110">
-        <v>1120</v>
+        <v>4020</v>
       </c>
       <c r="D110">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>48</v>
@@ -3077,10 +3077,10 @@
         <v>1010</v>
       </c>
       <c r="C111">
-        <v>1130</v>
+        <v>4020</v>
       </c>
       <c r="D111">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>48</v>
@@ -3094,10 +3094,10 @@
         <v>1010</v>
       </c>
       <c r="C112">
-        <v>1140</v>
+        <v>4030</v>
       </c>
       <c r="D112">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>48</v>
@@ -3111,10 +3111,10 @@
         <v>1010</v>
       </c>
       <c r="C113">
-        <v>1150</v>
+        <v>4030</v>
       </c>
       <c r="D113">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>48</v>
@@ -3125,13 +3125,13 @@
         <v>50060</v>
       </c>
       <c r="B114">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C114">
-        <v>4010</v>
+        <v>30</v>
       </c>
       <c r="D114">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>48</v>
@@ -3142,13 +3142,13 @@
         <v>50060</v>
       </c>
       <c r="B115">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C115">
-        <v>4020</v>
+        <v>20</v>
       </c>
       <c r="D115">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>48</v>
@@ -3162,10 +3162,10 @@
         <v>1010</v>
       </c>
       <c r="C116">
-        <v>4020</v>
+        <v>4310</v>
       </c>
       <c r="D116">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>48</v>
@@ -3179,10 +3179,10 @@
         <v>1010</v>
       </c>
       <c r="C117">
-        <v>4030</v>
+        <v>5010</v>
       </c>
       <c r="D117">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>48</v>
@@ -3196,10 +3196,10 @@
         <v>1010</v>
       </c>
       <c r="C118">
-        <v>4030</v>
+        <v>5020</v>
       </c>
       <c r="D118">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>48</v>
@@ -3207,120 +3207,35 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119">
-        <v>50060</v>
+        <v>60010</v>
       </c>
       <c r="B119">
-        <v>4010</v>
+        <v>2020</v>
       </c>
       <c r="C119">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D119">
-        <v>10</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>48</v>
+        <v>1</v>
+      </c>
+      <c r="E119" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120">
-        <v>50060</v>
+        <v>60010</v>
       </c>
       <c r="B120">
-        <v>4010</v>
+        <v>2</v>
       </c>
       <c r="C120">
         <v>20</v>
       </c>
       <c r="D120">
-        <v>20</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
-      <c r="A121">
-        <v>50060</v>
-      </c>
-      <c r="B121">
-        <v>1010</v>
-      </c>
-      <c r="C121">
-        <v>4310</v>
-      </c>
-      <c r="D121">
-        <v>30</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
-      <c r="A122">
-        <v>50060</v>
-      </c>
-      <c r="B122">
-        <v>1010</v>
-      </c>
-      <c r="C122">
-        <v>5010</v>
-      </c>
-      <c r="D122">
-        <v>5</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5">
-      <c r="A123">
-        <v>50060</v>
-      </c>
-      <c r="B123">
-        <v>1010</v>
-      </c>
-      <c r="C123">
-        <v>5020</v>
-      </c>
-      <c r="D123">
-        <v>5</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5">
-      <c r="A124">
-        <v>60010</v>
-      </c>
-      <c r="B124">
-        <v>2020</v>
-      </c>
-      <c r="C124">
-        <v>50</v>
-      </c>
-      <c r="D124">
-        <v>1</v>
-      </c>
-      <c r="E124" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5">
-      <c r="A125">
-        <v>60010</v>
-      </c>
-      <c r="B125">
-        <v>2</v>
-      </c>
-      <c r="C125">
-        <v>20</v>
-      </c>
-      <c r="D125">
         <v>0</v>
       </c>
-      <c r="E125" t="s">
+      <c r="E120" t="s">
         <v>8</v>
       </c>
     </row>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="71">
   <si>
     <t>Id</t>
   </si>
@@ -110,6 +110,9 @@
     <t>初級指南書</t>
   </si>
   <si>
+    <t>初級指南書x2</t>
+  </si>
+  <si>
     <t>初級指南書x3</t>
   </si>
   <si>
@@ -119,7 +122,7 @@
     <t>中級指南書</t>
   </si>
   <si>
-    <t>中級指南書xx3</t>
+    <t>中級指南書x3</t>
   </si>
   <si>
     <t>中級指南書x5</t>
@@ -232,10 +235,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -260,6 +263,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -268,22 +287,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -296,24 +300,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -329,30 +318,30 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -373,6 +362,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -381,19 +377,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -406,7 +409,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -418,85 +565,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -508,67 +577,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,13 +589,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -632,35 +635,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -697,6 +674,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -705,25 +708,25 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -732,118 +735,118 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1173,7 +1176,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="19.2727272727273" customWidth="1"/>
@@ -1983,7 +1986,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47">
-        <v>14013</v>
+        <v>14012</v>
       </c>
       <c r="B47">
         <v>1010</v>
@@ -1992,7 +1995,7 @@
         <v>4010</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47" t="s">
         <v>31</v>
@@ -2000,7 +2003,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48">
-        <v>14015</v>
+        <v>14013</v>
       </c>
       <c r="B48">
         <v>1010</v>
@@ -2009,7 +2012,7 @@
         <v>4010</v>
       </c>
       <c r="D48">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E48" t="s">
         <v>32</v>
@@ -2017,16 +2020,16 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49">
-        <v>14020</v>
+        <v>14015</v>
       </c>
       <c r="B49">
         <v>1010</v>
       </c>
       <c r="C49">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E49" t="s">
         <v>33</v>
@@ -2034,7 +2037,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50">
-        <v>14023</v>
+        <v>14020</v>
       </c>
       <c r="B50">
         <v>1010</v>
@@ -2043,7 +2046,7 @@
         <v>4020</v>
       </c>
       <c r="D50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E50" t="s">
         <v>34</v>
@@ -2051,7 +2054,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51">
-        <v>14025</v>
+        <v>14023</v>
       </c>
       <c r="B51">
         <v>1010</v>
@@ -2060,7 +2063,7 @@
         <v>4020</v>
       </c>
       <c r="D51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E51" t="s">
         <v>35</v>
@@ -2068,16 +2071,16 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52">
-        <v>14030</v>
+        <v>14025</v>
       </c>
       <c r="B52">
         <v>1010</v>
       </c>
       <c r="C52">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E52" t="s">
         <v>36</v>
@@ -2085,7 +2088,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53">
-        <v>14033</v>
+        <v>14030</v>
       </c>
       <c r="B53">
         <v>1010</v>
@@ -2094,7 +2097,7 @@
         <v>4030</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E53" t="s">
         <v>37</v>
@@ -2102,7 +2105,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>14035</v>
+        <v>14033</v>
       </c>
       <c r="B54">
         <v>1010</v>
@@ -2111,7 +2114,7 @@
         <v>4030</v>
       </c>
       <c r="D54">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E54" t="s">
         <v>38</v>
@@ -2119,16 +2122,16 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>14040</v>
+        <v>14035</v>
       </c>
       <c r="B55">
         <v>1010</v>
       </c>
       <c r="C55">
-        <v>4040</v>
+        <v>4030</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E55" t="s">
         <v>39</v>
@@ -2136,13 +2139,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56">
-        <v>14310</v>
+        <v>14040</v>
       </c>
       <c r="B56">
         <v>1010</v>
       </c>
       <c r="C56">
-        <v>4310</v>
+        <v>4040</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2153,13 +2156,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57">
-        <v>15040</v>
+        <v>14310</v>
       </c>
       <c r="B57">
         <v>1010</v>
       </c>
       <c r="C57">
-        <v>5040</v>
+        <v>4310</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -2170,13 +2173,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58">
-        <v>15050</v>
+        <v>15040</v>
       </c>
       <c r="B58">
         <v>1010</v>
       </c>
       <c r="C58">
-        <v>5050</v>
+        <v>5040</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2187,13 +2190,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>15060</v>
+        <v>15050</v>
       </c>
       <c r="B59">
         <v>1010</v>
       </c>
       <c r="C59">
-        <v>5060</v>
+        <v>5050</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2204,101 +2207,101 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60">
-        <v>20010</v>
+        <v>15052</v>
       </c>
       <c r="B60">
-        <v>2010</v>
+        <v>1010</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>5050</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E60" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61">
-        <v>31010</v>
+        <v>15053</v>
       </c>
       <c r="B61">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="C61">
-        <v>1010</v>
+        <v>5050</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E61" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62">
-        <v>31020</v>
+        <v>15060</v>
       </c>
       <c r="B62">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="C62">
-        <v>1020</v>
+        <v>5060</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>40010</v>
+        <v>20010</v>
       </c>
       <c r="B63">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="C63">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>40020</v>
+        <v>31010</v>
       </c>
       <c r="B64">
-        <v>2020</v>
+        <v>1020</v>
       </c>
       <c r="C64">
-        <v>10</v>
+        <v>1010</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>40030</v>
+        <v>31020</v>
       </c>
       <c r="B65">
-        <v>2020</v>
+        <v>1020</v>
       </c>
       <c r="C65">
-        <v>5</v>
+        <v>1020</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65" t="s">
         <v>47</v>
@@ -2306,58 +2309,58 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>50010</v>
+        <v>40010</v>
       </c>
       <c r="B66">
-        <v>1020</v>
+        <v>2020</v>
       </c>
       <c r="C66">
-        <v>6010</v>
+        <v>15</v>
       </c>
       <c r="D66">
-        <v>25</v>
-      </c>
-      <c r="E66" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E66" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>50010</v>
+        <v>40020</v>
       </c>
       <c r="B67">
-        <v>1010</v>
+        <v>2020</v>
       </c>
       <c r="C67">
-        <v>4010</v>
+        <v>10</v>
       </c>
       <c r="D67">
-        <v>4</v>
-      </c>
-      <c r="E67" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E67" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>50010</v>
+        <v>40030</v>
       </c>
       <c r="B68">
-        <v>1010</v>
+        <v>2020</v>
       </c>
       <c r="C68">
-        <v>5050</v>
+        <v>5</v>
       </c>
       <c r="D68">
-        <v>5</v>
-      </c>
-      <c r="E68" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E68" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>50020</v>
+        <v>50010</v>
       </c>
       <c r="B69">
         <v>1020</v>
@@ -2369,12 +2372,12 @@
         <v>25</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
-        <v>50020</v>
+        <v>50010</v>
       </c>
       <c r="B70">
         <v>1010</v>
@@ -2386,24 +2389,24 @@
         <v>4</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71">
-        <v>50020</v>
+        <v>50010</v>
       </c>
       <c r="B71">
         <v>1010</v>
       </c>
       <c r="C71">
-        <v>4020</v>
+        <v>5050</v>
       </c>
       <c r="D71">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2411,16 +2414,16 @@
         <v>50020</v>
       </c>
       <c r="B72">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="C72">
-        <v>5050</v>
+        <v>6010</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2428,67 +2431,67 @@
         <v>50020</v>
       </c>
       <c r="B73">
+        <v>1010</v>
+      </c>
+      <c r="C73">
         <v>4010</v>
       </c>
-      <c r="C73">
-        <v>20</v>
-      </c>
       <c r="D73">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B74">
         <v>1010</v>
       </c>
       <c r="C74">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B75">
         <v>1010</v>
       </c>
       <c r="C75">
-        <v>4020</v>
+        <v>5050</v>
       </c>
       <c r="D75">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B76">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C76">
-        <v>5050</v>
+        <v>20</v>
       </c>
       <c r="D76">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2499,13 +2502,13 @@
         <v>1010</v>
       </c>
       <c r="C77">
-        <v>5060</v>
+        <v>4010</v>
       </c>
       <c r="D77">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2513,152 +2516,152 @@
         <v>50030</v>
       </c>
       <c r="B78">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C78">
-        <v>20</v>
+        <v>4020</v>
       </c>
       <c r="D78">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B79">
         <v>1010</v>
       </c>
       <c r="C79">
-        <v>4010</v>
+        <v>5050</v>
       </c>
       <c r="D79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B80">
         <v>1010</v>
       </c>
       <c r="C80">
-        <v>4020</v>
+        <v>5060</v>
       </c>
       <c r="D80">
         <v>8</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B81">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C81">
-        <v>5050</v>
+        <v>20</v>
       </c>
       <c r="D81">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B82">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="C82">
-        <v>5060</v>
+        <v>6020</v>
       </c>
       <c r="D82">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B83">
-        <v>4010</v>
+        <v>1020</v>
       </c>
       <c r="C83">
-        <v>20</v>
+        <v>6030</v>
       </c>
       <c r="D83">
         <v>25</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B84">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="C84">
-        <v>4310</v>
+        <v>6040</v>
       </c>
       <c r="D84">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B85">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="C85">
-        <v>1010</v>
+        <v>6050</v>
       </c>
       <c r="D85">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B86">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="C86">
-        <v>1020</v>
+        <v>6060</v>
       </c>
       <c r="D86">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2669,13 +2672,13 @@
         <v>1010</v>
       </c>
       <c r="C87">
-        <v>1030</v>
+        <v>4010</v>
       </c>
       <c r="D87">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2686,13 +2689,13 @@
         <v>1010</v>
       </c>
       <c r="C88">
-        <v>1040</v>
+        <v>4020</v>
       </c>
       <c r="D88">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2703,149 +2706,149 @@
         <v>1010</v>
       </c>
       <c r="C89">
-        <v>1050</v>
+        <v>5050</v>
       </c>
       <c r="D89">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B90">
         <v>1010</v>
       </c>
       <c r="C90">
-        <v>1110</v>
+        <v>5060</v>
       </c>
       <c r="D90">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B91">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C91">
-        <v>1120</v>
+        <v>20</v>
       </c>
       <c r="D91">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B92">
         <v>1010</v>
       </c>
       <c r="C92">
-        <v>1130</v>
+        <v>4310</v>
       </c>
       <c r="D92">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B93">
         <v>1010</v>
       </c>
       <c r="C93">
-        <v>1140</v>
+        <v>1010</v>
       </c>
       <c r="D93">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B94">
         <v>1010</v>
       </c>
       <c r="C94">
-        <v>1150</v>
+        <v>1020</v>
       </c>
       <c r="D94">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B95">
         <v>1010</v>
       </c>
       <c r="C95">
-        <v>4010</v>
+        <v>1030</v>
       </c>
       <c r="D95">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B96">
         <v>1010</v>
       </c>
       <c r="C96">
-        <v>4020</v>
+        <v>1040</v>
       </c>
       <c r="D96">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B97">
         <v>1010</v>
       </c>
       <c r="C97">
-        <v>4020</v>
+        <v>1050</v>
       </c>
       <c r="D97">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2856,13 +2859,13 @@
         <v>1010</v>
       </c>
       <c r="C98">
-        <v>4030</v>
+        <v>1110</v>
       </c>
       <c r="D98">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2870,16 +2873,16 @@
         <v>50050</v>
       </c>
       <c r="B99">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C99">
-        <v>30</v>
+        <v>1120</v>
       </c>
       <c r="D99">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2887,16 +2890,16 @@
         <v>50050</v>
       </c>
       <c r="B100">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C100">
-        <v>20</v>
+        <v>1130</v>
       </c>
       <c r="D100">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2907,13 +2910,13 @@
         <v>1010</v>
       </c>
       <c r="C101">
-        <v>4310</v>
+        <v>1140</v>
       </c>
       <c r="D101">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2924,13 +2927,13 @@
         <v>1010</v>
       </c>
       <c r="C102">
-        <v>5010</v>
+        <v>1150</v>
       </c>
       <c r="D102">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2941,149 +2944,149 @@
         <v>1010</v>
       </c>
       <c r="C103">
-        <v>5020</v>
+        <v>4010</v>
       </c>
       <c r="D103">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B104">
         <v>1010</v>
       </c>
       <c r="C104">
-        <v>1110</v>
+        <v>4020</v>
       </c>
       <c r="D104">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B105">
         <v>1010</v>
       </c>
       <c r="C105">
-        <v>1120</v>
+        <v>4020</v>
       </c>
       <c r="D105">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B106">
         <v>1010</v>
       </c>
       <c r="C106">
-        <v>1130</v>
+        <v>4030</v>
       </c>
       <c r="D106">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B107">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C107">
-        <v>1140</v>
+        <v>30</v>
       </c>
       <c r="D107">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B108">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C108">
-        <v>1150</v>
+        <v>20</v>
       </c>
       <c r="D108">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B109">
         <v>1010</v>
       </c>
       <c r="C109">
-        <v>4010</v>
+        <v>4310</v>
       </c>
       <c r="D109">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B110">
         <v>1010</v>
       </c>
       <c r="C110">
-        <v>4020</v>
+        <v>5010</v>
       </c>
       <c r="D110">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B111">
         <v>1010</v>
       </c>
       <c r="C111">
-        <v>4020</v>
+        <v>5020</v>
       </c>
       <c r="D111">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -3094,13 +3097,13 @@
         <v>1010</v>
       </c>
       <c r="C112">
-        <v>4030</v>
+        <v>1110</v>
       </c>
       <c r="D112">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -3111,13 +3114,13 @@
         <v>1010</v>
       </c>
       <c r="C113">
-        <v>4030</v>
+        <v>1120</v>
       </c>
       <c r="D113">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -3125,16 +3128,16 @@
         <v>50060</v>
       </c>
       <c r="B114">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C114">
-        <v>30</v>
+        <v>1130</v>
       </c>
       <c r="D114">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -3142,16 +3145,16 @@
         <v>50060</v>
       </c>
       <c r="B115">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C115">
-        <v>20</v>
+        <v>1140</v>
       </c>
       <c r="D115">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -3162,13 +3165,13 @@
         <v>1010</v>
       </c>
       <c r="C116">
-        <v>4310</v>
+        <v>1150</v>
       </c>
       <c r="D116">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -3179,13 +3182,13 @@
         <v>1010</v>
       </c>
       <c r="C117">
-        <v>5010</v>
+        <v>4010</v>
       </c>
       <c r="D117">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -3196,46 +3199,182 @@
         <v>1010</v>
       </c>
       <c r="C118">
-        <v>5020</v>
+        <v>4020</v>
       </c>
       <c r="D118">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119">
-        <v>60010</v>
+        <v>50060</v>
       </c>
       <c r="B119">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="C119">
-        <v>50</v>
+        <v>4020</v>
       </c>
       <c r="D119">
-        <v>1</v>
-      </c>
-      <c r="E119" t="s">
+        <v>8</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120">
+        <v>50060</v>
+      </c>
+      <c r="B120">
+        <v>1010</v>
+      </c>
+      <c r="C120">
+        <v>4030</v>
+      </c>
+      <c r="D120">
+        <v>12</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121">
+        <v>50060</v>
+      </c>
+      <c r="B121">
+        <v>1010</v>
+      </c>
+      <c r="C121">
+        <v>4030</v>
+      </c>
+      <c r="D121">
+        <v>12</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122">
+        <v>50060</v>
+      </c>
+      <c r="B122">
+        <v>4010</v>
+      </c>
+      <c r="C122">
+        <v>30</v>
+      </c>
+      <c r="D122">
+        <v>10</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123">
+        <v>50060</v>
+      </c>
+      <c r="B123">
+        <v>4010</v>
+      </c>
+      <c r="C123">
+        <v>20</v>
+      </c>
+      <c r="D123">
+        <v>25</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124">
+        <v>50060</v>
+      </c>
+      <c r="B124">
+        <v>1010</v>
+      </c>
+      <c r="C124">
+        <v>4310</v>
+      </c>
+      <c r="D124">
+        <v>30</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125">
+        <v>50060</v>
+      </c>
+      <c r="B125">
+        <v>1010</v>
+      </c>
+      <c r="C125">
+        <v>5010</v>
+      </c>
+      <c r="D125">
+        <v>5</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126">
+        <v>50060</v>
+      </c>
+      <c r="B126">
+        <v>1010</v>
+      </c>
+      <c r="C126">
+        <v>5020</v>
+      </c>
+      <c r="D126">
+        <v>5</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127">
         <v>60010</v>
       </c>
-      <c r="B120">
+      <c r="B127">
+        <v>2020</v>
+      </c>
+      <c r="C127">
+        <v>50</v>
+      </c>
+      <c r="D127">
+        <v>1</v>
+      </c>
+      <c r="E127" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128">
+        <v>60010</v>
+      </c>
+      <c r="B128">
         <v>2</v>
       </c>
-      <c r="C120">
+      <c r="C128">
         <v>20</v>
       </c>
-      <c r="D120">
+      <c r="D128">
         <v>0</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E128" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3254,7 +3393,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3262,7 +3401,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3270,7 +3409,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3278,7 +3417,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3286,7 +3425,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3302,7 +3441,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3310,7 +3449,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3318,7 +3457,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3326,7 +3465,7 @@
         <v>71</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3334,7 +3473,7 @@
         <v>100</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3342,7 +3481,7 @@
         <v>101</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3350,7 +3489,7 @@
         <v>210</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3358,7 +3497,7 @@
         <v>1010</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3366,7 +3505,7 @@
         <v>1020</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3374,7 +3513,7 @@
         <v>2010</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3382,7 +3521,7 @@
         <v>2020</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3390,7 +3529,7 @@
         <v>2030</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3398,7 +3537,7 @@
         <v>2040</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3406,7 +3545,7 @@
         <v>4010</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3414,7 +3553,7 @@
         <v>4020</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -235,10 +235,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -256,26 +256,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -286,8 +278,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -300,35 +324,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -348,7 +355,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,41 +392,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -409,13 +409,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -427,7 +439,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -439,13 +463,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -463,7 +493,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -475,7 +505,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -487,109 +583,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -600,6 +600,24 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -614,6 +632,32 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -637,16 +681,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -665,41 +700,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -708,7 +708,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -717,136 +717,136 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignme